--- a/pib_nowcast/data/news_impacts.xlsx
+++ b/pib_nowcast/data/news_impacts.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,7 +757,7 @@
       <c r="E15" t="n">
         <v>0.005716107041734316</v>
       </c>
-      <c r="F15" s="2" t="n">
+      <c r="F15" s="1" t="n">
         <v>46197</v>
       </c>
     </row>
@@ -777,7 +777,7 @@
       <c r="E16" t="n">
         <v>0.005303860885268083</v>
       </c>
-      <c r="F16" s="2" t="n">
+      <c r="F16" s="1" t="n">
         <v>46197</v>
       </c>
     </row>
@@ -797,7 +797,7 @@
       <c r="E17" t="n">
         <v>-0.02394831869986776</v>
       </c>
-      <c r="F17" s="2" t="n">
+      <c r="F17" s="1" t="n">
         <v>46197</v>
       </c>
     </row>
@@ -817,7 +817,7 @@
       <c r="E18" t="n">
         <v>0.118809179230305</v>
       </c>
-      <c r="F18" s="2" t="n">
+      <c r="F18" s="1" t="n">
         <v>46197</v>
       </c>
     </row>
@@ -837,7 +837,7 @@
       <c r="E19" t="n">
         <v>-0.01351229883953193</v>
       </c>
-      <c r="F19" s="2" t="n">
+      <c r="F19" s="1" t="n">
         <v>46197</v>
       </c>
     </row>
@@ -857,7 +857,7 @@
       <c r="E20" t="n">
         <v>0.0220634343859287</v>
       </c>
-      <c r="F20" s="2" t="n">
+      <c r="F20" s="1" t="n">
         <v>46197</v>
       </c>
     </row>
@@ -877,7 +877,7 @@
       <c r="E21" t="n">
         <v>-0.03396927801421143</v>
       </c>
-      <c r="F21" s="2" t="n">
+      <c r="F21" s="1" t="n">
         <v>46197</v>
       </c>
     </row>
@@ -897,7 +897,7 @@
       <c r="E22" t="n">
         <v>-0.01740045793069086</v>
       </c>
-      <c r="F22" s="2" t="n">
+      <c r="F22" s="1" t="n">
         <v>46197</v>
       </c>
     </row>
@@ -917,7 +917,7 @@
       <c r="E23" t="n">
         <v>0.007190159433840849</v>
       </c>
-      <c r="F23" s="2" t="n">
+      <c r="F23" s="1" t="n">
         <v>46197</v>
       </c>
     </row>
@@ -937,7 +937,7 @@
       <c r="E24" t="n">
         <v>-0.03368498543109711</v>
       </c>
-      <c r="F24" s="2" t="n">
+      <c r="F24" s="1" t="n">
         <v>46197</v>
       </c>
     </row>
@@ -957,7 +957,7 @@
       <c r="E25" t="n">
         <v>0.004358680351470958</v>
       </c>
-      <c r="F25" s="2" t="n">
+      <c r="F25" s="1" t="n">
         <v>46197</v>
       </c>
     </row>
@@ -977,7 +977,7 @@
       <c r="E26" t="n">
         <v>-0.01960064106362932</v>
       </c>
-      <c r="F26" s="2" t="n">
+      <c r="F26" s="1" t="n">
         <v>46197</v>
       </c>
     </row>
@@ -997,8 +997,308 @@
       <c r="E27" t="n">
         <v>-0.00491084285846865</v>
       </c>
-      <c r="F27" s="2" t="n">
-        <v>46197</v>
+      <c r="F27" s="1" t="n">
+        <v>46197</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>all prior revisions</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.001411214935714386</v>
+      </c>
+      <c r="F28" s="1" t="n">
+        <v>46202</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>igp10</t>
+        </is>
+      </c>
+      <c r="D29" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E29" t="n">
+        <v>-0.002608184372946774</v>
+      </c>
+      <c r="F29" s="1" t="n">
+        <v>46202</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>igpm</t>
+        </is>
+      </c>
+      <c r="D30" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E30" t="n">
+        <v>-0.0008700970987201401</v>
+      </c>
+      <c r="F30" s="1" t="n">
+        <v>46202</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ipam</t>
+        </is>
+      </c>
+      <c r="D31" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E31" t="n">
+        <v>-5.217991094694235e-05</v>
+      </c>
+      <c r="F31" s="1" t="n">
+        <v>46202</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>ipca15</t>
+        </is>
+      </c>
+      <c r="D32" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E32" t="n">
+        <v>-0.0007298351479237805</v>
+      </c>
+      <c r="F32" s="1" t="n">
+        <v>46202</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>all prior revisions</t>
+        </is>
+      </c>
+      <c r="D33" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.001411214935714386</v>
+      </c>
+      <c r="F33" s="1" t="n">
+        <v>46202</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>igp10</t>
+        </is>
+      </c>
+      <c r="D34" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E34" t="n">
+        <v>-0.002608184372946774</v>
+      </c>
+      <c r="F34" s="1" t="n">
+        <v>46202</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>igpm</t>
+        </is>
+      </c>
+      <c r="D35" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E35" t="n">
+        <v>-0.0008700970987201401</v>
+      </c>
+      <c r="F35" s="1" t="n">
+        <v>46202</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>ipam</t>
+        </is>
+      </c>
+      <c r="D36" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-5.217991094694235e-05</v>
+      </c>
+      <c r="F36" s="1" t="n">
+        <v>46202</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>ipca15</t>
+        </is>
+      </c>
+      <c r="D37" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E37" t="n">
+        <v>-0.0007298351479237805</v>
+      </c>
+      <c r="F37" s="1" t="n">
+        <v>46202</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>all prior revisions</t>
+        </is>
+      </c>
+      <c r="D38" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.001411214935714386</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>46202</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>igp10</t>
+        </is>
+      </c>
+      <c r="D39" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E39" t="n">
+        <v>-0.002608184372946774</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>46202</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>igpm</t>
+        </is>
+      </c>
+      <c r="D40" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E40" t="n">
+        <v>-0.0008700970987201401</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>46202</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>ipam</t>
+        </is>
+      </c>
+      <c r="D41" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E41" t="n">
+        <v>-5.217991094694235e-05</v>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>46202</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>ipca15</t>
+        </is>
+      </c>
+      <c r="D42" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E42" t="n">
+        <v>-0.0007298351479237805</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>46202</v>
       </c>
     </row>
   </sheetData>

--- a/pib_nowcast/data/news_impacts.xlsx
+++ b/pib_nowcast/data/news_impacts.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F426"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1217,7 +1217,7 @@
       <c r="E38" t="n">
         <v>0.001411214935714386</v>
       </c>
-      <c r="F38" s="2" t="n">
+      <c r="F38" s="1" t="n">
         <v>46202</v>
       </c>
     </row>
@@ -1237,7 +1237,7 @@
       <c r="E39" t="n">
         <v>-0.002608184372946774</v>
       </c>
-      <c r="F39" s="2" t="n">
+      <c r="F39" s="1" t="n">
         <v>46202</v>
       </c>
     </row>
@@ -1257,7 +1257,7 @@
       <c r="E40" t="n">
         <v>-0.0008700970987201401</v>
       </c>
-      <c r="F40" s="2" t="n">
+      <c r="F40" s="1" t="n">
         <v>46202</v>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
       <c r="E41" t="n">
         <v>-5.217991094694235e-05</v>
       </c>
-      <c r="F41" s="2" t="n">
+      <c r="F41" s="1" t="n">
         <v>46202</v>
       </c>
     </row>
@@ -1297,8 +1297,7688 @@
       <c r="E42" t="n">
         <v>-0.0007298351479237805</v>
       </c>
-      <c r="F42" s="2" t="n">
+      <c r="F42" s="1" t="n">
         <v>46202</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" s="1" t="n">
+        <v>45778</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>all prior revisions</t>
+        </is>
+      </c>
+      <c r="D43" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E43" t="n">
+        <v>-6.626529447541624e-05</v>
+      </c>
+      <c r="F43" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>caged_estoque</t>
+        </is>
+      </c>
+      <c r="D44" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E44" t="n">
+        <v>-1.841675137711242e-08</v>
+      </c>
+      <c r="F44" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>cons_energ_comercial</t>
+        </is>
+      </c>
+      <c r="D45" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E45" t="n">
+        <v>-4.353922066907349e-05</v>
+      </c>
+      <c r="F45" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>cons_energ_industrial</t>
+        </is>
+      </c>
+      <c r="D46" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E46" t="n">
+        <v>-3.949361567708235e-06</v>
+      </c>
+      <c r="F46" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+      <c r="B47" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>cons_energ_outros</t>
+        </is>
+      </c>
+      <c r="D47" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E47" t="n">
+        <v>-4.353922066907358e-05</v>
+      </c>
+      <c r="F47" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+      <c r="B48" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>cons_energ_residencial</t>
+        </is>
+      </c>
+      <c r="D48" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E48" t="n">
+        <v>-4.034182748090585e-05</v>
+      </c>
+      <c r="F48" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr"/>
+      <c r="B49" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>prod_aco_bruto</t>
+        </is>
+      </c>
+      <c r="D49" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E49" t="n">
+        <v>-2.159534205555353e-05</v>
+      </c>
+      <c r="F49" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr"/>
+      <c r="B50" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>renda_disponivel_familias_restrita</t>
+        </is>
+      </c>
+      <c r="D50" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E50" t="n">
+        <v>-3.802700469633388e-08</v>
+      </c>
+      <c r="F50" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+      <c r="B51" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>icc_fecomercio</t>
+        </is>
+      </c>
+      <c r="D51" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E51" t="n">
+        <v>-6.347686022607787e-09</v>
+      </c>
+      <c r="F51" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+      <c r="B52" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>icea_fecomercio</t>
+        </is>
+      </c>
+      <c r="D52" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E52" t="n">
+        <v>7.570392316677181e-09</v>
+      </c>
+      <c r="F52" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr"/>
+      <c r="B53" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>ief_fecomercio</t>
+        </is>
+      </c>
+      <c r="D53" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E53" t="n">
+        <v>-6.023736961001136e-08</v>
+      </c>
+      <c r="F53" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr"/>
+      <c r="B54" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>igp10</t>
+        </is>
+      </c>
+      <c r="D54" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E54" t="n">
+        <v>-5.831284850237467e-07</v>
+      </c>
+      <c r="F54" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr"/>
+      <c r="B55" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>igpm</t>
+        </is>
+      </c>
+      <c r="D55" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E55" t="n">
+        <v>1.557217896977457e-05</v>
+      </c>
+      <c r="F55" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr"/>
+      <c r="B56" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>ipam</t>
+        </is>
+      </c>
+      <c r="D56" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E56" t="n">
+        <v>9.091691628917693e-06</v>
+      </c>
+      <c r="F56" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr"/>
+      <c r="B57" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>ipc_fipe</t>
+        </is>
+      </c>
+      <c r="D57" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E57" t="n">
+        <v>5.899241006441921e-07</v>
+      </c>
+      <c r="F57" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr"/>
+      <c r="B58" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>ipca15</t>
+        </is>
+      </c>
+      <c r="D58" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E58" t="n">
+        <v>4.593355911787993e-07</v>
+      </c>
+      <c r="F58" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr"/>
+      <c r="B59" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>caged_estoque</t>
+        </is>
+      </c>
+      <c r="D59" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E59" t="n">
+        <v>1.153214877039098e-09</v>
+      </c>
+      <c r="F59" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr"/>
+      <c r="B60" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>cons_energ_comercial</t>
+        </is>
+      </c>
+      <c r="D60" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E60" t="n">
+        <v>-3.340108326321829e-06</v>
+      </c>
+      <c r="F60" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr"/>
+      <c r="B61" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>cons_energ_industrial</t>
+        </is>
+      </c>
+      <c r="D61" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E61" t="n">
+        <v>-5.624797288076677e-06</v>
+      </c>
+      <c r="F61" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr"/>
+      <c r="B62" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>cons_energ_outros</t>
+        </is>
+      </c>
+      <c r="D62" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E62" t="n">
+        <v>-3.340108326321842e-06</v>
+      </c>
+      <c r="F62" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr"/>
+      <c r="B63" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>cons_energ_residencial</t>
+        </is>
+      </c>
+      <c r="D63" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E63" t="n">
+        <v>9.279838169959956e-06</v>
+      </c>
+      <c r="F63" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr"/>
+      <c r="B64" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>prod_aco_bruto</t>
+        </is>
+      </c>
+      <c r="D64" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E64" t="n">
+        <v>4.365185987741091e-06</v>
+      </c>
+      <c r="F64" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr"/>
+      <c r="B65" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>renda_disponivel_familias_restrita</t>
+        </is>
+      </c>
+      <c r="D65" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E65" t="n">
+        <v>-1.406279411440646e-08</v>
+      </c>
+      <c r="F65" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr"/>
+      <c r="B66" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>icc_fecomercio</t>
+        </is>
+      </c>
+      <c r="D66" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E66" t="n">
+        <v>-2.287559720438153e-10</v>
+      </c>
+      <c r="F66" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr"/>
+      <c r="B67" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>icea_fecomercio</t>
+        </is>
+      </c>
+      <c r="D67" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E67" t="n">
+        <v>7.086075448808836e-10</v>
+      </c>
+      <c r="F67" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr"/>
+      <c r="B68" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>igp10</t>
+        </is>
+      </c>
+      <c r="D68" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E68" t="n">
+        <v>4.643968731989389e-08</v>
+      </c>
+      <c r="F68" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr"/>
+      <c r="B69" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>igpm</t>
+        </is>
+      </c>
+      <c r="D69" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E69" t="n">
+        <v>-9.873893466466123e-08</v>
+      </c>
+      <c r="F69" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr"/>
+      <c r="B70" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>ipam</t>
+        </is>
+      </c>
+      <c r="D70" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E70" t="n">
+        <v>-3.408560845002734e-08</v>
+      </c>
+      <c r="F70" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr"/>
+      <c r="B71" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>ipc_fipe</t>
+        </is>
+      </c>
+      <c r="D71" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E71" t="n">
+        <v>-1.130115868910291e-09</v>
+      </c>
+      <c r="F71" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr"/>
+      <c r="B72" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>ipca15</t>
+        </is>
+      </c>
+      <c r="D72" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E72" t="n">
+        <v>-1.5974852311021e-09</v>
+      </c>
+      <c r="F72" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr"/>
+      <c r="B73" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>caged_estoque</t>
+        </is>
+      </c>
+      <c r="D73" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E73" t="n">
+        <v>1.012416830918402e-08</v>
+      </c>
+      <c r="F73" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr"/>
+      <c r="B74" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>cons_energ_comercial</t>
+        </is>
+      </c>
+      <c r="D74" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E74" t="n">
+        <v>-1.933878207098305e-07</v>
+      </c>
+      <c r="F74" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr"/>
+      <c r="B75" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>cons_energ_industrial</t>
+        </is>
+      </c>
+      <c r="D75" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1.912045667873641e-06</v>
+      </c>
+      <c r="F75" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr"/>
+      <c r="B76" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>cons_energ_outros</t>
+        </is>
+      </c>
+      <c r="D76" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E76" t="n">
+        <v>-1.933878207098304e-07</v>
+      </c>
+      <c r="F76" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr"/>
+      <c r="B77" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>cons_energ_residencial</t>
+        </is>
+      </c>
+      <c r="D77" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E77" t="n">
+        <v>-4.682936264692832e-07</v>
+      </c>
+      <c r="F77" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr"/>
+      <c r="B78" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>prod_aco_bruto</t>
+        </is>
+      </c>
+      <c r="D78" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E78" t="n">
+        <v>2.691797810027552e-06</v>
+      </c>
+      <c r="F78" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr"/>
+      <c r="B79" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>renda_disponivel_familias_restrita</t>
+        </is>
+      </c>
+      <c r="D79" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E79" t="n">
+        <v>-5.400004167126128e-10</v>
+      </c>
+      <c r="F79" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr"/>
+      <c r="B80" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>icc_fecomercio</t>
+        </is>
+      </c>
+      <c r="D80" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E80" t="n">
+        <v>6.721039539782534e-09</v>
+      </c>
+      <c r="F80" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr"/>
+      <c r="B81" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>icea_fecomercio</t>
+        </is>
+      </c>
+      <c r="D81" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E81" t="n">
+        <v>8.45803867624905e-09</v>
+      </c>
+      <c r="F81" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr"/>
+      <c r="B82" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>ief_fecomercio</t>
+        </is>
+      </c>
+      <c r="D82" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E82" t="n">
+        <v>-2.100497646903858e-08</v>
+      </c>
+      <c r="F82" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr"/>
+      <c r="B83" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>igp10</t>
+        </is>
+      </c>
+      <c r="D83" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E83" t="n">
+        <v>-3.366283490174172e-07</v>
+      </c>
+      <c r="F83" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr"/>
+      <c r="B84" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>igpm</t>
+        </is>
+      </c>
+      <c r="D84" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E84" t="n">
+        <v>6.180646785790646e-07</v>
+      </c>
+      <c r="F84" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr"/>
+      <c r="B85" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>ipam</t>
+        </is>
+      </c>
+      <c r="D85" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E85" t="n">
+        <v>1.580914462446119e-07</v>
+      </c>
+      <c r="F85" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr"/>
+      <c r="B86" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>ipca15</t>
+        </is>
+      </c>
+      <c r="D86" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E86" t="n">
+        <v>-2.022343081493345e-08</v>
+      </c>
+      <c r="F86" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr"/>
+      <c r="B87" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>caged_estoque</t>
+        </is>
+      </c>
+      <c r="D87" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E87" t="n">
+        <v>-9.146590981340076e-08</v>
+      </c>
+      <c r="F87" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr"/>
+      <c r="B88" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>cons_energ_comercial</t>
+        </is>
+      </c>
+      <c r="D88" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E88" t="n">
+        <v>1.778625284815955e-05</v>
+      </c>
+      <c r="F88" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr"/>
+      <c r="B89" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>cons_energ_industrial</t>
+        </is>
+      </c>
+      <c r="D89" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E89" t="n">
+        <v>6.858818025047004e-06</v>
+      </c>
+      <c r="F89" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr"/>
+      <c r="B90" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>cons_energ_outros</t>
+        </is>
+      </c>
+      <c r="D90" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E90" t="n">
+        <v>1.778625284815958e-05</v>
+      </c>
+      <c r="F90" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr"/>
+      <c r="B91" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>cons_energ_residencial</t>
+        </is>
+      </c>
+      <c r="D91" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E91" t="n">
+        <v>4.879014932391213e-06</v>
+      </c>
+      <c r="F91" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr"/>
+      <c r="B92" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>prod_aco_bruto</t>
+        </is>
+      </c>
+      <c r="D92" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E92" t="n">
+        <v>-3.54755660178476e-07</v>
+      </c>
+      <c r="F92" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr"/>
+      <c r="B93" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>renda_disponivel_familias_restrita</t>
+        </is>
+      </c>
+      <c r="D93" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E93" t="n">
+        <v>2.99222305178381e-08</v>
+      </c>
+      <c r="F93" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr"/>
+      <c r="B94" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>icc_fecomercio</t>
+        </is>
+      </c>
+      <c r="D94" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E94" t="n">
+        <v>-1.255029255047148e-08</v>
+      </c>
+      <c r="F94" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr"/>
+      <c r="B95" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>icea_fecomercio</t>
+        </is>
+      </c>
+      <c r="D95" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E95" t="n">
+        <v>-9.908196040963476e-09</v>
+      </c>
+      <c r="F95" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr"/>
+      <c r="B96" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>ief_fecomercio</t>
+        </is>
+      </c>
+      <c r="D96" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E96" t="n">
+        <v>4.99983057801477e-08</v>
+      </c>
+      <c r="F96" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr"/>
+      <c r="B97" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>igp10</t>
+        </is>
+      </c>
+      <c r="D97" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E97" t="n">
+        <v>-1.02510683299169e-06</v>
+      </c>
+      <c r="F97" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr"/>
+      <c r="B98" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>igpm</t>
+        </is>
+      </c>
+      <c r="D98" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E98" t="n">
+        <v>1.820246203868549e-06</v>
+      </c>
+      <c r="F98" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr"/>
+      <c r="B99" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>ipam</t>
+        </is>
+      </c>
+      <c r="D99" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E99" t="n">
+        <v>8.132358467458134e-07</v>
+      </c>
+      <c r="F99" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr"/>
+      <c r="B100" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>ipc_fipe</t>
+        </is>
+      </c>
+      <c r="D100" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E100" t="n">
+        <v>-8.813141477336209e-08</v>
+      </c>
+      <c r="F100" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr"/>
+      <c r="B101" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>ipca15</t>
+        </is>
+      </c>
+      <c r="D101" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E101" t="n">
+        <v>-2.257420078970991e-07</v>
+      </c>
+      <c r="F101" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr"/>
+      <c r="B102" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>caged_estoque</t>
+        </is>
+      </c>
+      <c r="D102" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E102" t="n">
+        <v>-1.133025599163038e-08</v>
+      </c>
+      <c r="F102" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr"/>
+      <c r="B103" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>cons_energ_comercial</t>
+        </is>
+      </c>
+      <c r="D103" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E103" t="n">
+        <v>-0.0002731638881253252</v>
+      </c>
+      <c r="F103" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr"/>
+      <c r="B104" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>cons_energ_industrial</t>
+        </is>
+      </c>
+      <c r="D104" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E104" t="n">
+        <v>-3.361028946407739e-06</v>
+      </c>
+      <c r="F104" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr"/>
+      <c r="B105" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>cons_energ_outros</t>
+        </is>
+      </c>
+      <c r="D105" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E105" t="n">
+        <v>-0.0002731638881253264</v>
+      </c>
+      <c r="F105" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr"/>
+      <c r="B106" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>cons_energ_residencial</t>
+        </is>
+      </c>
+      <c r="D106" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E106" t="n">
+        <v>-0.0001878594928344081</v>
+      </c>
+      <c r="F106" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr"/>
+      <c r="B107" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>prod_aco_bruto</t>
+        </is>
+      </c>
+      <c r="D107" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E107" t="n">
+        <v>-1.380317306304696e-05</v>
+      </c>
+      <c r="F107" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr"/>
+      <c r="B108" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>renda_disponivel_familias_restrita</t>
+        </is>
+      </c>
+      <c r="D108" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E108" t="n">
+        <v>7.625709126346174e-09</v>
+      </c>
+      <c r="F108" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr"/>
+      <c r="B109" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>icc_fecomercio</t>
+        </is>
+      </c>
+      <c r="D109" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E109" t="n">
+        <v>2.177279985136486e-10</v>
+      </c>
+      <c r="F109" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr"/>
+      <c r="B110" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>icea_fecomercio</t>
+        </is>
+      </c>
+      <c r="D110" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E110" t="n">
+        <v>2.874624089860853e-10</v>
+      </c>
+      <c r="F110" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr"/>
+      <c r="B111" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>ief_fecomercio</t>
+        </is>
+      </c>
+      <c r="D111" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E111" t="n">
+        <v>-3.017398137494154e-10</v>
+      </c>
+      <c r="F111" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr"/>
+      <c r="B112" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>igp10</t>
+        </is>
+      </c>
+      <c r="D112" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E112" t="n">
+        <v>-1.798932553084492e-07</v>
+      </c>
+      <c r="F112" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr"/>
+      <c r="B113" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>igpm</t>
+        </is>
+      </c>
+      <c r="D113" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E113" t="n">
+        <v>1.691736879950699e-07</v>
+      </c>
+      <c r="F113" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr"/>
+      <c r="B114" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>ipam</t>
+        </is>
+      </c>
+      <c r="D114" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E114" t="n">
+        <v>1.115176100640181e-07</v>
+      </c>
+      <c r="F114" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr"/>
+      <c r="B115" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>ipc_fipe</t>
+        </is>
+      </c>
+      <c r="D115" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E115" t="n">
+        <v>-1.729503491462086e-10</v>
+      </c>
+      <c r="F115" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr"/>
+      <c r="B116" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>ipca15</t>
+        </is>
+      </c>
+      <c r="D116" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E116" t="n">
+        <v>1.693275710415724e-10</v>
+      </c>
+      <c r="F116" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr"/>
+      <c r="B117" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>caged_estoque</t>
+        </is>
+      </c>
+      <c r="D117" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E117" t="n">
+        <v>-6.063501692324043e-10</v>
+      </c>
+      <c r="F117" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr"/>
+      <c r="B118" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>cons_energ_comercial</t>
+        </is>
+      </c>
+      <c r="D118" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E118" t="n">
+        <v>-0.0003852043393453019</v>
+      </c>
+      <c r="F118" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr"/>
+      <c r="B119" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>cons_energ_industrial</t>
+        </is>
+      </c>
+      <c r="D119" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E119" t="n">
+        <v>3.402203874882571e-07</v>
+      </c>
+      <c r="F119" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr"/>
+      <c r="B120" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>cons_energ_outros</t>
+        </is>
+      </c>
+      <c r="D120" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E120" t="n">
+        <v>-0.0003852043393453016</v>
+      </c>
+      <c r="F120" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr"/>
+      <c r="B121" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>cons_energ_residencial</t>
+        </is>
+      </c>
+      <c r="D121" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E121" t="n">
+        <v>-0.0001736778242346749</v>
+      </c>
+      <c r="F121" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr"/>
+      <c r="B122" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>prod_aco_bruto</t>
+        </is>
+      </c>
+      <c r="D122" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E122" t="n">
+        <v>-1.785197105101958e-05</v>
+      </c>
+      <c r="F122" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr"/>
+      <c r="B123" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>renda_disponivel_familias_restrita</t>
+        </is>
+      </c>
+      <c r="D123" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E123" t="n">
+        <v>-1.311898121428156e-08</v>
+      </c>
+      <c r="F123" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr"/>
+      <c r="B124" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>icc_fecomercio</t>
+        </is>
+      </c>
+      <c r="D124" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E124" t="n">
+        <v>3.635830999700665e-09</v>
+      </c>
+      <c r="F124" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr"/>
+      <c r="B125" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>icea_fecomercio</t>
+        </is>
+      </c>
+      <c r="D125" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E125" t="n">
+        <v>8.510282114675453e-09</v>
+      </c>
+      <c r="F125" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr"/>
+      <c r="B126" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>ief_fecomercio</t>
+        </is>
+      </c>
+      <c r="D126" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E126" t="n">
+        <v>4.090735054371079e-09</v>
+      </c>
+      <c r="F126" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr"/>
+      <c r="B127" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>igp10</t>
+        </is>
+      </c>
+      <c r="D127" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E127" t="n">
+        <v>4.435386895486166e-07</v>
+      </c>
+      <c r="F127" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr"/>
+      <c r="B128" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>igpm</t>
+        </is>
+      </c>
+      <c r="D128" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E128" t="n">
+        <v>-7.071864811785101e-06</v>
+      </c>
+      <c r="F128" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr"/>
+      <c r="B129" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>ipam</t>
+        </is>
+      </c>
+      <c r="D129" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E129" t="n">
+        <v>-3.459132404131126e-06</v>
+      </c>
+      <c r="F129" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr"/>
+      <c r="B130" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>ipc_fipe</t>
+        </is>
+      </c>
+      <c r="D130" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E130" t="n">
+        <v>2.181765808836199e-08</v>
+      </c>
+      <c r="F130" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr"/>
+      <c r="B131" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>ipca15</t>
+        </is>
+      </c>
+      <c r="D131" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E131" t="n">
+        <v>-6.035526167716267e-08</v>
+      </c>
+      <c r="F131" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr"/>
+      <c r="B132" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>caged_estoque</t>
+        </is>
+      </c>
+      <c r="D132" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E132" t="n">
+        <v>6.454688358924292e-08</v>
+      </c>
+      <c r="F132" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr"/>
+      <c r="B133" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>cons_energ_comercial</t>
+        </is>
+      </c>
+      <c r="D133" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.0001217623874218309</v>
+      </c>
+      <c r="F133" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr"/>
+      <c r="B134" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>cons_energ_industrial</t>
+        </is>
+      </c>
+      <c r="D134" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E134" t="n">
+        <v>-5.454581278599834e-05</v>
+      </c>
+      <c r="F134" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr"/>
+      <c r="B135" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>cons_energ_outros</t>
+        </is>
+      </c>
+      <c r="D135" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.0001217623874218311</v>
+      </c>
+      <c r="F135" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr"/>
+      <c r="B136" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>cons_energ_residencial</t>
+        </is>
+      </c>
+      <c r="D136" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E136" t="n">
+        <v>-7.512617657336721e-05</v>
+      </c>
+      <c r="F136" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr"/>
+      <c r="B137" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>prod_aco_bruto</t>
+        </is>
+      </c>
+      <c r="D137" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E137" t="n">
+        <v>9.084642547969636e-06</v>
+      </c>
+      <c r="F137" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr"/>
+      <c r="B138" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>renda_disponivel_familias_restrita</t>
+        </is>
+      </c>
+      <c r="D138" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E138" t="n">
+        <v>1.529734021132683e-08</v>
+      </c>
+      <c r="F138" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr"/>
+      <c r="B139" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>icc_fecomercio</t>
+        </is>
+      </c>
+      <c r="D139" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E139" t="n">
+        <v>8.160811632611545e-09</v>
+      </c>
+      <c r="F139" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr"/>
+      <c r="B140" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>icea_fecomercio</t>
+        </is>
+      </c>
+      <c r="D140" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E140" t="n">
+        <v>7.428731567463906e-09</v>
+      </c>
+      <c r="F140" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr"/>
+      <c r="B141" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>ief_fecomercio</t>
+        </is>
+      </c>
+      <c r="D141" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E141" t="n">
+        <v>8.210321877796036e-08</v>
+      </c>
+      <c r="F141" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr"/>
+      <c r="B142" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>igp10</t>
+        </is>
+      </c>
+      <c r="D142" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E142" t="n">
+        <v>4.041524162254295e-07</v>
+      </c>
+      <c r="F142" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr"/>
+      <c r="B143" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>igpm</t>
+        </is>
+      </c>
+      <c r="D143" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E143" t="n">
+        <v>-2.271869222413808e-05</v>
+      </c>
+      <c r="F143" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr"/>
+      <c r="B144" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>ipam</t>
+        </is>
+      </c>
+      <c r="D144" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E144" t="n">
+        <v>-1.470564365216666e-05</v>
+      </c>
+      <c r="F144" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr"/>
+      <c r="B145" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>ipc_fipe</t>
+        </is>
+      </c>
+      <c r="D145" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E145" t="n">
+        <v>-6.232461580576883e-07</v>
+      </c>
+      <c r="F145" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr"/>
+      <c r="B146" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>ipca15</t>
+        </is>
+      </c>
+      <c r="D146" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E146" t="n">
+        <v>-1.770161817267546e-06</v>
+      </c>
+      <c r="F146" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr"/>
+      <c r="B147" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>caged_estoque</t>
+        </is>
+      </c>
+      <c r="D147" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E147" t="n">
+        <v>-2.733492452538744e-07</v>
+      </c>
+      <c r="F147" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr"/>
+      <c r="B148" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>cons_energ_comercial</t>
+        </is>
+      </c>
+      <c r="D148" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E148" t="n">
+        <v>-0.0004789415905811423</v>
+      </c>
+      <c r="F148" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr"/>
+      <c r="B149" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>cons_energ_industrial</t>
+        </is>
+      </c>
+      <c r="D149" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E149" t="n">
+        <v>0.0001064032621303446</v>
+      </c>
+      <c r="F149" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr"/>
+      <c r="B150" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>cons_energ_outros</t>
+        </is>
+      </c>
+      <c r="D150" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E150" t="n">
+        <v>-0.0004789415905811444</v>
+      </c>
+      <c r="F150" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr"/>
+      <c r="B151" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>cons_energ_residencial</t>
+        </is>
+      </c>
+      <c r="D151" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E151" t="n">
+        <v>0.0007743811781957759</v>
+      </c>
+      <c r="F151" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr"/>
+      <c r="B152" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>prod_aco_bruto</t>
+        </is>
+      </c>
+      <c r="D152" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E152" t="n">
+        <v>-1.682588362506308e-05</v>
+      </c>
+      <c r="F152" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr"/>
+      <c r="B153" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>renda_disponivel_familias_restrita</t>
+        </is>
+      </c>
+      <c r="D153" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E153" t="n">
+        <v>-3.580301966179141e-08</v>
+      </c>
+      <c r="F153" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr"/>
+      <c r="B154" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>icc_fecomercio</t>
+        </is>
+      </c>
+      <c r="D154" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E154" t="n">
+        <v>-9.20140600365944e-09</v>
+      </c>
+      <c r="F154" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr"/>
+      <c r="B155" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>icea_fecomercio</t>
+        </is>
+      </c>
+      <c r="D155" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E155" t="n">
+        <v>-9.226561675696588e-09</v>
+      </c>
+      <c r="F155" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr"/>
+      <c r="B156" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>ief_fecomercio</t>
+        </is>
+      </c>
+      <c r="D156" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E156" t="n">
+        <v>9.631357238071531e-08</v>
+      </c>
+      <c r="F156" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr"/>
+      <c r="B157" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>igp10</t>
+        </is>
+      </c>
+      <c r="D157" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E157" t="n">
+        <v>-1.543989848501457e-07</v>
+      </c>
+      <c r="F157" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr"/>
+      <c r="B158" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>igpm</t>
+        </is>
+      </c>
+      <c r="D158" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E158" t="n">
+        <v>-8.781124175168338e-06</v>
+      </c>
+      <c r="F158" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr"/>
+      <c r="B159" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>ipam</t>
+        </is>
+      </c>
+      <c r="D159" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E159" t="n">
+        <v>-9.814531070032751e-06</v>
+      </c>
+      <c r="F159" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr"/>
+      <c r="B160" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>ipc_fipe</t>
+        </is>
+      </c>
+      <c r="D160" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E160" t="n">
+        <v>6.024820126476282e-08</v>
+      </c>
+      <c r="F160" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr"/>
+      <c r="B161" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>ipca15</t>
+        </is>
+      </c>
+      <c r="D161" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E161" t="n">
+        <v>4.2916114457559e-07</v>
+      </c>
+      <c r="F161" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr"/>
+      <c r="B162" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>caged_estoque</t>
+        </is>
+      </c>
+      <c r="D162" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E162" t="n">
+        <v>1.000532561827845e-06</v>
+      </c>
+      <c r="F162" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr"/>
+      <c r="B163" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>cons_energ_comercial</t>
+        </is>
+      </c>
+      <c r="D163" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E163" t="n">
+        <v>0.0004636041089695896</v>
+      </c>
+      <c r="F163" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr"/>
+      <c r="B164" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>cons_energ_industrial</t>
+        </is>
+      </c>
+      <c r="D164" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E164" t="n">
+        <v>-4.283730818817201e-05</v>
+      </c>
+      <c r="F164" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr"/>
+      <c r="B165" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>cons_energ_outros</t>
+        </is>
+      </c>
+      <c r="D165" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E165" t="n">
+        <v>0.0004636041089695888</v>
+      </c>
+      <c r="F165" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr"/>
+      <c r="B166" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>cons_energ_residencial</t>
+        </is>
+      </c>
+      <c r="D166" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E166" t="n">
+        <v>0.0005439855860983304</v>
+      </c>
+      <c r="F166" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr"/>
+      <c r="B167" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>prod_aco_bruto</t>
+        </is>
+      </c>
+      <c r="D167" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E167" t="n">
+        <v>-3.418456075613271e-05</v>
+      </c>
+      <c r="F167" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr"/>
+      <c r="B168" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>renda_disponivel_familias_restrita</t>
+        </is>
+      </c>
+      <c r="D168" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E168" t="n">
+        <v>5.547097622644052e-08</v>
+      </c>
+      <c r="F168" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr"/>
+      <c r="B169" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>icc_fecomercio</t>
+        </is>
+      </c>
+      <c r="D169" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E169" t="n">
+        <v>-2.450518705980281e-08</v>
+      </c>
+      <c r="F169" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr"/>
+      <c r="B170" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>icea_fecomercio</t>
+        </is>
+      </c>
+      <c r="D170" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E170" t="n">
+        <v>-2.388477897297732e-08</v>
+      </c>
+      <c r="F170" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr"/>
+      <c r="B171" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>ief_fecomercio</t>
+        </is>
+      </c>
+      <c r="D171" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E171" t="n">
+        <v>3.989662059980975e-07</v>
+      </c>
+      <c r="F171" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr"/>
+      <c r="B172" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>igp10</t>
+        </is>
+      </c>
+      <c r="D172" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E172" t="n">
+        <v>1.847484602009339e-06</v>
+      </c>
+      <c r="F172" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr"/>
+      <c r="B173" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>igpm</t>
+        </is>
+      </c>
+      <c r="D173" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E173" t="n">
+        <v>4.009444979471029e-05</v>
+      </c>
+      <c r="F173" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr"/>
+      <c r="B174" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>ipam</t>
+        </is>
+      </c>
+      <c r="D174" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E174" t="n">
+        <v>6.430942623294371e-06</v>
+      </c>
+      <c r="F174" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr"/>
+      <c r="B175" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>ipc_fipe</t>
+        </is>
+      </c>
+      <c r="D175" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E175" t="n">
+        <v>5.667118189123249e-07</v>
+      </c>
+      <c r="F175" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr"/>
+      <c r="B176" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>ipca15</t>
+        </is>
+      </c>
+      <c r="D176" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E176" t="n">
+        <v>6.729892355019294e-06</v>
+      </c>
+      <c r="F176" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr"/>
+      <c r="B177" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>caged_estoque</t>
+        </is>
+      </c>
+      <c r="D177" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E177" t="n">
+        <v>-8.341286768394392e-07</v>
+      </c>
+      <c r="F177" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr"/>
+      <c r="B178" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>cons_energ_comercial</t>
+        </is>
+      </c>
+      <c r="D178" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E178" t="n">
+        <v>-0.004933551658315339</v>
+      </c>
+      <c r="F178" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr"/>
+      <c r="B179" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>cons_energ_industrial</t>
+        </is>
+      </c>
+      <c r="D179" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E179" t="n">
+        <v>0.0002603127162542728</v>
+      </c>
+      <c r="F179" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr"/>
+      <c r="B180" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>cons_energ_outros</t>
+        </is>
+      </c>
+      <c r="D180" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E180" t="n">
+        <v>-0.004933551658315347</v>
+      </c>
+      <c r="F180" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr"/>
+      <c r="B181" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>cons_energ_residencial</t>
+        </is>
+      </c>
+      <c r="D181" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E181" t="n">
+        <v>-0.004443520087774804</v>
+      </c>
+      <c r="F181" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr"/>
+      <c r="B182" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>prod_aco_bruto</t>
+        </is>
+      </c>
+      <c r="D182" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E182" t="n">
+        <v>0.0001431785904452659</v>
+      </c>
+      <c r="F182" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr"/>
+      <c r="B183" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>renda_disponivel_familias_restrita</t>
+        </is>
+      </c>
+      <c r="D183" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E183" t="n">
+        <v>1.38111228784209e-06</v>
+      </c>
+      <c r="F183" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr"/>
+      <c r="B184" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>icc_fecomercio</t>
+        </is>
+      </c>
+      <c r="D184" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E184" t="n">
+        <v>-1.20521810534903e-07</v>
+      </c>
+      <c r="F184" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr"/>
+      <c r="B185" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>icea_fecomercio</t>
+        </is>
+      </c>
+      <c r="D185" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E185" t="n">
+        <v>-1.017198814832297e-07</v>
+      </c>
+      <c r="F185" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr"/>
+      <c r="B186" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>ief_fecomercio</t>
+        </is>
+      </c>
+      <c r="D186" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E186" t="n">
+        <v>4.021042701563232e-07</v>
+      </c>
+      <c r="F186" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr"/>
+      <c r="B187" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>igp10</t>
+        </is>
+      </c>
+      <c r="D187" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E187" t="n">
+        <v>1.341446979767632e-05</v>
+      </c>
+      <c r="F187" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr"/>
+      <c r="B188" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>igpm</t>
+        </is>
+      </c>
+      <c r="D188" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E188" t="n">
+        <v>0.000302991330253799</v>
+      </c>
+      <c r="F188" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr"/>
+      <c r="B189" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>ipam</t>
+        </is>
+      </c>
+      <c r="D189" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E189" t="n">
+        <v>0.0001517097914155054</v>
+      </c>
+      <c r="F189" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr"/>
+      <c r="B190" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>ipc_fipe</t>
+        </is>
+      </c>
+      <c r="D190" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E190" t="n">
+        <v>7.255329768393732e-06</v>
+      </c>
+      <c r="F190" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr"/>
+      <c r="B191" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>ipca15</t>
+        </is>
+      </c>
+      <c r="D191" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E191" t="n">
+        <v>1.433350741726462e-05</v>
+      </c>
+      <c r="F191" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr"/>
+      <c r="B192" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>caged_estoque</t>
+        </is>
+      </c>
+      <c r="D192" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E192" t="n">
+        <v>-2.383342393125458e-05</v>
+      </c>
+      <c r="F192" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr"/>
+      <c r="B193" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>cons_energ_comercial</t>
+        </is>
+      </c>
+      <c r="D193" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E193" t="n">
+        <v>-0.003965035796577845</v>
+      </c>
+      <c r="F193" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr"/>
+      <c r="B194" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>cons_energ_industrial</t>
+        </is>
+      </c>
+      <c r="D194" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E194" t="n">
+        <v>-0.0005235437784814356</v>
+      </c>
+      <c r="F194" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr"/>
+      <c r="B195" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>cons_energ_outros</t>
+        </is>
+      </c>
+      <c r="D195" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E195" t="n">
+        <v>-0.003965035796577863</v>
+      </c>
+      <c r="F195" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr"/>
+      <c r="B196" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>cons_energ_residencial</t>
+        </is>
+      </c>
+      <c r="D196" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E196" t="n">
+        <v>0.001471804138917308</v>
+      </c>
+      <c r="F196" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr"/>
+      <c r="B197" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>prod_aco_bruto</t>
+        </is>
+      </c>
+      <c r="D197" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E197" t="n">
+        <v>8.224029260279609e-05</v>
+      </c>
+      <c r="F197" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr"/>
+      <c r="B198" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>renda_disponivel_familias_restrita</t>
+        </is>
+      </c>
+      <c r="D198" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E198" t="n">
+        <v>1.39733771184987e-05</v>
+      </c>
+      <c r="F198" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr"/>
+      <c r="B199" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>icc_fecomercio</t>
+        </is>
+      </c>
+      <c r="D199" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E199" t="n">
+        <v>-2.152553841004061e-07</v>
+      </c>
+      <c r="F199" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr"/>
+      <c r="B200" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>icea_fecomercio</t>
+        </is>
+      </c>
+      <c r="D200" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E200" t="n">
+        <v>-7.826495284182403e-08</v>
+      </c>
+      <c r="F200" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr"/>
+      <c r="B201" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>ief_fecomercio</t>
+        </is>
+      </c>
+      <c r="D201" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E201" t="n">
+        <v>-3.513106844828495e-06</v>
+      </c>
+      <c r="F201" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr"/>
+      <c r="B202" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>igp10</t>
+        </is>
+      </c>
+      <c r="D202" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E202" t="n">
+        <v>-3.01002003303516e-05</v>
+      </c>
+      <c r="F202" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr"/>
+      <c r="B203" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>igpm</t>
+        </is>
+      </c>
+      <c r="D203" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E203" t="n">
+        <v>0.0001172630327439481</v>
+      </c>
+      <c r="F203" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr"/>
+      <c r="B204" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>ipam</t>
+        </is>
+      </c>
+      <c r="D204" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E204" t="n">
+        <v>4.267321087474355e-05</v>
+      </c>
+      <c r="F204" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr"/>
+      <c r="B205" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>ipc_fipe</t>
+        </is>
+      </c>
+      <c r="D205" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E205" t="n">
+        <v>2.798834584660181e-05</v>
+      </c>
+      <c r="F205" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr"/>
+      <c r="B206" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>ipca15</t>
+        </is>
+      </c>
+      <c r="D206" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E206" t="n">
+        <v>-9.065958002846467e-05</v>
+      </c>
+      <c r="F206" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr"/>
+      <c r="B207" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>caged_estoque</t>
+        </is>
+      </c>
+      <c r="D207" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E207" t="n">
+        <v>2.731136613926534e-05</v>
+      </c>
+      <c r="F207" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr"/>
+      <c r="B208" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>cons_energ_comercial</t>
+        </is>
+      </c>
+      <c r="D208" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E208" t="n">
+        <v>0.04274944814552613</v>
+      </c>
+      <c r="F208" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr"/>
+      <c r="B209" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>cons_energ_industrial</t>
+        </is>
+      </c>
+      <c r="D209" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E209" t="n">
+        <v>-0.03811904081061233</v>
+      </c>
+      <c r="F209" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr"/>
+      <c r="B210" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>cons_energ_outros</t>
+        </is>
+      </c>
+      <c r="D210" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E210" t="n">
+        <v>0.0427494481455262</v>
+      </c>
+      <c r="F210" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr"/>
+      <c r="B211" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>cons_energ_residencial</t>
+        </is>
+      </c>
+      <c r="D211" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E211" t="n">
+        <v>0.01582848834874863</v>
+      </c>
+      <c r="F211" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr"/>
+      <c r="B212" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>prod_aco_bruto</t>
+        </is>
+      </c>
+      <c r="D212" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E212" t="n">
+        <v>0.008523675801718792</v>
+      </c>
+      <c r="F212" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr"/>
+      <c r="B213" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>renda_disponivel_familias_restrita</t>
+        </is>
+      </c>
+      <c r="D213" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E213" t="n">
+        <v>2.82275538099275e-05</v>
+      </c>
+      <c r="F213" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr"/>
+      <c r="B214" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>icc_fecomercio</t>
+        </is>
+      </c>
+      <c r="D214" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E214" t="n">
+        <v>-6.553846092422106e-08</v>
+      </c>
+      <c r="F214" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr"/>
+      <c r="B215" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>icea_fecomercio</t>
+        </is>
+      </c>
+      <c r="D215" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E215" t="n">
+        <v>-1.007636761579694e-07</v>
+      </c>
+      <c r="F215" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr"/>
+      <c r="B216" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>ief_fecomercio</t>
+        </is>
+      </c>
+      <c r="D216" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E216" t="n">
+        <v>1.564269568082943e-06</v>
+      </c>
+      <c r="F216" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr"/>
+      <c r="B217" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>igp10</t>
+        </is>
+      </c>
+      <c r="D217" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E217" t="n">
+        <v>3.648576745980332e-05</v>
+      </c>
+      <c r="F217" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr"/>
+      <c r="B218" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>igpm</t>
+        </is>
+      </c>
+      <c r="D218" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E218" t="n">
+        <v>0.000604045724779229</v>
+      </c>
+      <c r="F218" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr"/>
+      <c r="B219" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>ipam</t>
+        </is>
+      </c>
+      <c r="D219" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E219" t="n">
+        <v>0.0003300865214831774</v>
+      </c>
+      <c r="F219" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr"/>
+      <c r="B220" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>ipc_fipe</t>
+        </is>
+      </c>
+      <c r="D220" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E220" t="n">
+        <v>1.15918707551814e-05</v>
+      </c>
+      <c r="F220" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr"/>
+      <c r="B221" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>ipca15</t>
+        </is>
+      </c>
+      <c r="D221" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E221" t="n">
+        <v>2.613527385224568e-05</v>
+      </c>
+      <c r="F221" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr"/>
+      <c r="B222" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>fgv_nuci</t>
+        </is>
+      </c>
+      <c r="D222" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E222" t="n">
+        <v>0.01534056005552086</v>
+      </c>
+      <c r="F222" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr"/>
+      <c r="B223" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>icc_fecomercio</t>
+        </is>
+      </c>
+      <c r="D223" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E223" t="n">
+        <v>1.183735791906435e-06</v>
+      </c>
+      <c r="F223" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr"/>
+      <c r="B224" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>icea_fecomercio</t>
+        </is>
+      </c>
+      <c r="D224" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E224" t="n">
+        <v>-3.516914797549018e-08</v>
+      </c>
+      <c r="F224" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr"/>
+      <c r="B225" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>ics_fgv</t>
+        </is>
+      </c>
+      <c r="D225" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E225" t="n">
+        <v>-0.0004476670780060573</v>
+      </c>
+      <c r="F225" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr"/>
+      <c r="B226" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>ief_fecomercio</t>
+        </is>
+      </c>
+      <c r="D226" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E226" t="n">
+        <v>6.649212800174457e-05</v>
+      </c>
+      <c r="F226" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr"/>
+      <c r="B227" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>ies_fgv</t>
+        </is>
+      </c>
+      <c r="D227" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E227" t="n">
+        <v>0.0006623886714659137</v>
+      </c>
+      <c r="F227" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr"/>
+      <c r="B228" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>igp10</t>
+        </is>
+      </c>
+      <c r="D228" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E228" t="n">
+        <v>0.001645211385892881</v>
+      </c>
+      <c r="F228" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr"/>
+      <c r="B229" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>igpm</t>
+        </is>
+      </c>
+      <c r="D229" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E229" t="n">
+        <v>0.0006652694196461632</v>
+      </c>
+      <c r="F229" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr"/>
+      <c r="B230" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>ipam</t>
+        </is>
+      </c>
+      <c r="D230" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E230" t="n">
+        <v>2.042473243647938e-05</v>
+      </c>
+      <c r="F230" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr"/>
+      <c r="B231" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>ipc_fipe</t>
+        </is>
+      </c>
+      <c r="D231" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E231" t="n">
+        <v>0.0005317662440358724</v>
+      </c>
+      <c r="F231" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr"/>
+      <c r="B232" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>ipca15</t>
+        </is>
+      </c>
+      <c r="D232" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E232" t="n">
+        <v>0.000713689525326454</v>
+      </c>
+      <c r="F232" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr"/>
+      <c r="B233" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>isas_fgv</t>
+        </is>
+      </c>
+      <c r="D233" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E233" t="n">
+        <v>-0.0001520637933125445</v>
+      </c>
+      <c r="F233" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr"/>
+      <c r="B234" s="1" t="n">
+        <v>45778</v>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>all prior revisions</t>
+        </is>
+      </c>
+      <c r="D234" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E234" t="n">
+        <v>-6.767678611338938e-05</v>
+      </c>
+      <c r="F234" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr"/>
+      <c r="B235" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>caged_estoque</t>
+        </is>
+      </c>
+      <c r="D235" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E235" t="n">
+        <v>-1.806986067570489e-08</v>
+      </c>
+      <c r="F235" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr"/>
+      <c r="B236" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>cons_energ_comercial</t>
+        </is>
+      </c>
+      <c r="D236" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E236" t="n">
+        <v>-4.372513299396422e-05</v>
+      </c>
+      <c r="F236" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr"/>
+      <c r="B237" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>cons_energ_industrial</t>
+        </is>
+      </c>
+      <c r="D237" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E237" t="n">
+        <v>-3.995736897696023e-06</v>
+      </c>
+      <c r="F237" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr"/>
+      <c r="B238" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>cons_energ_outros</t>
+        </is>
+      </c>
+      <c r="D238" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E238" t="n">
+        <v>-4.37251329939641e-05</v>
+      </c>
+      <c r="F238" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr"/>
+      <c r="B239" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>cons_energ_residencial</t>
+        </is>
+      </c>
+      <c r="D239" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E239" t="n">
+        <v>-4.070427536664081e-05</v>
+      </c>
+      <c r="F239" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr"/>
+      <c r="B240" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>prod_aco_bruto</t>
+        </is>
+      </c>
+      <c r="D240" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E240" t="n">
+        <v>-2.186857191301488e-05</v>
+      </c>
+      <c r="F240" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr"/>
+      <c r="B241" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>renda_disponivel_familias_restrita</t>
+        </is>
+      </c>
+      <c r="D241" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E241" t="n">
+        <v>-3.823952645825379e-08</v>
+      </c>
+      <c r="F241" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr"/>
+      <c r="B242" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>icc_fecomercio</t>
+        </is>
+      </c>
+      <c r="D242" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E242" t="n">
+        <v>-6.30547437522082e-09</v>
+      </c>
+      <c r="F242" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr"/>
+      <c r="B243" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>icea_fecomercio</t>
+        </is>
+      </c>
+      <c r="D243" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E243" t="n">
+        <v>7.52483329444972e-09</v>
+      </c>
+      <c r="F243" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr"/>
+      <c r="B244" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>ief_fecomercio</t>
+        </is>
+      </c>
+      <c r="D244" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E244" t="n">
+        <v>-5.882182477342406e-08</v>
+      </c>
+      <c r="F244" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr"/>
+      <c r="B245" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>igp10</t>
+        </is>
+      </c>
+      <c r="D245" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E245" t="n">
+        <v>-5.807335714906513e-07</v>
+      </c>
+      <c r="F245" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr"/>
+      <c r="B246" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>igpm</t>
+        </is>
+      </c>
+      <c r="D246" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E246" t="n">
+        <v>1.455445339797876e-05</v>
+      </c>
+      <c r="F246" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr"/>
+      <c r="B247" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>ipam</t>
+        </is>
+      </c>
+      <c r="D247" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E247" t="n">
+        <v>8.653370563502802e-06</v>
+      </c>
+      <c r="F247" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr"/>
+      <c r="B248" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>ipc_fipe</t>
+        </is>
+      </c>
+      <c r="D248" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E248" t="n">
+        <v>5.848757032087921e-07</v>
+      </c>
+      <c r="F248" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr"/>
+      <c r="B249" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>ipca15</t>
+        </is>
+      </c>
+      <c r="D249" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E249" t="n">
+        <v>4.568853191682978e-07</v>
+      </c>
+      <c r="F249" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr"/>
+      <c r="B250" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>caged_estoque</t>
+        </is>
+      </c>
+      <c r="D250" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E250" t="n">
+        <v>1.667329514637693e-09</v>
+      </c>
+      <c r="F250" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr"/>
+      <c r="B251" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>cons_energ_comercial</t>
+        </is>
+      </c>
+      <c r="D251" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E251" t="n">
+        <v>-3.361966208546185e-06</v>
+      </c>
+      <c r="F251" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr"/>
+      <c r="B252" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>cons_energ_industrial</t>
+        </is>
+      </c>
+      <c r="D252" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E252" t="n">
+        <v>-5.643996471271497e-06</v>
+      </c>
+      <c r="F252" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr"/>
+      <c r="B253" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>cons_energ_outros</t>
+        </is>
+      </c>
+      <c r="D253" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E253" t="n">
+        <v>-3.361966208546186e-06</v>
+      </c>
+      <c r="F253" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr"/>
+      <c r="B254" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>cons_energ_residencial</t>
+        </is>
+      </c>
+      <c r="D254" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E254" t="n">
+        <v>9.34096889546022e-06</v>
+      </c>
+      <c r="F254" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr"/>
+      <c r="B255" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>prod_aco_bruto</t>
+        </is>
+      </c>
+      <c r="D255" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E255" t="n">
+        <v>4.382925290427956e-06</v>
+      </c>
+      <c r="F255" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr"/>
+      <c r="B256" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>renda_disponivel_familias_restrita</t>
+        </is>
+      </c>
+      <c r="D256" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E256" t="n">
+        <v>-1.573882570918851e-08</v>
+      </c>
+      <c r="F256" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr"/>
+      <c r="B257" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>icc_fecomercio</t>
+        </is>
+      </c>
+      <c r="D257" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E257" t="n">
+        <v>-2.891249282582984e-10</v>
+      </c>
+      <c r="F257" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr"/>
+      <c r="B258" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>icea_fecomercio</t>
+        </is>
+      </c>
+      <c r="D258" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E258" t="n">
+        <v>9.740551367190854e-10</v>
+      </c>
+      <c r="F258" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr"/>
+      <c r="B259" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>ief_fecomercio</t>
+        </is>
+      </c>
+      <c r="D259" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E259" t="n">
+        <v>1.160404978859518e-10</v>
+      </c>
+      <c r="F259" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr"/>
+      <c r="B260" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>igp10</t>
+        </is>
+      </c>
+      <c r="D260" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E260" t="n">
+        <v>3.893490751174692e-08</v>
+      </c>
+      <c r="F260" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr"/>
+      <c r="B261" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>igpm</t>
+        </is>
+      </c>
+      <c r="D261" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E261" t="n">
+        <v>-7.485138977200329e-08</v>
+      </c>
+      <c r="F261" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr"/>
+      <c r="B262" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>ipam</t>
+        </is>
+      </c>
+      <c r="D262" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E262" t="n">
+        <v>-2.764936998349154e-08</v>
+      </c>
+      <c r="F262" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr"/>
+      <c r="B263" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>ipc_fipe</t>
+        </is>
+      </c>
+      <c r="D263" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E263" t="n">
+        <v>7.483870970806079e-10</v>
+      </c>
+      <c r="F263" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr"/>
+      <c r="B264" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>ipca15</t>
+        </is>
+      </c>
+      <c r="D264" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E264" t="n">
+        <v>4.311774695690316e-10</v>
+      </c>
+      <c r="F264" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr"/>
+      <c r="B265" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>caged_estoque</t>
+        </is>
+      </c>
+      <c r="D265" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E265" t="n">
+        <v>9.023444380867132e-09</v>
+      </c>
+      <c r="F265" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr"/>
+      <c r="B266" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>cons_energ_comercial</t>
+        </is>
+      </c>
+      <c r="D266" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E266" t="n">
+        <v>-1.869098113107525e-07</v>
+      </c>
+      <c r="F266" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr"/>
+      <c r="B267" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>cons_energ_industrial</t>
+        </is>
+      </c>
+      <c r="D267" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E267" t="n">
+        <v>1.841783896636858e-06</v>
+      </c>
+      <c r="F267" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr"/>
+      <c r="B268" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>cons_energ_outros</t>
+        </is>
+      </c>
+      <c r="D268" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E268" t="n">
+        <v>-1.869098113107501e-07</v>
+      </c>
+      <c r="F268" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr"/>
+      <c r="B269" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>cons_energ_residencial</t>
+        </is>
+      </c>
+      <c r="D269" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E269" t="n">
+        <v>-4.52347486123709e-07</v>
+      </c>
+      <c r="F269" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr"/>
+      <c r="B270" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>prod_aco_bruto</t>
+        </is>
+      </c>
+      <c r="D270" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E270" t="n">
+        <v>2.597143111361442e-06</v>
+      </c>
+      <c r="F270" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr"/>
+      <c r="B271" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>renda_disponivel_familias_restrita</t>
+        </is>
+      </c>
+      <c r="D271" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E271" t="n">
+        <v>-4.990200353427761e-10</v>
+      </c>
+      <c r="F271" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr"/>
+      <c r="B272" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>icc_fecomercio</t>
+        </is>
+      </c>
+      <c r="D272" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E272" t="n">
+        <v>7.256675642235031e-09</v>
+      </c>
+      <c r="F272" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr"/>
+      <c r="B273" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>icea_fecomercio</t>
+        </is>
+      </c>
+      <c r="D273" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E273" t="n">
+        <v>8.958209610934607e-09</v>
+      </c>
+      <c r="F273" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr"/>
+      <c r="B274" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>ief_fecomercio</t>
+        </is>
+      </c>
+      <c r="D274" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E274" t="n">
+        <v>-1.801779655778714e-08</v>
+      </c>
+      <c r="F274" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr"/>
+      <c r="B275" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>igp10</t>
+        </is>
+      </c>
+      <c r="D275" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E275" t="n">
+        <v>-3.648752101648047e-07</v>
+      </c>
+      <c r="F275" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr"/>
+      <c r="B276" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>igpm</t>
+        </is>
+      </c>
+      <c r="D276" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E276" t="n">
+        <v>6.016079072599208e-07</v>
+      </c>
+      <c r="F276" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr"/>
+      <c r="B277" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>ipam</t>
+        </is>
+      </c>
+      <c r="D277" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E277" t="n">
+        <v>1.641097955604313e-07</v>
+      </c>
+      <c r="F277" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr"/>
+      <c r="B278" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>ipc_fipe</t>
+        </is>
+      </c>
+      <c r="D278" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E278" t="n">
+        <v>-7.008594310268701e-09</v>
+      </c>
+      <c r="F278" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr"/>
+      <c r="B279" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>ipca15</t>
+        </is>
+      </c>
+      <c r="D279" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E279" t="n">
+        <v>-2.753458258816785e-08</v>
+      </c>
+      <c r="F279" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr"/>
+      <c r="B280" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>caged_estoque</t>
+        </is>
+      </c>
+      <c r="D280" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E280" t="n">
+        <v>-8.603078536859787e-08</v>
+      </c>
+      <c r="F280" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr"/>
+      <c r="B281" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>cons_energ_comercial</t>
+        </is>
+      </c>
+      <c r="D281" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E281" t="n">
+        <v>1.784324298254596e-05</v>
+      </c>
+      <c r="F281" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr"/>
+      <c r="B282" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>cons_energ_industrial</t>
+        </is>
+      </c>
+      <c r="D282" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E282" t="n">
+        <v>6.930649375914306e-06</v>
+      </c>
+      <c r="F282" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr"/>
+      <c r="B283" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>cons_energ_outros</t>
+        </is>
+      </c>
+      <c r="D283" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E283" t="n">
+        <v>1.784324298254587e-05</v>
+      </c>
+      <c r="F283" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr"/>
+      <c r="B284" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>cons_energ_residencial</t>
+        </is>
+      </c>
+      <c r="D284" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E284" t="n">
+        <v>4.91731393678267e-06</v>
+      </c>
+      <c r="F284" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr"/>
+      <c r="B285" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>prod_aco_bruto</t>
+        </is>
+      </c>
+      <c r="D285" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E285" t="n">
+        <v>-3.588430531904211e-07</v>
+      </c>
+      <c r="F285" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr"/>
+      <c r="B286" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>renda_disponivel_familias_restrita</t>
+        </is>
+      </c>
+      <c r="D286" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E286" t="n">
+        <v>2.786549980201554e-08</v>
+      </c>
+      <c r="F286" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr"/>
+      <c r="B287" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>icc_fecomercio</t>
+        </is>
+      </c>
+      <c r="D287" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E287" t="n">
+        <v>-1.258699079445072e-08</v>
+      </c>
+      <c r="F287" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr"/>
+      <c r="B288" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>icea_fecomercio</t>
+        </is>
+      </c>
+      <c r="D288" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E288" t="n">
+        <v>-9.961270104455088e-09</v>
+      </c>
+      <c r="F288" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr"/>
+      <c r="B289" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>ief_fecomercio</t>
+        </is>
+      </c>
+      <c r="D289" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E289" t="n">
+        <v>4.859610140082849e-08</v>
+      </c>
+      <c r="F289" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr"/>
+      <c r="B290" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>igp10</t>
+        </is>
+      </c>
+      <c r="D290" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E290" t="n">
+        <v>-1.012104829252881e-06</v>
+      </c>
+      <c r="F290" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr"/>
+      <c r="B291" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>igpm</t>
+        </is>
+      </c>
+      <c r="D291" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E291" t="n">
+        <v>1.683868052684164e-06</v>
+      </c>
+      <c r="F291" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr"/>
+      <c r="B292" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>ipam</t>
+        </is>
+      </c>
+      <c r="D292" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E292" t="n">
+        <v>7.647310319292462e-07</v>
+      </c>
+      <c r="F292" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr"/>
+      <c r="B293" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>ipc_fipe</t>
+        </is>
+      </c>
+      <c r="D293" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E293" t="n">
+        <v>-8.758837053625556e-08</v>
+      </c>
+      <c r="F293" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr"/>
+      <c r="B294" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>ipca15</t>
+        </is>
+      </c>
+      <c r="D294" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E294" t="n">
+        <v>-2.254663421035848e-07</v>
+      </c>
+      <c r="F294" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr"/>
+      <c r="B295" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>caged_estoque</t>
+        </is>
+      </c>
+      <c r="D295" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E295" t="n">
+        <v>-8.834701594580101e-09</v>
+      </c>
+      <c r="F295" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr"/>
+      <c r="B296" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>cons_energ_comercial</t>
+        </is>
+      </c>
+      <c r="D296" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E296" t="n">
+        <v>-0.0002747266515150265</v>
+      </c>
+      <c r="F296" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr"/>
+      <c r="B297" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>cons_energ_industrial</t>
+        </is>
+      </c>
+      <c r="D297" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E297" t="n">
+        <v>-3.370532417871826e-06</v>
+      </c>
+      <c r="F297" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr"/>
+      <c r="B298" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>cons_energ_outros</t>
+        </is>
+      </c>
+      <c r="D298" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E298" t="n">
+        <v>-0.0002747266515150266</v>
+      </c>
+      <c r="F298" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr"/>
+      <c r="B299" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>cons_energ_residencial</t>
+        </is>
+      </c>
+      <c r="D299" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E299" t="n">
+        <v>-0.0001889112218946398</v>
+      </c>
+      <c r="F299" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr"/>
+      <c r="B300" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>prod_aco_bruto</t>
+        </is>
+      </c>
+      <c r="D300" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E300" t="n">
+        <v>-1.385003169361316e-05</v>
+      </c>
+      <c r="F300" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr"/>
+      <c r="B301" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>renda_disponivel_familias_restrita</t>
+        </is>
+      </c>
+      <c r="D301" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E301" t="n">
+        <v>8.078995644911486e-09</v>
+      </c>
+      <c r="F301" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr"/>
+      <c r="B302" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>icc_fecomercio</t>
+        </is>
+      </c>
+      <c r="D302" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E302" t="n">
+        <v>2.390846927456127e-10</v>
+      </c>
+      <c r="F302" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr"/>
+      <c r="B303" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>icea_fecomercio</t>
+        </is>
+      </c>
+      <c r="D303" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E303" t="n">
+        <v>2.897590524081282e-10</v>
+      </c>
+      <c r="F303" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr"/>
+      <c r="B304" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>ief_fecomercio</t>
+        </is>
+      </c>
+      <c r="D304" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E304" t="n">
+        <v>1.222122747315816e-09</v>
+      </c>
+      <c r="F304" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr"/>
+      <c r="B305" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>igp10</t>
+        </is>
+      </c>
+      <c r="D305" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E305" t="n">
+        <v>-1.376527075547137e-07</v>
+      </c>
+      <c r="F305" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr"/>
+      <c r="B306" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>igpm</t>
+        </is>
+      </c>
+      <c r="D306" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E306" t="n">
+        <v>1.148773326066973e-07</v>
+      </c>
+      <c r="F306" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr"/>
+      <c r="B307" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>ipam</t>
+        </is>
+      </c>
+      <c r="D307" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E307" t="n">
+        <v>7.719528269623227e-08</v>
+      </c>
+      <c r="F307" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr"/>
+      <c r="B308" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>ipc_fipe</t>
+        </is>
+      </c>
+      <c r="D308" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E308" t="n">
+        <v>-1.417224368993234e-09</v>
+      </c>
+      <c r="F308" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr"/>
+      <c r="B309" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>ipca15</t>
+        </is>
+      </c>
+      <c r="D309" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E309" t="n">
+        <v>3.014780308534552e-10</v>
+      </c>
+      <c r="F309" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr"/>
+      <c r="B310" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>caged_estoque</t>
+        </is>
+      </c>
+      <c r="D310" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E310" t="n">
+        <v>-1.736982000887724e-10</v>
+      </c>
+      <c r="F310" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr"/>
+      <c r="B311" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>cons_energ_comercial</t>
+        </is>
+      </c>
+      <c r="D311" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E311" t="n">
+        <v>-0.0003722892399762872</v>
+      </c>
+      <c r="F311" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr"/>
+      <c r="B312" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>cons_energ_industrial</t>
+        </is>
+      </c>
+      <c r="D312" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E312" t="n">
+        <v>3.280519636641481e-07</v>
+      </c>
+      <c r="F312" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr"/>
+      <c r="B313" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>cons_energ_outros</t>
+        </is>
+      </c>
+      <c r="D313" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E313" t="n">
+        <v>-0.0003722892399762829</v>
+      </c>
+      <c r="F313" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr"/>
+      <c r="B314" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>cons_energ_residencial</t>
+        </is>
+      </c>
+      <c r="D314" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E314" t="n">
+        <v>-0.0001678284154961287</v>
+      </c>
+      <c r="F314" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr"/>
+      <c r="B315" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>prod_aco_bruto</t>
+        </is>
+      </c>
+      <c r="D315" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E315" t="n">
+        <v>-1.723039468133557e-05</v>
+      </c>
+      <c r="F315" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr"/>
+      <c r="B316" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>renda_disponivel_familias_restrita</t>
+        </is>
+      </c>
+      <c r="D316" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E316" t="n">
+        <v>-1.61601628626918e-08</v>
+      </c>
+      <c r="F316" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr"/>
+      <c r="B317" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>icc_fecomercio</t>
+        </is>
+      </c>
+      <c r="D317" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E317" t="n">
+        <v>3.823212647412811e-09</v>
+      </c>
+      <c r="F317" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr"/>
+      <c r="B318" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>icea_fecomercio</t>
+        </is>
+      </c>
+      <c r="D318" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E318" t="n">
+        <v>8.746832223569201e-09</v>
+      </c>
+      <c r="F318" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr"/>
+      <c r="B319" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>ief_fecomercio</t>
+        </is>
+      </c>
+      <c r="D319" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E319" t="n">
+        <v>3.269596598718983e-09</v>
+      </c>
+      <c r="F319" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr"/>
+      <c r="B320" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>igp10</t>
+        </is>
+      </c>
+      <c r="D320" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E320" t="n">
+        <v>5.025936831499769e-07</v>
+      </c>
+      <c r="F320" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr"/>
+      <c r="B321" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>igpm</t>
+        </is>
+      </c>
+      <c r="D321" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E321" t="n">
+        <v>-7.222800535877984e-06</v>
+      </c>
+      <c r="F321" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr"/>
+      <c r="B322" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>ipam</t>
+        </is>
+      </c>
+      <c r="D322" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E322" t="n">
+        <v>-3.807838724303162e-06</v>
+      </c>
+      <c r="F322" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr"/>
+      <c r="B323" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>ipc_fipe</t>
+        </is>
+      </c>
+      <c r="D323" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E323" t="n">
+        <v>-4.938348940754899e-08</v>
+      </c>
+      <c r="F323" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr"/>
+      <c r="B324" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>ipca15</t>
+        </is>
+      </c>
+      <c r="D324" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E324" t="n">
+        <v>-8.515229515192669e-08</v>
+      </c>
+      <c r="F324" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr"/>
+      <c r="B325" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>caged_estoque</t>
+        </is>
+      </c>
+      <c r="D325" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E325" t="n">
+        <v>6.423393567004242e-08</v>
+      </c>
+      <c r="F325" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr"/>
+      <c r="B326" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>cons_energ_comercial</t>
+        </is>
+      </c>
+      <c r="D326" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E326" t="n">
+        <v>0.0001219113915190124</v>
+      </c>
+      <c r="F326" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr"/>
+      <c r="B327" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>cons_energ_industrial</t>
+        </is>
+      </c>
+      <c r="D327" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E327" t="n">
+        <v>-5.48969560904824e-05</v>
+      </c>
+      <c r="F327" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr"/>
+      <c r="B328" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>cons_energ_outros</t>
+        </is>
+      </c>
+      <c r="D328" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E328" t="n">
+        <v>0.0001219113915190119</v>
+      </c>
+      <c r="F328" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr"/>
+      <c r="B329" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>cons_energ_residencial</t>
+        </is>
+      </c>
+      <c r="D329" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E329" t="n">
+        <v>-7.56103661157655e-05</v>
+      </c>
+      <c r="F329" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr"/>
+      <c r="B330" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>prod_aco_bruto</t>
+        </is>
+      </c>
+      <c r="D330" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E330" t="n">
+        <v>9.162044044983277e-06</v>
+      </c>
+      <c r="F330" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr"/>
+      <c r="B331" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>renda_disponivel_familias_restrita</t>
+        </is>
+      </c>
+      <c r="D331" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E331" t="n">
+        <v>1.562237362186938e-08</v>
+      </c>
+      <c r="F331" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr"/>
+      <c r="B332" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>icc_fecomercio</t>
+        </is>
+      </c>
+      <c r="D332" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E332" t="n">
+        <v>7.824301887351502e-09</v>
+      </c>
+      <c r="F332" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr"/>
+      <c r="B333" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>icea_fecomercio</t>
+        </is>
+      </c>
+      <c r="D333" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E333" t="n">
+        <v>7.03640638777097e-09</v>
+      </c>
+      <c r="F333" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr"/>
+      <c r="B334" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>ief_fecomercio</t>
+        </is>
+      </c>
+      <c r="D334" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E334" t="n">
+        <v>8.196372238976601e-08</v>
+      </c>
+      <c r="F334" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr"/>
+      <c r="B335" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>igp10</t>
+        </is>
+      </c>
+      <c r="D335" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E335" t="n">
+        <v>4.08836853886941e-07</v>
+      </c>
+      <c r="F335" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr"/>
+      <c r="B336" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>igpm</t>
+        </is>
+      </c>
+      <c r="D336" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E336" t="n">
+        <v>-2.158903761204297e-05</v>
+      </c>
+      <c r="F336" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr"/>
+      <c r="B337" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>ipam</t>
+        </is>
+      </c>
+      <c r="D337" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E337" t="n">
+        <v>-1.428330470205869e-05</v>
+      </c>
+      <c r="F337" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr"/>
+      <c r="B338" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>ipc_fipe</t>
+        </is>
+      </c>
+      <c r="D338" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E338" t="n">
+        <v>-6.200213679468061e-07</v>
+      </c>
+      <c r="F338" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr"/>
+      <c r="B339" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>ipca15</t>
+        </is>
+      </c>
+      <c r="D339" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E339" t="n">
+        <v>-1.74993186952609e-06</v>
+      </c>
+      <c r="F339" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr"/>
+      <c r="B340" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>caged_estoque</t>
+        </is>
+      </c>
+      <c r="D340" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E340" t="n">
+        <v>-3.035477068790604e-07</v>
+      </c>
+      <c r="F340" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr"/>
+      <c r="B341" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>cons_energ_comercial</t>
+        </is>
+      </c>
+      <c r="D341" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E341" t="n">
+        <v>-0.0004816544719639772</v>
+      </c>
+      <c r="F341" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr"/>
+      <c r="B342" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>cons_energ_industrial</t>
+        </is>
+      </c>
+      <c r="D342" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E342" t="n">
+        <v>0.0001069313095316109</v>
+      </c>
+      <c r="F342" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr"/>
+      <c r="B343" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>cons_energ_outros</t>
+        </is>
+      </c>
+      <c r="D343" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E343" t="n">
+        <v>-0.0004816544719639774</v>
+      </c>
+      <c r="F343" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr"/>
+      <c r="B344" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>cons_energ_residencial</t>
+        </is>
+      </c>
+      <c r="D344" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E344" t="n">
+        <v>0.0007787113485033558</v>
+      </c>
+      <c r="F344" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr"/>
+      <c r="B345" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>prod_aco_bruto</t>
+        </is>
+      </c>
+      <c r="D345" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E345" t="n">
+        <v>-1.68997106852096e-05</v>
+      </c>
+      <c r="F345" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr"/>
+      <c r="B346" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>renda_disponivel_familias_restrita</t>
+        </is>
+      </c>
+      <c r="D346" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E346" t="n">
+        <v>-3.962444001794565e-08</v>
+      </c>
+      <c r="F346" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr"/>
+      <c r="B347" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>icc_fecomercio</t>
+        </is>
+      </c>
+      <c r="D347" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E347" t="n">
+        <v>-1.049677674948758e-08</v>
+      </c>
+      <c r="F347" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr"/>
+      <c r="B348" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>icea_fecomercio</t>
+        </is>
+      </c>
+      <c r="D348" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E348" t="n">
+        <v>-1.051988993251497e-08</v>
+      </c>
+      <c r="F348" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr"/>
+      <c r="B349" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>ief_fecomercio</t>
+        </is>
+      </c>
+      <c r="D349" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E349" t="n">
+        <v>1.113130221670867e-07</v>
+      </c>
+      <c r="F349" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr"/>
+      <c r="B350" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>igp10</t>
+        </is>
+      </c>
+      <c r="D350" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E350" t="n">
+        <v>-1.2300894505301e-07</v>
+      </c>
+      <c r="F350" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr"/>
+      <c r="B351" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>igpm</t>
+        </is>
+      </c>
+      <c r="D351" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E351" t="n">
+        <v>-6.875883129612143e-06</v>
+      </c>
+      <c r="F351" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr"/>
+      <c r="B352" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>ipam</t>
+        </is>
+      </c>
+      <c r="D352" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E352" t="n">
+        <v>-8.524341084868481e-06</v>
+      </c>
+      <c r="F352" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr"/>
+      <c r="B353" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>ipc_fipe</t>
+        </is>
+      </c>
+      <c r="D353" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E353" t="n">
+        <v>5.945261042208791e-08</v>
+      </c>
+      <c r="F353" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr"/>
+      <c r="B354" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>ipca15</t>
+        </is>
+      </c>
+      <c r="D354" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E354" t="n">
+        <v>4.894735158688795e-07</v>
+      </c>
+      <c r="F354" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr"/>
+      <c r="B355" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>caged_estoque</t>
+        </is>
+      </c>
+      <c r="D355" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E355" t="n">
+        <v>1.130796339101029e-06</v>
+      </c>
+      <c r="F355" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr"/>
+      <c r="B356" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>cons_energ_comercial</t>
+        </is>
+      </c>
+      <c r="D356" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E356" t="n">
+        <v>0.0004456156043228075</v>
+      </c>
+      <c r="F356" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr"/>
+      <c r="B357" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>cons_energ_industrial</t>
+        </is>
+      </c>
+      <c r="D357" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E357" t="n">
+        <v>-4.187723233293524e-05</v>
+      </c>
+      <c r="F357" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr"/>
+      <c r="B358" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>cons_energ_outros</t>
+        </is>
+      </c>
+      <c r="D358" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E358" t="n">
+        <v>0.0004456156043228016</v>
+      </c>
+      <c r="F358" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr"/>
+      <c r="B359" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>cons_energ_residencial</t>
+        </is>
+      </c>
+      <c r="D359" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E359" t="n">
+        <v>0.0005184426008786788</v>
+      </c>
+      <c r="F359" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr"/>
+      <c r="B360" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>prod_aco_bruto</t>
+        </is>
+      </c>
+      <c r="D360" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E360" t="n">
+        <v>-3.314901841707785e-05</v>
+      </c>
+      <c r="F360" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr"/>
+      <c r="B361" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>renda_disponivel_familias_restrita</t>
+        </is>
+      </c>
+      <c r="D361" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E361" t="n">
+        <v>6.17136372222312e-08</v>
+      </c>
+      <c r="F361" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr"/>
+      <c r="B362" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>icc_fecomercio</t>
+        </is>
+      </c>
+      <c r="D362" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E362" t="n">
+        <v>-2.683261123301344e-08</v>
+      </c>
+      <c r="F362" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr"/>
+      <c r="B363" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>icea_fecomercio</t>
+        </is>
+      </c>
+      <c r="D363" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E363" t="n">
+        <v>-2.615144617694762e-08</v>
+      </c>
+      <c r="F363" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr"/>
+      <c r="B364" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>ief_fecomercio</t>
+        </is>
+      </c>
+      <c r="D364" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E364" t="n">
+        <v>4.498865760562718e-07</v>
+      </c>
+      <c r="F364" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr"/>
+      <c r="B365" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>igp10</t>
+        </is>
+      </c>
+      <c r="D365" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E365" t="n">
+        <v>2.213480272215252e-06</v>
+      </c>
+      <c r="F365" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr"/>
+      <c r="B366" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>igpm</t>
+        </is>
+      </c>
+      <c r="D366" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E366" t="n">
+        <v>4.464720181636617e-05</v>
+      </c>
+      <c r="F366" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr"/>
+      <c r="B367" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>ipam</t>
+        </is>
+      </c>
+      <c r="D367" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E367" t="n">
+        <v>8.858951394006388e-06</v>
+      </c>
+      <c r="F367" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr"/>
+      <c r="B368" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>ipc_fipe</t>
+        </is>
+      </c>
+      <c r="D368" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E368" t="n">
+        <v>6.35441869731177e-07</v>
+      </c>
+      <c r="F368" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr"/>
+      <c r="B369" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>ipca15</t>
+        </is>
+      </c>
+      <c r="D369" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E369" t="n">
+        <v>7.436642100652855e-06</v>
+      </c>
+      <c r="F369" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr"/>
+      <c r="B370" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>caged_estoque</t>
+        </is>
+      </c>
+      <c r="D370" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E370" t="n">
+        <v>6.872946555773688e-08</v>
+      </c>
+      <c r="F370" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr"/>
+      <c r="B371" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>cons_energ_comercial</t>
+        </is>
+      </c>
+      <c r="D371" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E371" t="n">
+        <v>-0.004575900515646497</v>
+      </c>
+      <c r="F371" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr"/>
+      <c r="B372" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>cons_energ_industrial</t>
+        </is>
+      </c>
+      <c r="D372" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E372" t="n">
+        <v>0.0002413556400984115</v>
+      </c>
+      <c r="F372" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr"/>
+      <c r="B373" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>cons_energ_outros</t>
+        </is>
+      </c>
+      <c r="D373" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E373" t="n">
+        <v>-0.004575900515646486</v>
+      </c>
+      <c r="F373" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr"/>
+      <c r="B374" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>cons_energ_residencial</t>
+        </is>
+      </c>
+      <c r="D374" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E374" t="n">
+        <v>-0.00412736121810222</v>
+      </c>
+      <c r="F374" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr"/>
+      <c r="B375" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>prod_aco_bruto</t>
+        </is>
+      </c>
+      <c r="D375" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E375" t="n">
+        <v>0.0001334978855629182</v>
+      </c>
+      <c r="F375" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr"/>
+      <c r="B376" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>renda_disponivel_familias_restrita</t>
+        </is>
+      </c>
+      <c r="D376" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E376" t="n">
+        <v>1.799057094022754e-06</v>
+      </c>
+      <c r="F376" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr"/>
+      <c r="B377" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>icc_fecomercio</t>
+        </is>
+      </c>
+      <c r="D377" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E377" t="n">
+        <v>-1.317366118396627e-07</v>
+      </c>
+      <c r="F377" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr"/>
+      <c r="B378" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>icea_fecomercio</t>
+        </is>
+      </c>
+      <c r="D378" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E378" t="n">
+        <v>-1.099681341326235e-07</v>
+      </c>
+      <c r="F378" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr"/>
+      <c r="B379" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>ief_fecomercio</t>
+        </is>
+      </c>
+      <c r="D379" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E379" t="n">
+        <v>2.357773488703392e-07</v>
+      </c>
+      <c r="F379" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr"/>
+      <c r="B380" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>igp10</t>
+        </is>
+      </c>
+      <c r="D380" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E380" t="n">
+        <v>1.493375716724124e-05</v>
+      </c>
+      <c r="F380" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr"/>
+      <c r="B381" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>igpm</t>
+        </is>
+      </c>
+      <c r="D381" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E381" t="n">
+        <v>0.0003097626901331015</v>
+      </c>
+      <c r="F381" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr"/>
+      <c r="B382" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>ipam</t>
+        </is>
+      </c>
+      <c r="D382" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E382" t="n">
+        <v>0.0001647741489429569</v>
+      </c>
+      <c r="F382" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr"/>
+      <c r="B383" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>ipc_fipe</t>
+        </is>
+      </c>
+      <c r="D383" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E383" t="n">
+        <v>9.322295016120074e-06</v>
+      </c>
+      <c r="F383" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr"/>
+      <c r="B384" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>ipca15</t>
+        </is>
+      </c>
+      <c r="D384" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E384" t="n">
+        <v>1.690431739002972e-05</v>
+      </c>
+      <c r="F384" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr"/>
+      <c r="B385" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>caged_estoque</t>
+        </is>
+      </c>
+      <c r="D385" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E385" t="n">
+        <v>-2.352602721439669e-05</v>
+      </c>
+      <c r="F385" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr"/>
+      <c r="B386" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>cons_energ_comercial</t>
+        </is>
+      </c>
+      <c r="D386" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E386" t="n">
+        <v>-0.003710912033265726</v>
+      </c>
+      <c r="F386" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr"/>
+      <c r="B387" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>cons_energ_industrial</t>
+        </is>
+      </c>
+      <c r="D387" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E387" t="n">
+        <v>-0.0004903920892688167</v>
+      </c>
+      <c r="F387" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr"/>
+      <c r="B388" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>cons_energ_outros</t>
+        </is>
+      </c>
+      <c r="D388" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E388" t="n">
+        <v>-0.003710912033265724</v>
+      </c>
+      <c r="F388" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr"/>
+      <c r="B389" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>cons_energ_residencial</t>
+        </is>
+      </c>
+      <c r="D389" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E389" t="n">
+        <v>0.001374088060342331</v>
+      </c>
+      <c r="F389" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr"/>
+      <c r="B390" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>prod_aco_bruto</t>
+        </is>
+      </c>
+      <c r="D390" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E390" t="n">
+        <v>7.702109771845746e-05</v>
+      </c>
+      <c r="F390" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr"/>
+      <c r="B391" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>renda_disponivel_familias_restrita</t>
+        </is>
+      </c>
+      <c r="D391" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E391" t="n">
+        <v>1.401792656866053e-05</v>
+      </c>
+      <c r="F391" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr"/>
+      <c r="B392" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>icc_fecomercio</t>
+        </is>
+      </c>
+      <c r="D392" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E392" t="n">
+        <v>-2.226575565520246e-07</v>
+      </c>
+      <c r="F392" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr"/>
+      <c r="B393" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>icea_fecomercio</t>
+        </is>
+      </c>
+      <c r="D393" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E393" t="n">
+        <v>-8.124618320775237e-08</v>
+      </c>
+      <c r="F393" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr"/>
+      <c r="B394" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>ief_fecomercio</t>
+        </is>
+      </c>
+      <c r="D394" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E394" t="n">
+        <v>-3.330962144551856e-06</v>
+      </c>
+      <c r="F394" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr"/>
+      <c r="B395" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>igp10</t>
+        </is>
+      </c>
+      <c r="D395" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E395" t="n">
+        <v>-3.119198423121126e-05</v>
+      </c>
+      <c r="F395" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr"/>
+      <c r="B396" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>igpm</t>
+        </is>
+      </c>
+      <c r="D396" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E396" t="n">
+        <v>0.0001132691368672017</v>
+      </c>
+      <c r="F396" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr"/>
+      <c r="B397" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>ipam</t>
+        </is>
+      </c>
+      <c r="D397" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E397" t="n">
+        <v>4.21921576603805e-05</v>
+      </c>
+      <c r="F397" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr"/>
+      <c r="B398" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>ipc_fipe</t>
+        </is>
+      </c>
+      <c r="D398" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E398" t="n">
+        <v>2.853178857184463e-05</v>
+      </c>
+      <c r="F398" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr"/>
+      <c r="B399" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>ipca15</t>
+        </is>
+      </c>
+      <c r="D399" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E399" t="n">
+        <v>-9.298437321751037e-05</v>
+      </c>
+      <c r="F399" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr"/>
+      <c r="B400" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>caged_estoque</t>
+        </is>
+      </c>
+      <c r="D400" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E400" t="n">
+        <v>2.012022207897281e-05</v>
+      </c>
+      <c r="F400" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr"/>
+      <c r="B401" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>cons_energ_comercial</t>
+        </is>
+      </c>
+      <c r="D401" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E401" t="n">
+        <v>0.04309346712843985</v>
+      </c>
+      <c r="F401" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr"/>
+      <c r="B402" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>cons_energ_industrial</t>
+        </is>
+      </c>
+      <c r="D402" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E402" t="n">
+        <v>-0.03634008302072622</v>
+      </c>
+      <c r="F402" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr"/>
+      <c r="B403" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>cons_energ_outros</t>
+        </is>
+      </c>
+      <c r="D403" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E403" t="n">
+        <v>0.04309346712843961</v>
+      </c>
+      <c r="F403" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr"/>
+      <c r="B404" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>cons_energ_residencial</t>
+        </is>
+      </c>
+      <c r="D404" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E404" t="n">
+        <v>0.01571151253829269</v>
+      </c>
+      <c r="F404" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr"/>
+      <c r="B405" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>prod_aco_bruto</t>
+        </is>
+      </c>
+      <c r="D405" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E405" t="n">
+        <v>0.009533374516245596</v>
+      </c>
+      <c r="F405" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr"/>
+      <c r="B406" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>renda_disponivel_familias_restrita</t>
+        </is>
+      </c>
+      <c r="D406" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E406" t="n">
+        <v>2.65479117820699e-05</v>
+      </c>
+      <c r="F406" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr"/>
+      <c r="B407" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>icc_fecomercio</t>
+        </is>
+      </c>
+      <c r="D407" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E407" t="n">
+        <v>-7.043091578074693e-08</v>
+      </c>
+      <c r="F407" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr"/>
+      <c r="B408" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>icea_fecomercio</t>
+        </is>
+      </c>
+      <c r="D408" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E408" t="n">
+        <v>-1.074154187249916e-07</v>
+      </c>
+      <c r="F408" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr"/>
+      <c r="B409" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>ief_fecomercio</t>
+        </is>
+      </c>
+      <c r="D409" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E409" t="n">
+        <v>1.444458858157158e-06</v>
+      </c>
+      <c r="F409" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr"/>
+      <c r="B410" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>igp10</t>
+        </is>
+      </c>
+      <c r="D410" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E410" t="n">
+        <v>3.98029168752878e-05</v>
+      </c>
+      <c r="F410" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr"/>
+      <c r="B411" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>igpm</t>
+        </is>
+      </c>
+      <c r="D411" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E411" t="n">
+        <v>0.0006112407955594704</v>
+      </c>
+      <c r="F411" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr"/>
+      <c r="B412" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>ipam</t>
+        </is>
+      </c>
+      <c r="D412" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E412" t="n">
+        <v>0.0003489351452854184</v>
+      </c>
+      <c r="F412" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr"/>
+      <c r="B413" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>ipc_fipe</t>
+        </is>
+      </c>
+      <c r="D413" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E413" t="n">
+        <v>1.366912609970924e-05</v>
+      </c>
+      <c r="F413" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr"/>
+      <c r="B414" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>ipca15</t>
+        </is>
+      </c>
+      <c r="D414" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E414" t="n">
+        <v>2.944837359237213e-05</v>
+      </c>
+      <c r="F414" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr"/>
+      <c r="B415" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>fgv_nuci</t>
+        </is>
+      </c>
+      <c r="D415" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E415" t="n">
+        <v>0.01395068877560402</v>
+      </c>
+      <c r="F415" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr"/>
+      <c r="B416" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>icc_fecomercio</t>
+        </is>
+      </c>
+      <c r="D416" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E416" t="n">
+        <v>-7.741918865068684e-07</v>
+      </c>
+      <c r="F416" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr"/>
+      <c r="B417" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>icea_fecomercio</t>
+        </is>
+      </c>
+      <c r="D417" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E417" t="n">
+        <v>-1.421163416323249e-06</v>
+      </c>
+      <c r="F417" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr"/>
+      <c r="B418" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>ics_fgv</t>
+        </is>
+      </c>
+      <c r="D418" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E418" t="n">
+        <v>-0.0003227554899714855</v>
+      </c>
+      <c r="F418" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr"/>
+      <c r="B419" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>ief_fecomercio</t>
+        </is>
+      </c>
+      <c r="D419" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E419" t="n">
+        <v>2.860055121383428e-05</v>
+      </c>
+      <c r="F419" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr"/>
+      <c r="B420" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>ies_fgv</t>
+        </is>
+      </c>
+      <c r="D420" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E420" t="n">
+        <v>0.0004846076988056408</v>
+      </c>
+      <c r="F420" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr"/>
+      <c r="B421" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>igp10</t>
+        </is>
+      </c>
+      <c r="D421" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E421" t="n">
+        <v>0.001212645213214508</v>
+      </c>
+      <c r="F421" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr"/>
+      <c r="B422" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>igpm</t>
+        </is>
+      </c>
+      <c r="D422" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E422" t="n">
+        <v>0.000368622912757828</v>
+      </c>
+      <c r="F422" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr"/>
+      <c r="B423" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>ipam</t>
+        </is>
+      </c>
+      <c r="D423" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E423" t="n">
+        <v>3.06455429576093e-05</v>
+      </c>
+      <c r="F423" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr"/>
+      <c r="B424" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>ipc_fipe</t>
+        </is>
+      </c>
+      <c r="D424" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E424" t="n">
+        <v>0.0003114996587612145</v>
+      </c>
+      <c r="F424" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr"/>
+      <c r="B425" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>ipca15</t>
+        </is>
+      </c>
+      <c r="D425" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E425" t="n">
+        <v>0.0004463955141161007</v>
+      </c>
+      <c r="F425" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr"/>
+      <c r="B426" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>isas_fgv</t>
+        </is>
+      </c>
+      <c r="D426" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E426" t="n">
+        <v>-9.266177938756956e-05</v>
+      </c>
+      <c r="F426" s="2" t="n">
+        <v>46209</v>
       </c>
     </row>
   </sheetData>

--- a/pib_nowcast/data/news_impacts.xlsx
+++ b/pib_nowcast/data/news_impacts.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F426"/>
+  <dimension ref="A1:F535"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5137,7 +5137,7 @@
       <c r="E234" t="n">
         <v>-6.767678611338938e-05</v>
       </c>
-      <c r="F234" s="2" t="n">
+      <c r="F234" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -5157,7 +5157,7 @@
       <c r="E235" t="n">
         <v>-1.806986067570489e-08</v>
       </c>
-      <c r="F235" s="2" t="n">
+      <c r="F235" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -5177,7 +5177,7 @@
       <c r="E236" t="n">
         <v>-4.372513299396422e-05</v>
       </c>
-      <c r="F236" s="2" t="n">
+      <c r="F236" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -5197,7 +5197,7 @@
       <c r="E237" t="n">
         <v>-3.995736897696023e-06</v>
       </c>
-      <c r="F237" s="2" t="n">
+      <c r="F237" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -5217,7 +5217,7 @@
       <c r="E238" t="n">
         <v>-4.37251329939641e-05</v>
       </c>
-      <c r="F238" s="2" t="n">
+      <c r="F238" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -5237,7 +5237,7 @@
       <c r="E239" t="n">
         <v>-4.070427536664081e-05</v>
       </c>
-      <c r="F239" s="2" t="n">
+      <c r="F239" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -5257,7 +5257,7 @@
       <c r="E240" t="n">
         <v>-2.186857191301488e-05</v>
       </c>
-      <c r="F240" s="2" t="n">
+      <c r="F240" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -5277,7 +5277,7 @@
       <c r="E241" t="n">
         <v>-3.823952645825379e-08</v>
       </c>
-      <c r="F241" s="2" t="n">
+      <c r="F241" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -5297,7 +5297,7 @@
       <c r="E242" t="n">
         <v>-6.30547437522082e-09</v>
       </c>
-      <c r="F242" s="2" t="n">
+      <c r="F242" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -5317,7 +5317,7 @@
       <c r="E243" t="n">
         <v>7.52483329444972e-09</v>
       </c>
-      <c r="F243" s="2" t="n">
+      <c r="F243" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -5337,7 +5337,7 @@
       <c r="E244" t="n">
         <v>-5.882182477342406e-08</v>
       </c>
-      <c r="F244" s="2" t="n">
+      <c r="F244" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -5357,7 +5357,7 @@
       <c r="E245" t="n">
         <v>-5.807335714906513e-07</v>
       </c>
-      <c r="F245" s="2" t="n">
+      <c r="F245" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -5377,7 +5377,7 @@
       <c r="E246" t="n">
         <v>1.455445339797876e-05</v>
       </c>
-      <c r="F246" s="2" t="n">
+      <c r="F246" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -5397,7 +5397,7 @@
       <c r="E247" t="n">
         <v>8.653370563502802e-06</v>
       </c>
-      <c r="F247" s="2" t="n">
+      <c r="F247" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -5417,7 +5417,7 @@
       <c r="E248" t="n">
         <v>5.848757032087921e-07</v>
       </c>
-      <c r="F248" s="2" t="n">
+      <c r="F248" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -5437,7 +5437,7 @@
       <c r="E249" t="n">
         <v>4.568853191682978e-07</v>
       </c>
-      <c r="F249" s="2" t="n">
+      <c r="F249" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -5457,7 +5457,7 @@
       <c r="E250" t="n">
         <v>1.667329514637693e-09</v>
       </c>
-      <c r="F250" s="2" t="n">
+      <c r="F250" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -5477,7 +5477,7 @@
       <c r="E251" t="n">
         <v>-3.361966208546185e-06</v>
       </c>
-      <c r="F251" s="2" t="n">
+      <c r="F251" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -5497,7 +5497,7 @@
       <c r="E252" t="n">
         <v>-5.643996471271497e-06</v>
       </c>
-      <c r="F252" s="2" t="n">
+      <c r="F252" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -5517,7 +5517,7 @@
       <c r="E253" t="n">
         <v>-3.361966208546186e-06</v>
       </c>
-      <c r="F253" s="2" t="n">
+      <c r="F253" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -5537,7 +5537,7 @@
       <c r="E254" t="n">
         <v>9.34096889546022e-06</v>
       </c>
-      <c r="F254" s="2" t="n">
+      <c r="F254" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -5557,7 +5557,7 @@
       <c r="E255" t="n">
         <v>4.382925290427956e-06</v>
       </c>
-      <c r="F255" s="2" t="n">
+      <c r="F255" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -5577,7 +5577,7 @@
       <c r="E256" t="n">
         <v>-1.573882570918851e-08</v>
       </c>
-      <c r="F256" s="2" t="n">
+      <c r="F256" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -5597,7 +5597,7 @@
       <c r="E257" t="n">
         <v>-2.891249282582984e-10</v>
       </c>
-      <c r="F257" s="2" t="n">
+      <c r="F257" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -5617,7 +5617,7 @@
       <c r="E258" t="n">
         <v>9.740551367190854e-10</v>
       </c>
-      <c r="F258" s="2" t="n">
+      <c r="F258" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -5637,7 +5637,7 @@
       <c r="E259" t="n">
         <v>1.160404978859518e-10</v>
       </c>
-      <c r="F259" s="2" t="n">
+      <c r="F259" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -5657,7 +5657,7 @@
       <c r="E260" t="n">
         <v>3.893490751174692e-08</v>
       </c>
-      <c r="F260" s="2" t="n">
+      <c r="F260" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -5677,7 +5677,7 @@
       <c r="E261" t="n">
         <v>-7.485138977200329e-08</v>
       </c>
-      <c r="F261" s="2" t="n">
+      <c r="F261" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       <c r="E262" t="n">
         <v>-2.764936998349154e-08</v>
       </c>
-      <c r="F262" s="2" t="n">
+      <c r="F262" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -5717,7 +5717,7 @@
       <c r="E263" t="n">
         <v>7.483870970806079e-10</v>
       </c>
-      <c r="F263" s="2" t="n">
+      <c r="F263" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -5737,7 +5737,7 @@
       <c r="E264" t="n">
         <v>4.311774695690316e-10</v>
       </c>
-      <c r="F264" s="2" t="n">
+      <c r="F264" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -5757,7 +5757,7 @@
       <c r="E265" t="n">
         <v>9.023444380867132e-09</v>
       </c>
-      <c r="F265" s="2" t="n">
+      <c r="F265" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -5777,7 +5777,7 @@
       <c r="E266" t="n">
         <v>-1.869098113107525e-07</v>
       </c>
-      <c r="F266" s="2" t="n">
+      <c r="F266" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -5797,7 +5797,7 @@
       <c r="E267" t="n">
         <v>1.841783896636858e-06</v>
       </c>
-      <c r="F267" s="2" t="n">
+      <c r="F267" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -5817,7 +5817,7 @@
       <c r="E268" t="n">
         <v>-1.869098113107501e-07</v>
       </c>
-      <c r="F268" s="2" t="n">
+      <c r="F268" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -5837,7 +5837,7 @@
       <c r="E269" t="n">
         <v>-4.52347486123709e-07</v>
       </c>
-      <c r="F269" s="2" t="n">
+      <c r="F269" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -5857,7 +5857,7 @@
       <c r="E270" t="n">
         <v>2.597143111361442e-06</v>
       </c>
-      <c r="F270" s="2" t="n">
+      <c r="F270" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -5877,7 +5877,7 @@
       <c r="E271" t="n">
         <v>-4.990200353427761e-10</v>
       </c>
-      <c r="F271" s="2" t="n">
+      <c r="F271" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -5897,7 +5897,7 @@
       <c r="E272" t="n">
         <v>7.256675642235031e-09</v>
       </c>
-      <c r="F272" s="2" t="n">
+      <c r="F272" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -5917,7 +5917,7 @@
       <c r="E273" t="n">
         <v>8.958209610934607e-09</v>
       </c>
-      <c r="F273" s="2" t="n">
+      <c r="F273" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -5937,7 +5937,7 @@
       <c r="E274" t="n">
         <v>-1.801779655778714e-08</v>
       </c>
-      <c r="F274" s="2" t="n">
+      <c r="F274" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -5957,7 +5957,7 @@
       <c r="E275" t="n">
         <v>-3.648752101648047e-07</v>
       </c>
-      <c r="F275" s="2" t="n">
+      <c r="F275" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -5977,7 +5977,7 @@
       <c r="E276" t="n">
         <v>6.016079072599208e-07</v>
       </c>
-      <c r="F276" s="2" t="n">
+      <c r="F276" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -5997,7 +5997,7 @@
       <c r="E277" t="n">
         <v>1.641097955604313e-07</v>
       </c>
-      <c r="F277" s="2" t="n">
+      <c r="F277" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -6017,7 +6017,7 @@
       <c r="E278" t="n">
         <v>-7.008594310268701e-09</v>
       </c>
-      <c r="F278" s="2" t="n">
+      <c r="F278" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -6037,7 +6037,7 @@
       <c r="E279" t="n">
         <v>-2.753458258816785e-08</v>
       </c>
-      <c r="F279" s="2" t="n">
+      <c r="F279" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -6057,7 +6057,7 @@
       <c r="E280" t="n">
         <v>-8.603078536859787e-08</v>
       </c>
-      <c r="F280" s="2" t="n">
+      <c r="F280" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -6077,7 +6077,7 @@
       <c r="E281" t="n">
         <v>1.784324298254596e-05</v>
       </c>
-      <c r="F281" s="2" t="n">
+      <c r="F281" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -6097,7 +6097,7 @@
       <c r="E282" t="n">
         <v>6.930649375914306e-06</v>
       </c>
-      <c r="F282" s="2" t="n">
+      <c r="F282" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -6117,7 +6117,7 @@
       <c r="E283" t="n">
         <v>1.784324298254587e-05</v>
       </c>
-      <c r="F283" s="2" t="n">
+      <c r="F283" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -6137,7 +6137,7 @@
       <c r="E284" t="n">
         <v>4.91731393678267e-06</v>
       </c>
-      <c r="F284" s="2" t="n">
+      <c r="F284" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -6157,7 +6157,7 @@
       <c r="E285" t="n">
         <v>-3.588430531904211e-07</v>
       </c>
-      <c r="F285" s="2" t="n">
+      <c r="F285" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -6177,7 +6177,7 @@
       <c r="E286" t="n">
         <v>2.786549980201554e-08</v>
       </c>
-      <c r="F286" s="2" t="n">
+      <c r="F286" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -6197,7 +6197,7 @@
       <c r="E287" t="n">
         <v>-1.258699079445072e-08</v>
       </c>
-      <c r="F287" s="2" t="n">
+      <c r="F287" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -6217,7 +6217,7 @@
       <c r="E288" t="n">
         <v>-9.961270104455088e-09</v>
       </c>
-      <c r="F288" s="2" t="n">
+      <c r="F288" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -6237,7 +6237,7 @@
       <c r="E289" t="n">
         <v>4.859610140082849e-08</v>
       </c>
-      <c r="F289" s="2" t="n">
+      <c r="F289" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -6257,7 +6257,7 @@
       <c r="E290" t="n">
         <v>-1.012104829252881e-06</v>
       </c>
-      <c r="F290" s="2" t="n">
+      <c r="F290" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -6277,7 +6277,7 @@
       <c r="E291" t="n">
         <v>1.683868052684164e-06</v>
       </c>
-      <c r="F291" s="2" t="n">
+      <c r="F291" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -6297,7 +6297,7 @@
       <c r="E292" t="n">
         <v>7.647310319292462e-07</v>
       </c>
-      <c r="F292" s="2" t="n">
+      <c r="F292" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -6317,7 +6317,7 @@
       <c r="E293" t="n">
         <v>-8.758837053625556e-08</v>
       </c>
-      <c r="F293" s="2" t="n">
+      <c r="F293" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -6337,7 +6337,7 @@
       <c r="E294" t="n">
         <v>-2.254663421035848e-07</v>
       </c>
-      <c r="F294" s="2" t="n">
+      <c r="F294" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -6357,7 +6357,7 @@
       <c r="E295" t="n">
         <v>-8.834701594580101e-09</v>
       </c>
-      <c r="F295" s="2" t="n">
+      <c r="F295" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -6377,7 +6377,7 @@
       <c r="E296" t="n">
         <v>-0.0002747266515150265</v>
       </c>
-      <c r="F296" s="2" t="n">
+      <c r="F296" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -6397,7 +6397,7 @@
       <c r="E297" t="n">
         <v>-3.370532417871826e-06</v>
       </c>
-      <c r="F297" s="2" t="n">
+      <c r="F297" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -6417,7 +6417,7 @@
       <c r="E298" t="n">
         <v>-0.0002747266515150266</v>
       </c>
-      <c r="F298" s="2" t="n">
+      <c r="F298" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -6437,7 +6437,7 @@
       <c r="E299" t="n">
         <v>-0.0001889112218946398</v>
       </c>
-      <c r="F299" s="2" t="n">
+      <c r="F299" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -6457,7 +6457,7 @@
       <c r="E300" t="n">
         <v>-1.385003169361316e-05</v>
       </c>
-      <c r="F300" s="2" t="n">
+      <c r="F300" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -6477,7 +6477,7 @@
       <c r="E301" t="n">
         <v>8.078995644911486e-09</v>
       </c>
-      <c r="F301" s="2" t="n">
+      <c r="F301" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -6497,7 +6497,7 @@
       <c r="E302" t="n">
         <v>2.390846927456127e-10</v>
       </c>
-      <c r="F302" s="2" t="n">
+      <c r="F302" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -6517,7 +6517,7 @@
       <c r="E303" t="n">
         <v>2.897590524081282e-10</v>
       </c>
-      <c r="F303" s="2" t="n">
+      <c r="F303" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -6537,7 +6537,7 @@
       <c r="E304" t="n">
         <v>1.222122747315816e-09</v>
       </c>
-      <c r="F304" s="2" t="n">
+      <c r="F304" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -6557,7 +6557,7 @@
       <c r="E305" t="n">
         <v>-1.376527075547137e-07</v>
       </c>
-      <c r="F305" s="2" t="n">
+      <c r="F305" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -6577,7 +6577,7 @@
       <c r="E306" t="n">
         <v>1.148773326066973e-07</v>
       </c>
-      <c r="F306" s="2" t="n">
+      <c r="F306" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -6597,7 +6597,7 @@
       <c r="E307" t="n">
         <v>7.719528269623227e-08</v>
       </c>
-      <c r="F307" s="2" t="n">
+      <c r="F307" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -6617,7 +6617,7 @@
       <c r="E308" t="n">
         <v>-1.417224368993234e-09</v>
       </c>
-      <c r="F308" s="2" t="n">
+      <c r="F308" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -6637,7 +6637,7 @@
       <c r="E309" t="n">
         <v>3.014780308534552e-10</v>
       </c>
-      <c r="F309" s="2" t="n">
+      <c r="F309" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -6657,7 +6657,7 @@
       <c r="E310" t="n">
         <v>-1.736982000887724e-10</v>
       </c>
-      <c r="F310" s="2" t="n">
+      <c r="F310" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       <c r="E311" t="n">
         <v>-0.0003722892399762872</v>
       </c>
-      <c r="F311" s="2" t="n">
+      <c r="F311" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -6697,7 +6697,7 @@
       <c r="E312" t="n">
         <v>3.280519636641481e-07</v>
       </c>
-      <c r="F312" s="2" t="n">
+      <c r="F312" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -6717,7 +6717,7 @@
       <c r="E313" t="n">
         <v>-0.0003722892399762829</v>
       </c>
-      <c r="F313" s="2" t="n">
+      <c r="F313" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -6737,7 +6737,7 @@
       <c r="E314" t="n">
         <v>-0.0001678284154961287</v>
       </c>
-      <c r="F314" s="2" t="n">
+      <c r="F314" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -6757,7 +6757,7 @@
       <c r="E315" t="n">
         <v>-1.723039468133557e-05</v>
       </c>
-      <c r="F315" s="2" t="n">
+      <c r="F315" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -6777,7 +6777,7 @@
       <c r="E316" t="n">
         <v>-1.61601628626918e-08</v>
       </c>
-      <c r="F316" s="2" t="n">
+      <c r="F316" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -6797,7 +6797,7 @@
       <c r="E317" t="n">
         <v>3.823212647412811e-09</v>
       </c>
-      <c r="F317" s="2" t="n">
+      <c r="F317" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -6817,7 +6817,7 @@
       <c r="E318" t="n">
         <v>8.746832223569201e-09</v>
       </c>
-      <c r="F318" s="2" t="n">
+      <c r="F318" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -6837,7 +6837,7 @@
       <c r="E319" t="n">
         <v>3.269596598718983e-09</v>
       </c>
-      <c r="F319" s="2" t="n">
+      <c r="F319" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -6857,7 +6857,7 @@
       <c r="E320" t="n">
         <v>5.025936831499769e-07</v>
       </c>
-      <c r="F320" s="2" t="n">
+      <c r="F320" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -6877,7 +6877,7 @@
       <c r="E321" t="n">
         <v>-7.222800535877984e-06</v>
       </c>
-      <c r="F321" s="2" t="n">
+      <c r="F321" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -6897,7 +6897,7 @@
       <c r="E322" t="n">
         <v>-3.807838724303162e-06</v>
       </c>
-      <c r="F322" s="2" t="n">
+      <c r="F322" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -6917,7 +6917,7 @@
       <c r="E323" t="n">
         <v>-4.938348940754899e-08</v>
       </c>
-      <c r="F323" s="2" t="n">
+      <c r="F323" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -6937,7 +6937,7 @@
       <c r="E324" t="n">
         <v>-8.515229515192669e-08</v>
       </c>
-      <c r="F324" s="2" t="n">
+      <c r="F324" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -6957,7 +6957,7 @@
       <c r="E325" t="n">
         <v>6.423393567004242e-08</v>
       </c>
-      <c r="F325" s="2" t="n">
+      <c r="F325" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -6977,7 +6977,7 @@
       <c r="E326" t="n">
         <v>0.0001219113915190124</v>
       </c>
-      <c r="F326" s="2" t="n">
+      <c r="F326" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -6997,7 +6997,7 @@
       <c r="E327" t="n">
         <v>-5.48969560904824e-05</v>
       </c>
-      <c r="F327" s="2" t="n">
+      <c r="F327" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -7017,7 +7017,7 @@
       <c r="E328" t="n">
         <v>0.0001219113915190119</v>
       </c>
-      <c r="F328" s="2" t="n">
+      <c r="F328" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -7037,7 +7037,7 @@
       <c r="E329" t="n">
         <v>-7.56103661157655e-05</v>
       </c>
-      <c r="F329" s="2" t="n">
+      <c r="F329" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -7057,7 +7057,7 @@
       <c r="E330" t="n">
         <v>9.162044044983277e-06</v>
       </c>
-      <c r="F330" s="2" t="n">
+      <c r="F330" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -7077,7 +7077,7 @@
       <c r="E331" t="n">
         <v>1.562237362186938e-08</v>
       </c>
-      <c r="F331" s="2" t="n">
+      <c r="F331" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -7097,7 +7097,7 @@
       <c r="E332" t="n">
         <v>7.824301887351502e-09</v>
       </c>
-      <c r="F332" s="2" t="n">
+      <c r="F332" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -7117,7 +7117,7 @@
       <c r="E333" t="n">
         <v>7.03640638777097e-09</v>
       </c>
-      <c r="F333" s="2" t="n">
+      <c r="F333" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -7137,7 +7137,7 @@
       <c r="E334" t="n">
         <v>8.196372238976601e-08</v>
       </c>
-      <c r="F334" s="2" t="n">
+      <c r="F334" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -7157,7 +7157,7 @@
       <c r="E335" t="n">
         <v>4.08836853886941e-07</v>
       </c>
-      <c r="F335" s="2" t="n">
+      <c r="F335" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -7177,7 +7177,7 @@
       <c r="E336" t="n">
         <v>-2.158903761204297e-05</v>
       </c>
-      <c r="F336" s="2" t="n">
+      <c r="F336" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -7197,7 +7197,7 @@
       <c r="E337" t="n">
         <v>-1.428330470205869e-05</v>
       </c>
-      <c r="F337" s="2" t="n">
+      <c r="F337" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -7217,7 +7217,7 @@
       <c r="E338" t="n">
         <v>-6.200213679468061e-07</v>
       </c>
-      <c r="F338" s="2" t="n">
+      <c r="F338" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -7237,7 +7237,7 @@
       <c r="E339" t="n">
         <v>-1.74993186952609e-06</v>
       </c>
-      <c r="F339" s="2" t="n">
+      <c r="F339" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -7257,7 +7257,7 @@
       <c r="E340" t="n">
         <v>-3.035477068790604e-07</v>
       </c>
-      <c r="F340" s="2" t="n">
+      <c r="F340" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -7277,7 +7277,7 @@
       <c r="E341" t="n">
         <v>-0.0004816544719639772</v>
       </c>
-      <c r="F341" s="2" t="n">
+      <c r="F341" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -7297,7 +7297,7 @@
       <c r="E342" t="n">
         <v>0.0001069313095316109</v>
       </c>
-      <c r="F342" s="2" t="n">
+      <c r="F342" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -7317,7 +7317,7 @@
       <c r="E343" t="n">
         <v>-0.0004816544719639774</v>
       </c>
-      <c r="F343" s="2" t="n">
+      <c r="F343" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -7337,7 +7337,7 @@
       <c r="E344" t="n">
         <v>0.0007787113485033558</v>
       </c>
-      <c r="F344" s="2" t="n">
+      <c r="F344" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -7357,7 +7357,7 @@
       <c r="E345" t="n">
         <v>-1.68997106852096e-05</v>
       </c>
-      <c r="F345" s="2" t="n">
+      <c r="F345" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -7377,7 +7377,7 @@
       <c r="E346" t="n">
         <v>-3.962444001794565e-08</v>
       </c>
-      <c r="F346" s="2" t="n">
+      <c r="F346" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -7397,7 +7397,7 @@
       <c r="E347" t="n">
         <v>-1.049677674948758e-08</v>
       </c>
-      <c r="F347" s="2" t="n">
+      <c r="F347" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -7417,7 +7417,7 @@
       <c r="E348" t="n">
         <v>-1.051988993251497e-08</v>
       </c>
-      <c r="F348" s="2" t="n">
+      <c r="F348" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -7437,7 +7437,7 @@
       <c r="E349" t="n">
         <v>1.113130221670867e-07</v>
       </c>
-      <c r="F349" s="2" t="n">
+      <c r="F349" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -7457,7 +7457,7 @@
       <c r="E350" t="n">
         <v>-1.2300894505301e-07</v>
       </c>
-      <c r="F350" s="2" t="n">
+      <c r="F350" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -7477,7 +7477,7 @@
       <c r="E351" t="n">
         <v>-6.875883129612143e-06</v>
       </c>
-      <c r="F351" s="2" t="n">
+      <c r="F351" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -7497,7 +7497,7 @@
       <c r="E352" t="n">
         <v>-8.524341084868481e-06</v>
       </c>
-      <c r="F352" s="2" t="n">
+      <c r="F352" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -7517,7 +7517,7 @@
       <c r="E353" t="n">
         <v>5.945261042208791e-08</v>
       </c>
-      <c r="F353" s="2" t="n">
+      <c r="F353" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -7537,7 +7537,7 @@
       <c r="E354" t="n">
         <v>4.894735158688795e-07</v>
       </c>
-      <c r="F354" s="2" t="n">
+      <c r="F354" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -7557,7 +7557,7 @@
       <c r="E355" t="n">
         <v>1.130796339101029e-06</v>
       </c>
-      <c r="F355" s="2" t="n">
+      <c r="F355" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -7577,7 +7577,7 @@
       <c r="E356" t="n">
         <v>0.0004456156043228075</v>
       </c>
-      <c r="F356" s="2" t="n">
+      <c r="F356" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -7597,7 +7597,7 @@
       <c r="E357" t="n">
         <v>-4.187723233293524e-05</v>
       </c>
-      <c r="F357" s="2" t="n">
+      <c r="F357" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -7617,7 +7617,7 @@
       <c r="E358" t="n">
         <v>0.0004456156043228016</v>
       </c>
-      <c r="F358" s="2" t="n">
+      <c r="F358" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -7637,7 +7637,7 @@
       <c r="E359" t="n">
         <v>0.0005184426008786788</v>
       </c>
-      <c r="F359" s="2" t="n">
+      <c r="F359" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -7657,7 +7657,7 @@
       <c r="E360" t="n">
         <v>-3.314901841707785e-05</v>
       </c>
-      <c r="F360" s="2" t="n">
+      <c r="F360" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -7677,7 +7677,7 @@
       <c r="E361" t="n">
         <v>6.17136372222312e-08</v>
       </c>
-      <c r="F361" s="2" t="n">
+      <c r="F361" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -7697,7 +7697,7 @@
       <c r="E362" t="n">
         <v>-2.683261123301344e-08</v>
       </c>
-      <c r="F362" s="2" t="n">
+      <c r="F362" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -7717,7 +7717,7 @@
       <c r="E363" t="n">
         <v>-2.615144617694762e-08</v>
       </c>
-      <c r="F363" s="2" t="n">
+      <c r="F363" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -7737,7 +7737,7 @@
       <c r="E364" t="n">
         <v>4.498865760562718e-07</v>
       </c>
-      <c r="F364" s="2" t="n">
+      <c r="F364" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -7757,7 +7757,7 @@
       <c r="E365" t="n">
         <v>2.213480272215252e-06</v>
       </c>
-      <c r="F365" s="2" t="n">
+      <c r="F365" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -7777,7 +7777,7 @@
       <c r="E366" t="n">
         <v>4.464720181636617e-05</v>
       </c>
-      <c r="F366" s="2" t="n">
+      <c r="F366" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -7797,7 +7797,7 @@
       <c r="E367" t="n">
         <v>8.858951394006388e-06</v>
       </c>
-      <c r="F367" s="2" t="n">
+      <c r="F367" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -7817,7 +7817,7 @@
       <c r="E368" t="n">
         <v>6.35441869731177e-07</v>
       </c>
-      <c r="F368" s="2" t="n">
+      <c r="F368" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -7837,7 +7837,7 @@
       <c r="E369" t="n">
         <v>7.436642100652855e-06</v>
       </c>
-      <c r="F369" s="2" t="n">
+      <c r="F369" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -7857,7 +7857,7 @@
       <c r="E370" t="n">
         <v>6.872946555773688e-08</v>
       </c>
-      <c r="F370" s="2" t="n">
+      <c r="F370" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -7877,7 +7877,7 @@
       <c r="E371" t="n">
         <v>-0.004575900515646497</v>
       </c>
-      <c r="F371" s="2" t="n">
+      <c r="F371" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -7897,7 +7897,7 @@
       <c r="E372" t="n">
         <v>0.0002413556400984115</v>
       </c>
-      <c r="F372" s="2" t="n">
+      <c r="F372" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -7917,7 +7917,7 @@
       <c r="E373" t="n">
         <v>-0.004575900515646486</v>
       </c>
-      <c r="F373" s="2" t="n">
+      <c r="F373" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -7937,7 +7937,7 @@
       <c r="E374" t="n">
         <v>-0.00412736121810222</v>
       </c>
-      <c r="F374" s="2" t="n">
+      <c r="F374" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -7957,7 +7957,7 @@
       <c r="E375" t="n">
         <v>0.0001334978855629182</v>
       </c>
-      <c r="F375" s="2" t="n">
+      <c r="F375" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -7977,7 +7977,7 @@
       <c r="E376" t="n">
         <v>1.799057094022754e-06</v>
       </c>
-      <c r="F376" s="2" t="n">
+      <c r="F376" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -7997,7 +7997,7 @@
       <c r="E377" t="n">
         <v>-1.317366118396627e-07</v>
       </c>
-      <c r="F377" s="2" t="n">
+      <c r="F377" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -8017,7 +8017,7 @@
       <c r="E378" t="n">
         <v>-1.099681341326235e-07</v>
       </c>
-      <c r="F378" s="2" t="n">
+      <c r="F378" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -8037,7 +8037,7 @@
       <c r="E379" t="n">
         <v>2.357773488703392e-07</v>
       </c>
-      <c r="F379" s="2" t="n">
+      <c r="F379" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -8057,7 +8057,7 @@
       <c r="E380" t="n">
         <v>1.493375716724124e-05</v>
       </c>
-      <c r="F380" s="2" t="n">
+      <c r="F380" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -8077,7 +8077,7 @@
       <c r="E381" t="n">
         <v>0.0003097626901331015</v>
       </c>
-      <c r="F381" s="2" t="n">
+      <c r="F381" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -8097,7 +8097,7 @@
       <c r="E382" t="n">
         <v>0.0001647741489429569</v>
       </c>
-      <c r="F382" s="2" t="n">
+      <c r="F382" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -8117,7 +8117,7 @@
       <c r="E383" t="n">
         <v>9.322295016120074e-06</v>
       </c>
-      <c r="F383" s="2" t="n">
+      <c r="F383" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -8137,7 +8137,7 @@
       <c r="E384" t="n">
         <v>1.690431739002972e-05</v>
       </c>
-      <c r="F384" s="2" t="n">
+      <c r="F384" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -8157,7 +8157,7 @@
       <c r="E385" t="n">
         <v>-2.352602721439669e-05</v>
       </c>
-      <c r="F385" s="2" t="n">
+      <c r="F385" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -8177,7 +8177,7 @@
       <c r="E386" t="n">
         <v>-0.003710912033265726</v>
       </c>
-      <c r="F386" s="2" t="n">
+      <c r="F386" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -8197,7 +8197,7 @@
       <c r="E387" t="n">
         <v>-0.0004903920892688167</v>
       </c>
-      <c r="F387" s="2" t="n">
+      <c r="F387" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -8217,7 +8217,7 @@
       <c r="E388" t="n">
         <v>-0.003710912033265724</v>
       </c>
-      <c r="F388" s="2" t="n">
+      <c r="F388" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -8237,7 +8237,7 @@
       <c r="E389" t="n">
         <v>0.001374088060342331</v>
       </c>
-      <c r="F389" s="2" t="n">
+      <c r="F389" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -8257,7 +8257,7 @@
       <c r="E390" t="n">
         <v>7.702109771845746e-05</v>
       </c>
-      <c r="F390" s="2" t="n">
+      <c r="F390" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -8277,7 +8277,7 @@
       <c r="E391" t="n">
         <v>1.401792656866053e-05</v>
       </c>
-      <c r="F391" s="2" t="n">
+      <c r="F391" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -8297,7 +8297,7 @@
       <c r="E392" t="n">
         <v>-2.226575565520246e-07</v>
       </c>
-      <c r="F392" s="2" t="n">
+      <c r="F392" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -8317,7 +8317,7 @@
       <c r="E393" t="n">
         <v>-8.124618320775237e-08</v>
       </c>
-      <c r="F393" s="2" t="n">
+      <c r="F393" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -8337,7 +8337,7 @@
       <c r="E394" t="n">
         <v>-3.330962144551856e-06</v>
       </c>
-      <c r="F394" s="2" t="n">
+      <c r="F394" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -8357,7 +8357,7 @@
       <c r="E395" t="n">
         <v>-3.119198423121126e-05</v>
       </c>
-      <c r="F395" s="2" t="n">
+      <c r="F395" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -8377,7 +8377,7 @@
       <c r="E396" t="n">
         <v>0.0001132691368672017</v>
       </c>
-      <c r="F396" s="2" t="n">
+      <c r="F396" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -8397,7 +8397,7 @@
       <c r="E397" t="n">
         <v>4.21921576603805e-05</v>
       </c>
-      <c r="F397" s="2" t="n">
+      <c r="F397" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -8417,7 +8417,7 @@
       <c r="E398" t="n">
         <v>2.853178857184463e-05</v>
       </c>
-      <c r="F398" s="2" t="n">
+      <c r="F398" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -8437,7 +8437,7 @@
       <c r="E399" t="n">
         <v>-9.298437321751037e-05</v>
       </c>
-      <c r="F399" s="2" t="n">
+      <c r="F399" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -8457,7 +8457,7 @@
       <c r="E400" t="n">
         <v>2.012022207897281e-05</v>
       </c>
-      <c r="F400" s="2" t="n">
+      <c r="F400" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -8477,7 +8477,7 @@
       <c r="E401" t="n">
         <v>0.04309346712843985</v>
       </c>
-      <c r="F401" s="2" t="n">
+      <c r="F401" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -8497,7 +8497,7 @@
       <c r="E402" t="n">
         <v>-0.03634008302072622</v>
       </c>
-      <c r="F402" s="2" t="n">
+      <c r="F402" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -8517,7 +8517,7 @@
       <c r="E403" t="n">
         <v>0.04309346712843961</v>
       </c>
-      <c r="F403" s="2" t="n">
+      <c r="F403" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -8537,7 +8537,7 @@
       <c r="E404" t="n">
         <v>0.01571151253829269</v>
       </c>
-      <c r="F404" s="2" t="n">
+      <c r="F404" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -8557,7 +8557,7 @@
       <c r="E405" t="n">
         <v>0.009533374516245596</v>
       </c>
-      <c r="F405" s="2" t="n">
+      <c r="F405" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -8577,7 +8577,7 @@
       <c r="E406" t="n">
         <v>2.65479117820699e-05</v>
       </c>
-      <c r="F406" s="2" t="n">
+      <c r="F406" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -8597,7 +8597,7 @@
       <c r="E407" t="n">
         <v>-7.043091578074693e-08</v>
       </c>
-      <c r="F407" s="2" t="n">
+      <c r="F407" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -8617,7 +8617,7 @@
       <c r="E408" t="n">
         <v>-1.074154187249916e-07</v>
       </c>
-      <c r="F408" s="2" t="n">
+      <c r="F408" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
       <c r="E409" t="n">
         <v>1.444458858157158e-06</v>
       </c>
-      <c r="F409" s="2" t="n">
+      <c r="F409" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -8657,7 +8657,7 @@
       <c r="E410" t="n">
         <v>3.98029168752878e-05</v>
       </c>
-      <c r="F410" s="2" t="n">
+      <c r="F410" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -8677,7 +8677,7 @@
       <c r="E411" t="n">
         <v>0.0006112407955594704</v>
       </c>
-      <c r="F411" s="2" t="n">
+      <c r="F411" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -8697,7 +8697,7 @@
       <c r="E412" t="n">
         <v>0.0003489351452854184</v>
       </c>
-      <c r="F412" s="2" t="n">
+      <c r="F412" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -8717,7 +8717,7 @@
       <c r="E413" t="n">
         <v>1.366912609970924e-05</v>
       </c>
-      <c r="F413" s="2" t="n">
+      <c r="F413" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -8737,7 +8737,7 @@
       <c r="E414" t="n">
         <v>2.944837359237213e-05</v>
       </c>
-      <c r="F414" s="2" t="n">
+      <c r="F414" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -8757,7 +8757,7 @@
       <c r="E415" t="n">
         <v>0.01395068877560402</v>
       </c>
-      <c r="F415" s="2" t="n">
+      <c r="F415" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -8777,7 +8777,7 @@
       <c r="E416" t="n">
         <v>-7.741918865068684e-07</v>
       </c>
-      <c r="F416" s="2" t="n">
+      <c r="F416" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -8797,7 +8797,7 @@
       <c r="E417" t="n">
         <v>-1.421163416323249e-06</v>
       </c>
-      <c r="F417" s="2" t="n">
+      <c r="F417" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -8817,7 +8817,7 @@
       <c r="E418" t="n">
         <v>-0.0003227554899714855</v>
       </c>
-      <c r="F418" s="2" t="n">
+      <c r="F418" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -8837,7 +8837,7 @@
       <c r="E419" t="n">
         <v>2.860055121383428e-05</v>
       </c>
-      <c r="F419" s="2" t="n">
+      <c r="F419" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -8857,7 +8857,7 @@
       <c r="E420" t="n">
         <v>0.0004846076988056408</v>
       </c>
-      <c r="F420" s="2" t="n">
+      <c r="F420" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -8877,7 +8877,7 @@
       <c r="E421" t="n">
         <v>0.001212645213214508</v>
       </c>
-      <c r="F421" s="2" t="n">
+      <c r="F421" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -8897,7 +8897,7 @@
       <c r="E422" t="n">
         <v>0.000368622912757828</v>
       </c>
-      <c r="F422" s="2" t="n">
+      <c r="F422" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -8917,7 +8917,7 @@
       <c r="E423" t="n">
         <v>3.06455429576093e-05</v>
       </c>
-      <c r="F423" s="2" t="n">
+      <c r="F423" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -8937,7 +8937,7 @@
       <c r="E424" t="n">
         <v>0.0003114996587612145</v>
       </c>
-      <c r="F424" s="2" t="n">
+      <c r="F424" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -8957,7 +8957,7 @@
       <c r="E425" t="n">
         <v>0.0004463955141161007</v>
       </c>
-      <c r="F425" s="2" t="n">
+      <c r="F425" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -8977,7 +8977,2187 @@
       <c r="E426" t="n">
         <v>-9.266177938756956e-05</v>
       </c>
-      <c r="F426" s="2" t="n">
+      <c r="F426" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr"/>
+      <c r="B427" s="1" t="n">
+        <v>45778</v>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>all prior revisions</t>
+        </is>
+      </c>
+      <c r="D427" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E427" t="n">
+        <v>3.080399324711841e-07</v>
+      </c>
+      <c r="F427" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr"/>
+      <c r="B428" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>icc_fecomercio</t>
+        </is>
+      </c>
+      <c r="D428" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E428" t="n">
+        <v>-4.293780437073965e-08</v>
+      </c>
+      <c r="F428" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr"/>
+      <c r="B429" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>icea_fecomercio</t>
+        </is>
+      </c>
+      <c r="D429" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E429" t="n">
+        <v>8.545630516081242e-08</v>
+      </c>
+      <c r="F429" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr"/>
+      <c r="B430" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>ief_fecomercio</t>
+        </is>
+      </c>
+      <c r="D430" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E430" t="n">
+        <v>-7.630282832258344e-08</v>
+      </c>
+      <c r="F430" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr"/>
+      <c r="B431" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>igp10</t>
+        </is>
+      </c>
+      <c r="D431" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E431" t="n">
+        <v>1.183397154963098e-07</v>
+      </c>
+      <c r="F431" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr"/>
+      <c r="B432" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>igpm</t>
+        </is>
+      </c>
+      <c r="D432" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E432" t="n">
+        <v>-6.414488699167881e-07</v>
+      </c>
+      <c r="F432" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr"/>
+      <c r="B433" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>ipam</t>
+        </is>
+      </c>
+      <c r="D433" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E433" t="n">
+        <v>-4.052288825028671e-07</v>
+      </c>
+      <c r="F433" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr"/>
+      <c r="B434" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>ipc_fipe</t>
+        </is>
+      </c>
+      <c r="D434" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E434" t="n">
+        <v>7.977246902906276e-07</v>
+      </c>
+      <c r="F434" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr"/>
+      <c r="B435" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>ipca15</t>
+        </is>
+      </c>
+      <c r="D435" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E435" t="n">
+        <v>-4.41981654785581e-07</v>
+      </c>
+      <c r="F435" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr"/>
+      <c r="B436" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>icc_fecomercio</t>
+        </is>
+      </c>
+      <c r="D436" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E436" t="n">
+        <v>4.526382591827467e-09</v>
+      </c>
+      <c r="F436" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr"/>
+      <c r="B437" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>icea_fecomercio</t>
+        </is>
+      </c>
+      <c r="D437" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E437" t="n">
+        <v>-7.550418657950552e-09</v>
+      </c>
+      <c r="F437" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr"/>
+      <c r="B438" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>ief_fecomercio</t>
+        </is>
+      </c>
+      <c r="D438" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E438" t="n">
+        <v>1.544476090177551e-09</v>
+      </c>
+      <c r="F438" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr"/>
+      <c r="B439" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>igp10</t>
+        </is>
+      </c>
+      <c r="D439" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E439" t="n">
+        <v>-2.67071826596777e-08</v>
+      </c>
+      <c r="F439" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr"/>
+      <c r="B440" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>igpm</t>
+        </is>
+      </c>
+      <c r="D440" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E440" t="n">
+        <v>1.62160965016365e-08</v>
+      </c>
+      <c r="F440" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr"/>
+      <c r="B441" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>ipam</t>
+        </is>
+      </c>
+      <c r="D441" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E441" t="n">
+        <v>2.473842478802466e-09</v>
+      </c>
+      <c r="F441" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr"/>
+      <c r="B442" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>ipc_fipe</t>
+        </is>
+      </c>
+      <c r="D442" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E442" t="n">
+        <v>6.983904680348991e-08</v>
+      </c>
+      <c r="F442" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr"/>
+      <c r="B443" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>ipca15</t>
+        </is>
+      </c>
+      <c r="D443" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E443" t="n">
+        <v>-5.876530033939507e-08</v>
+      </c>
+      <c r="F443" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr"/>
+      <c r="B444" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>icc_fecomercio</t>
+        </is>
+      </c>
+      <c r="D444" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E444" t="n">
+        <v>1.390573204439922e-08</v>
+      </c>
+      <c r="F444" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr"/>
+      <c r="B445" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>icea_fecomercio</t>
+        </is>
+      </c>
+      <c r="D445" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E445" t="n">
+        <v>-3.491998548428055e-08</v>
+      </c>
+      <c r="F445" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr"/>
+      <c r="B446" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>ief_fecomercio</t>
+        </is>
+      </c>
+      <c r="D446" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E446" t="n">
+        <v>-5.662633645087397e-09</v>
+      </c>
+      <c r="F446" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr"/>
+      <c r="B447" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>igp10</t>
+        </is>
+      </c>
+      <c r="D447" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E447" t="n">
+        <v>-8.253223504676567e-08</v>
+      </c>
+      <c r="F447" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr"/>
+      <c r="B448" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>igpm</t>
+        </is>
+      </c>
+      <c r="D448" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E448" t="n">
+        <v>1.654596245256233e-08</v>
+      </c>
+      <c r="F448" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr"/>
+      <c r="B449" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>ipam</t>
+        </is>
+      </c>
+      <c r="D449" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E449" t="n">
+        <v>7.755980888237562e-09</v>
+      </c>
+      <c r="F449" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr"/>
+      <c r="B450" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>ipc_fipe</t>
+        </is>
+      </c>
+      <c r="D450" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E450" t="n">
+        <v>1.095389543745136e-07</v>
+      </c>
+      <c r="F450" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr"/>
+      <c r="B451" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>ipca15</t>
+        </is>
+      </c>
+      <c r="D451" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E451" t="n">
+        <v>-4.887229551666359e-08</v>
+      </c>
+      <c r="F451" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr"/>
+      <c r="B452" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>icc_fecomercio</t>
+        </is>
+      </c>
+      <c r="D452" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E452" t="n">
+        <v>-3.690663906697275e-09</v>
+      </c>
+      <c r="F452" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr"/>
+      <c r="B453" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>icea_fecomercio</t>
+        </is>
+      </c>
+      <c r="D453" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E453" t="n">
+        <v>-3.813755352306101e-08</v>
+      </c>
+      <c r="F453" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr"/>
+      <c r="B454" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>ief_fecomercio</t>
+        </is>
+      </c>
+      <c r="D454" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E454" t="n">
+        <v>-1.729640959957162e-08</v>
+      </c>
+      <c r="F454" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr"/>
+      <c r="B455" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>igp10</t>
+        </is>
+      </c>
+      <c r="D455" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E455" t="n">
+        <v>-5.1576366370461e-08</v>
+      </c>
+      <c r="F455" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr"/>
+      <c r="B456" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>igpm</t>
+        </is>
+      </c>
+      <c r="D456" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E456" t="n">
+        <v>2.951017165457155e-08</v>
+      </c>
+      <c r="F456" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr"/>
+      <c r="B457" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>ipam</t>
+        </is>
+      </c>
+      <c r="D457" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E457" t="n">
+        <v>1.246506063628394e-08</v>
+      </c>
+      <c r="F457" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr"/>
+      <c r="B458" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>ipc_fipe</t>
+        </is>
+      </c>
+      <c r="D458" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E458" t="n">
+        <v>1.748308402132644e-07</v>
+      </c>
+      <c r="F458" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr"/>
+      <c r="B459" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>ipca15</t>
+        </is>
+      </c>
+      <c r="D459" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E459" t="n">
+        <v>-7.421584662497928e-08</v>
+      </c>
+      <c r="F459" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr"/>
+      <c r="B460" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>icc_fecomercio</t>
+        </is>
+      </c>
+      <c r="D460" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E460" t="n">
+        <v>-2.345106445573731e-08</v>
+      </c>
+      <c r="F460" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr"/>
+      <c r="B461" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>icea_fecomercio</t>
+        </is>
+      </c>
+      <c r="D461" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E461" t="n">
+        <v>-5.471502422765532e-08</v>
+      </c>
+      <c r="F461" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr"/>
+      <c r="B462" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>ief_fecomercio</t>
+        </is>
+      </c>
+      <c r="D462" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E462" t="n">
+        <v>-1.038350540867043e-08</v>
+      </c>
+      <c r="F462" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr"/>
+      <c r="B463" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>igp10</t>
+        </is>
+      </c>
+      <c r="D463" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E463" t="n">
+        <v>-5.7711813243738e-08</v>
+      </c>
+      <c r="F463" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr"/>
+      <c r="B464" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>igpm</t>
+        </is>
+      </c>
+      <c r="D464" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E464" t="n">
+        <v>2.232084064810034e-08</v>
+      </c>
+      <c r="F464" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr"/>
+      <c r="B465" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>ipam</t>
+        </is>
+      </c>
+      <c r="D465" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E465" t="n">
+        <v>1.057309607321048e-08</v>
+      </c>
+      <c r="F465" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr"/>
+      <c r="B466" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>ipc_fipe</t>
+        </is>
+      </c>
+      <c r="D466" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E466" t="n">
+        <v>4.884304773171131e-08</v>
+      </c>
+      <c r="F466" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr"/>
+      <c r="B467" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>ipca15</t>
+        </is>
+      </c>
+      <c r="D467" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E467" t="n">
+        <v>8.309157404470481e-10</v>
+      </c>
+      <c r="F467" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr"/>
+      <c r="B468" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>icc_fecomercio</t>
+        </is>
+      </c>
+      <c r="D468" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E468" t="n">
+        <v>-3.873215121723031e-08</v>
+      </c>
+      <c r="F468" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr"/>
+      <c r="B469" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>icea_fecomercio</t>
+        </is>
+      </c>
+      <c r="D469" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E469" t="n">
+        <v>-7.748139495013588e-08</v>
+      </c>
+      <c r="F469" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr"/>
+      <c r="B470" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>ief_fecomercio</t>
+        </is>
+      </c>
+      <c r="D470" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E470" t="n">
+        <v>-5.407011809490032e-09</v>
+      </c>
+      <c r="F470" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr"/>
+      <c r="B471" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>igp10</t>
+        </is>
+      </c>
+      <c r="D471" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E471" t="n">
+        <v>-1.716444753949664e-08</v>
+      </c>
+      <c r="F471" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr"/>
+      <c r="B472" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>igpm</t>
+        </is>
+      </c>
+      <c r="D472" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E472" t="n">
+        <v>7.437237510641443e-08</v>
+      </c>
+      <c r="F472" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr"/>
+      <c r="B473" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>ipam</t>
+        </is>
+      </c>
+      <c r="D473" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E473" t="n">
+        <v>6.228570331281558e-08</v>
+      </c>
+      <c r="F473" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr"/>
+      <c r="B474" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>ipc_fipe</t>
+        </is>
+      </c>
+      <c r="D474" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E474" t="n">
+        <v>-3.912649435126538e-07</v>
+      </c>
+      <c r="F474" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr"/>
+      <c r="B475" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>ipca15</t>
+        </is>
+      </c>
+      <c r="D475" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E475" t="n">
+        <v>6.960121897033615e-08</v>
+      </c>
+      <c r="F475" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr"/>
+      <c r="B476" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>icc_fecomercio</t>
+        </is>
+      </c>
+      <c r="D476" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E476" t="n">
+        <v>-3.125327050942346e-08</v>
+      </c>
+      <c r="F476" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr"/>
+      <c r="B477" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>icea_fecomercio</t>
+        </is>
+      </c>
+      <c r="D477" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E477" t="n">
+        <v>-6.094390930968462e-08</v>
+      </c>
+      <c r="F477" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr"/>
+      <c r="B478" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>ief_fecomercio</t>
+        </is>
+      </c>
+      <c r="D478" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E478" t="n">
+        <v>3.536312647028299e-08</v>
+      </c>
+      <c r="F478" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr"/>
+      <c r="B479" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>igp10</t>
+        </is>
+      </c>
+      <c r="D479" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E479" t="n">
+        <v>3.228931359875883e-08</v>
+      </c>
+      <c r="F479" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr"/>
+      <c r="B480" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>igpm</t>
+        </is>
+      </c>
+      <c r="D480" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E480" t="n">
+        <v>1.049150029440693e-07</v>
+      </c>
+      <c r="F480" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr"/>
+      <c r="B481" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>ipam</t>
+        </is>
+      </c>
+      <c r="D481" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E481" t="n">
+        <v>8.357411217220693e-08</v>
+      </c>
+      <c r="F481" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr"/>
+      <c r="B482" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>ipc_fipe</t>
+        </is>
+      </c>
+      <c r="D482" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E482" t="n">
+        <v>-1.640064516341973e-07</v>
+      </c>
+      <c r="F482" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr"/>
+      <c r="B483" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>ipca15</t>
+        </is>
+      </c>
+      <c r="D483" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E483" t="n">
+        <v>3.168471028055077e-07</v>
+      </c>
+      <c r="F483" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr"/>
+      <c r="B484" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>icc_fecomercio</t>
+        </is>
+      </c>
+      <c r="D484" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E484" t="n">
+        <v>1.11195258156171e-07</v>
+      </c>
+      <c r="F484" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr"/>
+      <c r="B485" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>icea_fecomercio</t>
+        </is>
+      </c>
+      <c r="D485" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E485" t="n">
+        <v>-2.575192600586792e-08</v>
+      </c>
+      <c r="F485" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr"/>
+      <c r="B486" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>ief_fecomercio</t>
+        </is>
+      </c>
+      <c r="D486" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E486" t="n">
+        <v>2.805982168681365e-07</v>
+      </c>
+      <c r="F486" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr"/>
+      <c r="B487" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>igp10</t>
+        </is>
+      </c>
+      <c r="D487" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E487" t="n">
+        <v>6.11130544495851e-08</v>
+      </c>
+      <c r="F487" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr"/>
+      <c r="B488" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>igpm</t>
+        </is>
+      </c>
+      <c r="D488" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E488" t="n">
+        <v>1.782562286725336e-07</v>
+      </c>
+      <c r="F488" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr"/>
+      <c r="B489" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>ipam</t>
+        </is>
+      </c>
+      <c r="D489" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E489" t="n">
+        <v>1.34971519270629e-07</v>
+      </c>
+      <c r="F489" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr"/>
+      <c r="B490" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>ipc_fipe</t>
+        </is>
+      </c>
+      <c r="D490" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E490" t="n">
+        <v>-5.107544694769371e-07</v>
+      </c>
+      <c r="F490" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr"/>
+      <c r="B491" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>ipca15</t>
+        </is>
+      </c>
+      <c r="D491" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E491" t="n">
+        <v>2.580574337197524e-07</v>
+      </c>
+      <c r="F491" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr"/>
+      <c r="B492" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>icc_fecomercio</t>
+        </is>
+      </c>
+      <c r="D492" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E492" t="n">
+        <v>3.486753828493644e-07</v>
+      </c>
+      <c r="F492" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr"/>
+      <c r="B493" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>icea_fecomercio</t>
+        </is>
+      </c>
+      <c r="D493" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E493" t="n">
+        <v>-4.058206845529987e-08</v>
+      </c>
+      <c r="F493" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr"/>
+      <c r="B494" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>ief_fecomercio</t>
+        </is>
+      </c>
+      <c r="D494" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E494" t="n">
+        <v>6.074106589614992e-07</v>
+      </c>
+      <c r="F494" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr"/>
+      <c r="B495" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>igp10</t>
+        </is>
+      </c>
+      <c r="D495" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E495" t="n">
+        <v>1.103667367448352e-09</v>
+      </c>
+      <c r="F495" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr"/>
+      <c r="B496" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>igpm</t>
+        </is>
+      </c>
+      <c r="D496" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E496" t="n">
+        <v>2.483768284574687e-08</v>
+      </c>
+      <c r="F496" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr"/>
+      <c r="B497" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>ipam</t>
+        </is>
+      </c>
+      <c r="D497" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E497" t="n">
+        <v>1.622926852479553e-08</v>
+      </c>
+      <c r="F497" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr"/>
+      <c r="B498" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>ipc_fipe</t>
+        </is>
+      </c>
+      <c r="D498" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E498" t="n">
+        <v>-1.211403920979978e-06</v>
+      </c>
+      <c r="F498" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr"/>
+      <c r="B499" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>ipca15</t>
+        </is>
+      </c>
+      <c r="D499" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E499" t="n">
+        <v>1.364210110740208e-06</v>
+      </c>
+      <c r="F499" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr"/>
+      <c r="B500" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>icc_fecomercio</t>
+        </is>
+      </c>
+      <c r="D500" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E500" t="n">
+        <v>8.850894897054178e-07</v>
+      </c>
+      <c r="F500" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr"/>
+      <c r="B501" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>icea_fecomercio</t>
+        </is>
+      </c>
+      <c r="D501" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E501" t="n">
+        <v>1.987304731384238e-07</v>
+      </c>
+      <c r="F501" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr"/>
+      <c r="B502" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>ief_fecomercio</t>
+        </is>
+      </c>
+      <c r="D502" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E502" t="n">
+        <v>1.089565431646911e-06</v>
+      </c>
+      <c r="F502" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr"/>
+      <c r="B503" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>igp10</t>
+        </is>
+      </c>
+      <c r="D503" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E503" t="n">
+        <v>-1.845922734759358e-08</v>
+      </c>
+      <c r="F503" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr"/>
+      <c r="B504" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>igpm</t>
+        </is>
+      </c>
+      <c r="D504" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E504" t="n">
+        <v>-7.831918010595159e-07</v>
+      </c>
+      <c r="F504" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr"/>
+      <c r="B505" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>ipam</t>
+        </is>
+      </c>
+      <c r="D505" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E505" t="n">
+        <v>-5.441725568134334e-07</v>
+      </c>
+      <c r="F505" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr"/>
+      <c r="B506" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>ipc_fipe</t>
+        </is>
+      </c>
+      <c r="D506" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E506" t="n">
+        <v>-1.458298334970369e-06</v>
+      </c>
+      <c r="F506" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr"/>
+      <c r="B507" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>ipca15</t>
+        </is>
+      </c>
+      <c r="D507" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E507" t="n">
+        <v>8.455720906299109e-07</v>
+      </c>
+      <c r="F507" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr"/>
+      <c r="B508" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>icc_fecomercio</t>
+        </is>
+      </c>
+      <c r="D508" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E508" t="n">
+        <v>1.387507764408877e-06</v>
+      </c>
+      <c r="F508" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr"/>
+      <c r="B509" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>icea_fecomercio</t>
+        </is>
+      </c>
+      <c r="D509" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E509" t="n">
+        <v>2.214365443463274e-07</v>
+      </c>
+      <c r="F509" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr"/>
+      <c r="B510" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>ief_fecomercio</t>
+        </is>
+      </c>
+      <c r="D510" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E510" t="n">
+        <v>2.424160666852768e-06</v>
+      </c>
+      <c r="F510" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr"/>
+      <c r="B511" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>igp10</t>
+        </is>
+      </c>
+      <c r="D511" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E511" t="n">
+        <v>-1.932798254819803e-07</v>
+      </c>
+      <c r="F511" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr"/>
+      <c r="B512" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>igpm</t>
+        </is>
+      </c>
+      <c r="D512" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E512" t="n">
+        <v>-9.569497029341393e-07</v>
+      </c>
+      <c r="F512" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr"/>
+      <c r="B513" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>ipam</t>
+        </is>
+      </c>
+      <c r="D513" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E513" t="n">
+        <v>-3.77581844104991e-07</v>
+      </c>
+      <c r="F513" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr"/>
+      <c r="B514" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>ipc_fipe</t>
+        </is>
+      </c>
+      <c r="D514" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E514" t="n">
+        <v>-2.646791924961341e-06</v>
+      </c>
+      <c r="F514" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr"/>
+      <c r="B515" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>ipca15</t>
+        </is>
+      </c>
+      <c r="D515" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E515" t="n">
+        <v>-2.678852126459665e-06</v>
+      </c>
+      <c r="F515" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr"/>
+      <c r="B516" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>icc_fecomercio</t>
+        </is>
+      </c>
+      <c r="D516" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E516" t="n">
+        <v>-1.254185823893963e-05</v>
+      </c>
+      <c r="F516" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr"/>
+      <c r="B517" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>icea_fecomercio</t>
+        </is>
+      </c>
+      <c r="D517" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E517" t="n">
+        <v>-3.452924439647621e-06</v>
+      </c>
+      <c r="F517" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr"/>
+      <c r="B518" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>ief_fecomercio</t>
+        </is>
+      </c>
+      <c r="D518" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E518" t="n">
+        <v>-1.521943824156817e-05</v>
+      </c>
+      <c r="F518" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr"/>
+      <c r="B519" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>igp10</t>
+        </is>
+      </c>
+      <c r="D519" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E519" t="n">
+        <v>-5.850050357298003e-06</v>
+      </c>
+      <c r="F519" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr"/>
+      <c r="B520" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>igpm</t>
+        </is>
+      </c>
+      <c r="D520" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E520" t="n">
+        <v>3.107350906528596e-05</v>
+      </c>
+      <c r="F520" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr"/>
+      <c r="B521" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>ipam</t>
+        </is>
+      </c>
+      <c r="D521" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E521" t="n">
+        <v>2.3061305066898e-05</v>
+      </c>
+      <c r="F521" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr"/>
+      <c r="B522" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>ipc_fipe</t>
+        </is>
+      </c>
+      <c r="D522" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E522" t="n">
+        <v>-3.925957523312392e-06</v>
+      </c>
+      <c r="F522" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr"/>
+      <c r="B523" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>ipca15</t>
+        </is>
+      </c>
+      <c r="D523" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E523" t="n">
+        <v>1.122119603131102e-05</v>
+      </c>
+      <c r="F523" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr"/>
+      <c r="B524" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>fgv_nuci</t>
+        </is>
+      </c>
+      <c r="D524" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E524" t="n">
+        <v>0.01899132792957611</v>
+      </c>
+      <c r="F524" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr"/>
+      <c r="B525" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>icc_fecomercio</t>
+        </is>
+      </c>
+      <c r="D525" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E525" t="n">
+        <v>-0.0009516479421349262</v>
+      </c>
+      <c r="F525" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr"/>
+      <c r="B526" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>icea_fecomercio</t>
+        </is>
+      </c>
+      <c r="D526" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E526" t="n">
+        <v>-0.0001577230264613142</v>
+      </c>
+      <c r="F526" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr"/>
+      <c r="B527" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>ics_fgv</t>
+        </is>
+      </c>
+      <c r="D527" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E527" t="n">
+        <v>0.002103201277324499</v>
+      </c>
+      <c r="F527" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr"/>
+      <c r="B528" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>ief_fecomercio</t>
+        </is>
+      </c>
+      <c r="D528" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E528" t="n">
+        <v>-0.0008116241026366359</v>
+      </c>
+      <c r="F528" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr"/>
+      <c r="B529" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>ies_fgv</t>
+        </is>
+      </c>
+      <c r="D529" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E529" t="n">
+        <v>-0.0001257250987690297</v>
+      </c>
+      <c r="F529" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr"/>
+      <c r="B530" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>igp10</t>
+        </is>
+      </c>
+      <c r="D530" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E530" t="n">
+        <v>0.0004104855822765409</v>
+      </c>
+      <c r="F530" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr"/>
+      <c r="B531" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>igpm</t>
+        </is>
+      </c>
+      <c r="D531" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E531" t="n">
+        <v>0.0007594073484224079</v>
+      </c>
+      <c r="F531" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr"/>
+      <c r="B532" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>ipam</t>
+        </is>
+      </c>
+      <c r="D532" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E532" t="n">
+        <v>0.0006254102903339486</v>
+      </c>
+      <c r="F532" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr"/>
+      <c r="B533" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>ipc_fipe</t>
+        </is>
+      </c>
+      <c r="D533" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E533" t="n">
+        <v>0.0001810947310023466</v>
+      </c>
+      <c r="F533" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr"/>
+      <c r="B534" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>ipca15</t>
+        </is>
+      </c>
+      <c r="D534" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E534" t="n">
+        <v>7.995929517844551e-05</v>
+      </c>
+      <c r="F534" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr"/>
+      <c r="B535" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>isas_fgv</t>
+        </is>
+      </c>
+      <c r="D535" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E535" t="n">
+        <v>0.001991632406930498</v>
+      </c>
+      <c r="F535" s="2" t="n">
         <v>46209</v>
       </c>
     </row>

--- a/pib_nowcast/data/news_impacts.xlsx
+++ b/pib_nowcast/data/news_impacts.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F535"/>
+  <dimension ref="A1:F683"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8997,7 +8997,7 @@
       <c r="E427" t="n">
         <v>3.080399324711841e-07</v>
       </c>
-      <c r="F427" s="2" t="n">
+      <c r="F427" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -9017,7 +9017,7 @@
       <c r="E428" t="n">
         <v>-4.293780437073965e-08</v>
       </c>
-      <c r="F428" s="2" t="n">
+      <c r="F428" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -9037,7 +9037,7 @@
       <c r="E429" t="n">
         <v>8.545630516081242e-08</v>
       </c>
-      <c r="F429" s="2" t="n">
+      <c r="F429" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -9057,7 +9057,7 @@
       <c r="E430" t="n">
         <v>-7.630282832258344e-08</v>
       </c>
-      <c r="F430" s="2" t="n">
+      <c r="F430" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -9077,7 +9077,7 @@
       <c r="E431" t="n">
         <v>1.183397154963098e-07</v>
       </c>
-      <c r="F431" s="2" t="n">
+      <c r="F431" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -9097,7 +9097,7 @@
       <c r="E432" t="n">
         <v>-6.414488699167881e-07</v>
       </c>
-      <c r="F432" s="2" t="n">
+      <c r="F432" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -9117,7 +9117,7 @@
       <c r="E433" t="n">
         <v>-4.052288825028671e-07</v>
       </c>
-      <c r="F433" s="2" t="n">
+      <c r="F433" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -9137,7 +9137,7 @@
       <c r="E434" t="n">
         <v>7.977246902906276e-07</v>
       </c>
-      <c r="F434" s="2" t="n">
+      <c r="F434" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -9157,7 +9157,7 @@
       <c r="E435" t="n">
         <v>-4.41981654785581e-07</v>
       </c>
-      <c r="F435" s="2" t="n">
+      <c r="F435" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -9177,7 +9177,7 @@
       <c r="E436" t="n">
         <v>4.526382591827467e-09</v>
       </c>
-      <c r="F436" s="2" t="n">
+      <c r="F436" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -9197,7 +9197,7 @@
       <c r="E437" t="n">
         <v>-7.550418657950552e-09</v>
       </c>
-      <c r="F437" s="2" t="n">
+      <c r="F437" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -9217,7 +9217,7 @@
       <c r="E438" t="n">
         <v>1.544476090177551e-09</v>
       </c>
-      <c r="F438" s="2" t="n">
+      <c r="F438" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -9237,7 +9237,7 @@
       <c r="E439" t="n">
         <v>-2.67071826596777e-08</v>
       </c>
-      <c r="F439" s="2" t="n">
+      <c r="F439" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -9257,7 +9257,7 @@
       <c r="E440" t="n">
         <v>1.62160965016365e-08</v>
       </c>
-      <c r="F440" s="2" t="n">
+      <c r="F440" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -9277,7 +9277,7 @@
       <c r="E441" t="n">
         <v>2.473842478802466e-09</v>
       </c>
-      <c r="F441" s="2" t="n">
+      <c r="F441" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -9297,7 +9297,7 @@
       <c r="E442" t="n">
         <v>6.983904680348991e-08</v>
       </c>
-      <c r="F442" s="2" t="n">
+      <c r="F442" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -9317,7 +9317,7 @@
       <c r="E443" t="n">
         <v>-5.876530033939507e-08</v>
       </c>
-      <c r="F443" s="2" t="n">
+      <c r="F443" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -9337,7 +9337,7 @@
       <c r="E444" t="n">
         <v>1.390573204439922e-08</v>
       </c>
-      <c r="F444" s="2" t="n">
+      <c r="F444" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -9357,7 +9357,7 @@
       <c r="E445" t="n">
         <v>-3.491998548428055e-08</v>
       </c>
-      <c r="F445" s="2" t="n">
+      <c r="F445" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -9377,7 +9377,7 @@
       <c r="E446" t="n">
         <v>-5.662633645087397e-09</v>
       </c>
-      <c r="F446" s="2" t="n">
+      <c r="F446" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -9397,7 +9397,7 @@
       <c r="E447" t="n">
         <v>-8.253223504676567e-08</v>
       </c>
-      <c r="F447" s="2" t="n">
+      <c r="F447" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -9417,7 +9417,7 @@
       <c r="E448" t="n">
         <v>1.654596245256233e-08</v>
       </c>
-      <c r="F448" s="2" t="n">
+      <c r="F448" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -9437,7 +9437,7 @@
       <c r="E449" t="n">
         <v>7.755980888237562e-09</v>
       </c>
-      <c r="F449" s="2" t="n">
+      <c r="F449" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -9457,7 +9457,7 @@
       <c r="E450" t="n">
         <v>1.095389543745136e-07</v>
       </c>
-      <c r="F450" s="2" t="n">
+      <c r="F450" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -9477,7 +9477,7 @@
       <c r="E451" t="n">
         <v>-4.887229551666359e-08</v>
       </c>
-      <c r="F451" s="2" t="n">
+      <c r="F451" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -9497,7 +9497,7 @@
       <c r="E452" t="n">
         <v>-3.690663906697275e-09</v>
       </c>
-      <c r="F452" s="2" t="n">
+      <c r="F452" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -9517,7 +9517,7 @@
       <c r="E453" t="n">
         <v>-3.813755352306101e-08</v>
       </c>
-      <c r="F453" s="2" t="n">
+      <c r="F453" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -9537,7 +9537,7 @@
       <c r="E454" t="n">
         <v>-1.729640959957162e-08</v>
       </c>
-      <c r="F454" s="2" t="n">
+      <c r="F454" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -9557,7 +9557,7 @@
       <c r="E455" t="n">
         <v>-5.1576366370461e-08</v>
       </c>
-      <c r="F455" s="2" t="n">
+      <c r="F455" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -9577,7 +9577,7 @@
       <c r="E456" t="n">
         <v>2.951017165457155e-08</v>
       </c>
-      <c r="F456" s="2" t="n">
+      <c r="F456" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -9597,7 +9597,7 @@
       <c r="E457" t="n">
         <v>1.246506063628394e-08</v>
       </c>
-      <c r="F457" s="2" t="n">
+      <c r="F457" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       <c r="E458" t="n">
         <v>1.748308402132644e-07</v>
       </c>
-      <c r="F458" s="2" t="n">
+      <c r="F458" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -9637,7 +9637,7 @@
       <c r="E459" t="n">
         <v>-7.421584662497928e-08</v>
       </c>
-      <c r="F459" s="2" t="n">
+      <c r="F459" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -9657,7 +9657,7 @@
       <c r="E460" t="n">
         <v>-2.345106445573731e-08</v>
       </c>
-      <c r="F460" s="2" t="n">
+      <c r="F460" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -9677,7 +9677,7 @@
       <c r="E461" t="n">
         <v>-5.471502422765532e-08</v>
       </c>
-      <c r="F461" s="2" t="n">
+      <c r="F461" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -9697,7 +9697,7 @@
       <c r="E462" t="n">
         <v>-1.038350540867043e-08</v>
       </c>
-      <c r="F462" s="2" t="n">
+      <c r="F462" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -9717,7 +9717,7 @@
       <c r="E463" t="n">
         <v>-5.7711813243738e-08</v>
       </c>
-      <c r="F463" s="2" t="n">
+      <c r="F463" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -9737,7 +9737,7 @@
       <c r="E464" t="n">
         <v>2.232084064810034e-08</v>
       </c>
-      <c r="F464" s="2" t="n">
+      <c r="F464" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -9757,7 +9757,7 @@
       <c r="E465" t="n">
         <v>1.057309607321048e-08</v>
       </c>
-      <c r="F465" s="2" t="n">
+      <c r="F465" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -9777,7 +9777,7 @@
       <c r="E466" t="n">
         <v>4.884304773171131e-08</v>
       </c>
-      <c r="F466" s="2" t="n">
+      <c r="F466" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -9797,7 +9797,7 @@
       <c r="E467" t="n">
         <v>8.309157404470481e-10</v>
       </c>
-      <c r="F467" s="2" t="n">
+      <c r="F467" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -9817,7 +9817,7 @@
       <c r="E468" t="n">
         <v>-3.873215121723031e-08</v>
       </c>
-      <c r="F468" s="2" t="n">
+      <c r="F468" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -9837,7 +9837,7 @@
       <c r="E469" t="n">
         <v>-7.748139495013588e-08</v>
       </c>
-      <c r="F469" s="2" t="n">
+      <c r="F469" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -9857,7 +9857,7 @@
       <c r="E470" t="n">
         <v>-5.407011809490032e-09</v>
       </c>
-      <c r="F470" s="2" t="n">
+      <c r="F470" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -9877,7 +9877,7 @@
       <c r="E471" t="n">
         <v>-1.716444753949664e-08</v>
       </c>
-      <c r="F471" s="2" t="n">
+      <c r="F471" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -9897,7 +9897,7 @@
       <c r="E472" t="n">
         <v>7.437237510641443e-08</v>
       </c>
-      <c r="F472" s="2" t="n">
+      <c r="F472" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -9917,7 +9917,7 @@
       <c r="E473" t="n">
         <v>6.228570331281558e-08</v>
       </c>
-      <c r="F473" s="2" t="n">
+      <c r="F473" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -9937,7 +9937,7 @@
       <c r="E474" t="n">
         <v>-3.912649435126538e-07</v>
       </c>
-      <c r="F474" s="2" t="n">
+      <c r="F474" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -9957,7 +9957,7 @@
       <c r="E475" t="n">
         <v>6.960121897033615e-08</v>
       </c>
-      <c r="F475" s="2" t="n">
+      <c r="F475" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -9977,7 +9977,7 @@
       <c r="E476" t="n">
         <v>-3.125327050942346e-08</v>
       </c>
-      <c r="F476" s="2" t="n">
+      <c r="F476" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -9997,7 +9997,7 @@
       <c r="E477" t="n">
         <v>-6.094390930968462e-08</v>
       </c>
-      <c r="F477" s="2" t="n">
+      <c r="F477" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -10017,7 +10017,7 @@
       <c r="E478" t="n">
         <v>3.536312647028299e-08</v>
       </c>
-      <c r="F478" s="2" t="n">
+      <c r="F478" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -10037,7 +10037,7 @@
       <c r="E479" t="n">
         <v>3.228931359875883e-08</v>
       </c>
-      <c r="F479" s="2" t="n">
+      <c r="F479" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -10057,7 +10057,7 @@
       <c r="E480" t="n">
         <v>1.049150029440693e-07</v>
       </c>
-      <c r="F480" s="2" t="n">
+      <c r="F480" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -10077,7 +10077,7 @@
       <c r="E481" t="n">
         <v>8.357411217220693e-08</v>
       </c>
-      <c r="F481" s="2" t="n">
+      <c r="F481" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -10097,7 +10097,7 @@
       <c r="E482" t="n">
         <v>-1.640064516341973e-07</v>
       </c>
-      <c r="F482" s="2" t="n">
+      <c r="F482" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -10117,7 +10117,7 @@
       <c r="E483" t="n">
         <v>3.168471028055077e-07</v>
       </c>
-      <c r="F483" s="2" t="n">
+      <c r="F483" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -10137,7 +10137,7 @@
       <c r="E484" t="n">
         <v>1.11195258156171e-07</v>
       </c>
-      <c r="F484" s="2" t="n">
+      <c r="F484" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -10157,7 +10157,7 @@
       <c r="E485" t="n">
         <v>-2.575192600586792e-08</v>
       </c>
-      <c r="F485" s="2" t="n">
+      <c r="F485" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -10177,7 +10177,7 @@
       <c r="E486" t="n">
         <v>2.805982168681365e-07</v>
       </c>
-      <c r="F486" s="2" t="n">
+      <c r="F486" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -10197,7 +10197,7 @@
       <c r="E487" t="n">
         <v>6.11130544495851e-08</v>
       </c>
-      <c r="F487" s="2" t="n">
+      <c r="F487" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -10217,7 +10217,7 @@
       <c r="E488" t="n">
         <v>1.782562286725336e-07</v>
       </c>
-      <c r="F488" s="2" t="n">
+      <c r="F488" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -10237,7 +10237,7 @@
       <c r="E489" t="n">
         <v>1.34971519270629e-07</v>
       </c>
-      <c r="F489" s="2" t="n">
+      <c r="F489" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -10257,7 +10257,7 @@
       <c r="E490" t="n">
         <v>-5.107544694769371e-07</v>
       </c>
-      <c r="F490" s="2" t="n">
+      <c r="F490" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -10277,7 +10277,7 @@
       <c r="E491" t="n">
         <v>2.580574337197524e-07</v>
       </c>
-      <c r="F491" s="2" t="n">
+      <c r="F491" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -10297,7 +10297,7 @@
       <c r="E492" t="n">
         <v>3.486753828493644e-07</v>
       </c>
-      <c r="F492" s="2" t="n">
+      <c r="F492" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -10317,7 +10317,7 @@
       <c r="E493" t="n">
         <v>-4.058206845529987e-08</v>
       </c>
-      <c r="F493" s="2" t="n">
+      <c r="F493" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -10337,7 +10337,7 @@
       <c r="E494" t="n">
         <v>6.074106589614992e-07</v>
       </c>
-      <c r="F494" s="2" t="n">
+      <c r="F494" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -10357,7 +10357,7 @@
       <c r="E495" t="n">
         <v>1.103667367448352e-09</v>
       </c>
-      <c r="F495" s="2" t="n">
+      <c r="F495" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -10377,7 +10377,7 @@
       <c r="E496" t="n">
         <v>2.483768284574687e-08</v>
       </c>
-      <c r="F496" s="2" t="n">
+      <c r="F496" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -10397,7 +10397,7 @@
       <c r="E497" t="n">
         <v>1.622926852479553e-08</v>
       </c>
-      <c r="F497" s="2" t="n">
+      <c r="F497" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -10417,7 +10417,7 @@
       <c r="E498" t="n">
         <v>-1.211403920979978e-06</v>
       </c>
-      <c r="F498" s="2" t="n">
+      <c r="F498" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -10437,7 +10437,7 @@
       <c r="E499" t="n">
         <v>1.364210110740208e-06</v>
       </c>
-      <c r="F499" s="2" t="n">
+      <c r="F499" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -10457,7 +10457,7 @@
       <c r="E500" t="n">
         <v>8.850894897054178e-07</v>
       </c>
-      <c r="F500" s="2" t="n">
+      <c r="F500" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -10477,7 +10477,7 @@
       <c r="E501" t="n">
         <v>1.987304731384238e-07</v>
       </c>
-      <c r="F501" s="2" t="n">
+      <c r="F501" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -10497,7 +10497,7 @@
       <c r="E502" t="n">
         <v>1.089565431646911e-06</v>
       </c>
-      <c r="F502" s="2" t="n">
+      <c r="F502" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -10517,7 +10517,7 @@
       <c r="E503" t="n">
         <v>-1.845922734759358e-08</v>
       </c>
-      <c r="F503" s="2" t="n">
+      <c r="F503" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -10537,7 +10537,7 @@
       <c r="E504" t="n">
         <v>-7.831918010595159e-07</v>
       </c>
-      <c r="F504" s="2" t="n">
+      <c r="F504" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -10557,7 +10557,7 @@
       <c r="E505" t="n">
         <v>-5.441725568134334e-07</v>
       </c>
-      <c r="F505" s="2" t="n">
+      <c r="F505" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -10577,7 +10577,7 @@
       <c r="E506" t="n">
         <v>-1.458298334970369e-06</v>
       </c>
-      <c r="F506" s="2" t="n">
+      <c r="F506" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -10597,7 +10597,7 @@
       <c r="E507" t="n">
         <v>8.455720906299109e-07</v>
       </c>
-      <c r="F507" s="2" t="n">
+      <c r="F507" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -10617,7 +10617,7 @@
       <c r="E508" t="n">
         <v>1.387507764408877e-06</v>
       </c>
-      <c r="F508" s="2" t="n">
+      <c r="F508" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -10637,7 +10637,7 @@
       <c r="E509" t="n">
         <v>2.214365443463274e-07</v>
       </c>
-      <c r="F509" s="2" t="n">
+      <c r="F509" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -10657,7 +10657,7 @@
       <c r="E510" t="n">
         <v>2.424160666852768e-06</v>
       </c>
-      <c r="F510" s="2" t="n">
+      <c r="F510" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -10677,7 +10677,7 @@
       <c r="E511" t="n">
         <v>-1.932798254819803e-07</v>
       </c>
-      <c r="F511" s="2" t="n">
+      <c r="F511" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -10697,7 +10697,7 @@
       <c r="E512" t="n">
         <v>-9.569497029341393e-07</v>
       </c>
-      <c r="F512" s="2" t="n">
+      <c r="F512" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -10717,7 +10717,7 @@
       <c r="E513" t="n">
         <v>-3.77581844104991e-07</v>
       </c>
-      <c r="F513" s="2" t="n">
+      <c r="F513" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -10737,7 +10737,7 @@
       <c r="E514" t="n">
         <v>-2.646791924961341e-06</v>
       </c>
-      <c r="F514" s="2" t="n">
+      <c r="F514" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -10757,7 +10757,7 @@
       <c r="E515" t="n">
         <v>-2.678852126459665e-06</v>
       </c>
-      <c r="F515" s="2" t="n">
+      <c r="F515" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -10777,7 +10777,7 @@
       <c r="E516" t="n">
         <v>-1.254185823893963e-05</v>
       </c>
-      <c r="F516" s="2" t="n">
+      <c r="F516" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -10797,7 +10797,7 @@
       <c r="E517" t="n">
         <v>-3.452924439647621e-06</v>
       </c>
-      <c r="F517" s="2" t="n">
+      <c r="F517" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -10817,7 +10817,7 @@
       <c r="E518" t="n">
         <v>-1.521943824156817e-05</v>
       </c>
-      <c r="F518" s="2" t="n">
+      <c r="F518" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -10837,7 +10837,7 @@
       <c r="E519" t="n">
         <v>-5.850050357298003e-06</v>
       </c>
-      <c r="F519" s="2" t="n">
+      <c r="F519" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -10857,7 +10857,7 @@
       <c r="E520" t="n">
         <v>3.107350906528596e-05</v>
       </c>
-      <c r="F520" s="2" t="n">
+      <c r="F520" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -10877,7 +10877,7 @@
       <c r="E521" t="n">
         <v>2.3061305066898e-05</v>
       </c>
-      <c r="F521" s="2" t="n">
+      <c r="F521" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -10897,7 +10897,7 @@
       <c r="E522" t="n">
         <v>-3.925957523312392e-06</v>
       </c>
-      <c r="F522" s="2" t="n">
+      <c r="F522" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -10917,7 +10917,7 @@
       <c r="E523" t="n">
         <v>1.122119603131102e-05</v>
       </c>
-      <c r="F523" s="2" t="n">
+      <c r="F523" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -10937,7 +10937,7 @@
       <c r="E524" t="n">
         <v>0.01899132792957611</v>
       </c>
-      <c r="F524" s="2" t="n">
+      <c r="F524" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -10957,7 +10957,7 @@
       <c r="E525" t="n">
         <v>-0.0009516479421349262</v>
       </c>
-      <c r="F525" s="2" t="n">
+      <c r="F525" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -10977,7 +10977,7 @@
       <c r="E526" t="n">
         <v>-0.0001577230264613142</v>
       </c>
-      <c r="F526" s="2" t="n">
+      <c r="F526" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -10997,7 +10997,7 @@
       <c r="E527" t="n">
         <v>0.002103201277324499</v>
       </c>
-      <c r="F527" s="2" t="n">
+      <c r="F527" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -11017,7 +11017,7 @@
       <c r="E528" t="n">
         <v>-0.0008116241026366359</v>
       </c>
-      <c r="F528" s="2" t="n">
+      <c r="F528" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -11037,7 +11037,7 @@
       <c r="E529" t="n">
         <v>-0.0001257250987690297</v>
       </c>
-      <c r="F529" s="2" t="n">
+      <c r="F529" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -11057,7 +11057,7 @@
       <c r="E530" t="n">
         <v>0.0004104855822765409</v>
       </c>
-      <c r="F530" s="2" t="n">
+      <c r="F530" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -11077,7 +11077,7 @@
       <c r="E531" t="n">
         <v>0.0007594073484224079</v>
       </c>
-      <c r="F531" s="2" t="n">
+      <c r="F531" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -11097,7 +11097,7 @@
       <c r="E532" t="n">
         <v>0.0006254102903339486</v>
       </c>
-      <c r="F532" s="2" t="n">
+      <c r="F532" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -11117,7 +11117,7 @@
       <c r="E533" t="n">
         <v>0.0001810947310023466</v>
       </c>
-      <c r="F533" s="2" t="n">
+      <c r="F533" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -11137,7 +11137,7 @@
       <c r="E534" t="n">
         <v>7.995929517844551e-05</v>
       </c>
-      <c r="F534" s="2" t="n">
+      <c r="F534" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -11157,8 +11157,2968 @@
       <c r="E535" t="n">
         <v>0.001991632406930498</v>
       </c>
-      <c r="F535" s="2" t="n">
-        <v>46209</v>
+      <c r="F535" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr"/>
+      <c r="B536" s="1" t="n">
+        <v>45778</v>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>all prior revisions</t>
+        </is>
+      </c>
+      <c r="D536" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E536" t="n">
+        <v>7.98819364144928e-07</v>
+      </c>
+      <c r="F536" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr"/>
+      <c r="B537" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>icc_fecomercio</t>
+        </is>
+      </c>
+      <c r="D537" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E537" t="n">
+        <v>-4.293780437071264e-08</v>
+      </c>
+      <c r="F537" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr"/>
+      <c r="B538" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>icea_fecomercio</t>
+        </is>
+      </c>
+      <c r="D538" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E538" t="n">
+        <v>8.545630516073747e-08</v>
+      </c>
+      <c r="F538" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr"/>
+      <c r="B539" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>ief_fecomercio</t>
+        </is>
+      </c>
+      <c r="D539" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E539" t="n">
+        <v>-7.630282832253789e-08</v>
+      </c>
+      <c r="F539" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr"/>
+      <c r="B540" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>igp10</t>
+        </is>
+      </c>
+      <c r="D540" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E540" t="n">
+        <v>1.183397154962203e-07</v>
+      </c>
+      <c r="F540" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr"/>
+      <c r="B541" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>igpdi</t>
+        </is>
+      </c>
+      <c r="D541" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E541" t="n">
+        <v>-3.359260080329917e-07</v>
+      </c>
+      <c r="F541" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr"/>
+      <c r="B542" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>igpm</t>
+        </is>
+      </c>
+      <c r="D542" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E542" t="n">
+        <v>-6.414488699162901e-07</v>
+      </c>
+      <c r="F542" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr"/>
+      <c r="B543" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>incc</t>
+        </is>
+      </c>
+      <c r="D543" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E543" t="n">
+        <v>2.013238201231928e-07</v>
+      </c>
+      <c r="F543" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr"/>
+      <c r="B544" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>ipam</t>
+        </is>
+      </c>
+      <c r="D544" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E544" t="n">
+        <v>-4.052288825026222e-07</v>
+      </c>
+      <c r="F544" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr"/>
+      <c r="B545" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>ipc_fipe</t>
+        </is>
+      </c>
+      <c r="D545" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E545" t="n">
+        <v>7.977246902901275e-07</v>
+      </c>
+      <c r="F545" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr"/>
+      <c r="B546" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>ipca15</t>
+        </is>
+      </c>
+      <c r="D546" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E546" t="n">
+        <v>-4.419816547851638e-07</v>
+      </c>
+      <c r="F546" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr"/>
+      <c r="B547" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>ipcbr</t>
+        </is>
+      </c>
+      <c r="D547" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E547" t="n">
+        <v>-1.304836823952298e-07</v>
+      </c>
+      <c r="F547" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr"/>
+      <c r="B548" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>icc_fecomercio</t>
+        </is>
+      </c>
+      <c r="D548" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E548" t="n">
+        <v>4.526382591828891e-09</v>
+      </c>
+      <c r="F548" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr"/>
+      <c r="B549" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>icea_fecomercio</t>
+        </is>
+      </c>
+      <c r="D549" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E549" t="n">
+        <v>-7.55041865794639e-09</v>
+      </c>
+      <c r="F549" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr"/>
+      <c r="B550" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>ief_fecomercio</t>
+        </is>
+      </c>
+      <c r="D550" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E550" t="n">
+        <v>1.544476090176226e-09</v>
+      </c>
+      <c r="F550" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr"/>
+      <c r="B551" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>igp10</t>
+        </is>
+      </c>
+      <c r="D551" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E551" t="n">
+        <v>-2.670718265966824e-08</v>
+      </c>
+      <c r="F551" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr"/>
+      <c r="B552" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>igpdi</t>
+        </is>
+      </c>
+      <c r="D552" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E552" t="n">
+        <v>-6.475654040558864e-08</v>
+      </c>
+      <c r="F552" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr"/>
+      <c r="B553" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>igpm</t>
+        </is>
+      </c>
+      <c r="D553" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E553" t="n">
+        <v>1.62160965016311e-08</v>
+      </c>
+      <c r="F553" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr"/>
+      <c r="B554" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>incc</t>
+        </is>
+      </c>
+      <c r="D554" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E554" t="n">
+        <v>-7.355201946626783e-08</v>
+      </c>
+      <c r="F554" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr"/>
+      <c r="B555" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>ipam</t>
+        </is>
+      </c>
+      <c r="D555" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E555" t="n">
+        <v>2.473842478800401e-09</v>
+      </c>
+      <c r="F555" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr"/>
+      <c r="B556" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>ipc_fipe</t>
+        </is>
+      </c>
+      <c r="D556" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E556" t="n">
+        <v>6.983904680344467e-08</v>
+      </c>
+      <c r="F556" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr"/>
+      <c r="B557" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>ipca15</t>
+        </is>
+      </c>
+      <c r="D557" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E557" t="n">
+        <v>-5.876530033934545e-08</v>
+      </c>
+      <c r="F557" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr"/>
+      <c r="B558" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>ipcbr</t>
+        </is>
+      </c>
+      <c r="D558" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E558" t="n">
+        <v>-7.187012855351878e-09</v>
+      </c>
+      <c r="F558" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr"/>
+      <c r="B559" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>icc_fecomercio</t>
+        </is>
+      </c>
+      <c r="D559" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E559" t="n">
+        <v>1.390573204436751e-08</v>
+      </c>
+      <c r="F559" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr"/>
+      <c r="B560" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>icea_fecomercio</t>
+        </is>
+      </c>
+      <c r="D560" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E560" t="n">
+        <v>-3.491998548425237e-08</v>
+      </c>
+      <c r="F560" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr"/>
+      <c r="B561" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>ief_fecomercio</t>
+        </is>
+      </c>
+      <c r="D561" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E561" t="n">
+        <v>-5.662633645081213e-09</v>
+      </c>
+      <c r="F561" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr"/>
+      <c r="B562" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>igp10</t>
+        </is>
+      </c>
+      <c r="D562" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E562" t="n">
+        <v>-8.253223504672338e-08</v>
+      </c>
+      <c r="F562" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr"/>
+      <c r="B563" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>igpdi</t>
+        </is>
+      </c>
+      <c r="D563" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E563" t="n">
+        <v>-6.7338830391686e-08</v>
+      </c>
+      <c r="F563" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr"/>
+      <c r="B564" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>igpm</t>
+        </is>
+      </c>
+      <c r="D564" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E564" t="n">
+        <v>1.654596245255201e-08</v>
+      </c>
+      <c r="F564" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr"/>
+      <c r="B565" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>incc</t>
+        </is>
+      </c>
+      <c r="D565" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E565" t="n">
+        <v>-3.082045627510374e-07</v>
+      </c>
+      <c r="F565" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr"/>
+      <c r="B566" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>ipam</t>
+        </is>
+      </c>
+      <c r="D566" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E566" t="n">
+        <v>7.755980888235525e-09</v>
+      </c>
+      <c r="F566" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr"/>
+      <c r="B567" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>ipc_fipe</t>
+        </is>
+      </c>
+      <c r="D567" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E567" t="n">
+        <v>1.095389543744474e-07</v>
+      </c>
+      <c r="F567" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr"/>
+      <c r="B568" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>ipca15</t>
+        </is>
+      </c>
+      <c r="D568" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E568" t="n">
+        <v>-4.887229551662134e-08</v>
+      </c>
+      <c r="F568" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr"/>
+      <c r="B569" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>ipcbr</t>
+        </is>
+      </c>
+      <c r="D569" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E569" t="n">
+        <v>1.17095317553796e-09</v>
+      </c>
+      <c r="F569" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr"/>
+      <c r="B570" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>icc_fecomercio</t>
+        </is>
+      </c>
+      <c r="D570" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E570" t="n">
+        <v>-3.690663906721827e-09</v>
+      </c>
+      <c r="F570" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr"/>
+      <c r="B571" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>icea_fecomercio</t>
+        </is>
+      </c>
+      <c r="D571" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E571" t="n">
+        <v>-3.813755352308124e-08</v>
+      </c>
+      <c r="F571" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr"/>
+      <c r="B572" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>ief_fecomercio</t>
+        </is>
+      </c>
+      <c r="D572" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E572" t="n">
+        <v>-1.729640959961324e-08</v>
+      </c>
+      <c r="F572" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr"/>
+      <c r="B573" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>igp10</t>
+        </is>
+      </c>
+      <c r="D573" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E573" t="n">
+        <v>-5.157636637043248e-08</v>
+      </c>
+      <c r="F573" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr"/>
+      <c r="B574" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>igpdi</t>
+        </is>
+      </c>
+      <c r="D574" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E574" t="n">
+        <v>-1.50325343090218e-08</v>
+      </c>
+      <c r="F574" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr"/>
+      <c r="B575" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>igpm</t>
+        </is>
+      </c>
+      <c r="D575" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E575" t="n">
+        <v>2.951017165454774e-08</v>
+      </c>
+      <c r="F575" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr"/>
+      <c r="B576" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>incc</t>
+        </is>
+      </c>
+      <c r="D576" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E576" t="n">
+        <v>-2.572954825211388e-07</v>
+      </c>
+      <c r="F576" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr"/>
+      <c r="B577" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>ipam</t>
+        </is>
+      </c>
+      <c r="D577" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E577" t="n">
+        <v>1.246506063626314e-08</v>
+      </c>
+      <c r="F577" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr"/>
+      <c r="B578" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>ipc_fipe</t>
+        </is>
+      </c>
+      <c r="D578" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E578" t="n">
+        <v>1.748308402131451e-07</v>
+      </c>
+      <c r="F578" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr"/>
+      <c r="B579" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>ipca15</t>
+        </is>
+      </c>
+      <c r="D579" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E579" t="n">
+        <v>-7.421584662490442e-08</v>
+      </c>
+      <c r="F579" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr"/>
+      <c r="B580" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>ipcbr</t>
+        </is>
+      </c>
+      <c r="D580" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E580" t="n">
+        <v>6.369032680291947e-09</v>
+      </c>
+      <c r="F580" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr"/>
+      <c r="B581" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>icc_fecomercio</t>
+        </is>
+      </c>
+      <c r="D581" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E581" t="n">
+        <v>-2.345106445574658e-08</v>
+      </c>
+      <c r="F581" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr"/>
+      <c r="B582" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>icea_fecomercio</t>
+        </is>
+      </c>
+      <c r="D582" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E582" t="n">
+        <v>-5.47150242276734e-08</v>
+      </c>
+      <c r="F582" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr"/>
+      <c r="B583" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>ief_fecomercio</t>
+        </is>
+      </c>
+      <c r="D583" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E583" t="n">
+        <v>-1.038350540867797e-08</v>
+      </c>
+      <c r="F583" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr"/>
+      <c r="B584" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>igp10</t>
+        </is>
+      </c>
+      <c r="D584" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E584" t="n">
+        <v>-5.771181324366949e-08</v>
+      </c>
+      <c r="F584" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr"/>
+      <c r="B585" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>igpdi</t>
+        </is>
+      </c>
+      <c r="D585" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E585" t="n">
+        <v>1.909876041709092e-08</v>
+      </c>
+      <c r="F585" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr"/>
+      <c r="B586" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>igpm</t>
+        </is>
+      </c>
+      <c r="D586" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E586" t="n">
+        <v>2.23208406480748e-08</v>
+      </c>
+      <c r="F586" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr"/>
+      <c r="B587" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>incc</t>
+        </is>
+      </c>
+      <c r="D587" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E587" t="n">
+        <v>-1.984719721293012e-07</v>
+      </c>
+      <c r="F587" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr"/>
+      <c r="B588" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>ipam</t>
+        </is>
+      </c>
+      <c r="D588" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E588" t="n">
+        <v>1.057309607320894e-08</v>
+      </c>
+      <c r="F588" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr"/>
+      <c r="B589" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>ipc_fipe</t>
+        </is>
+      </c>
+      <c r="D589" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E589" t="n">
+        <v>4.884304773168595e-08</v>
+      </c>
+      <c r="F589" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr"/>
+      <c r="B590" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>ipca15</t>
+        </is>
+      </c>
+      <c r="D590" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E590" t="n">
+        <v>8.309157404461912e-10</v>
+      </c>
+      <c r="F590" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr"/>
+      <c r="B591" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>ipcbr</t>
+        </is>
+      </c>
+      <c r="D591" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E591" t="n">
+        <v>3.275803444540192e-09</v>
+      </c>
+      <c r="F591" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr"/>
+      <c r="B592" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>icc_fecomercio</t>
+        </is>
+      </c>
+      <c r="D592" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E592" t="n">
+        <v>-3.873215121722428e-08</v>
+      </c>
+      <c r="F592" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr"/>
+      <c r="B593" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>icea_fecomercio</t>
+        </is>
+      </c>
+      <c r="D593" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E593" t="n">
+        <v>-7.748139495010337e-08</v>
+      </c>
+      <c r="F593" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr"/>
+      <c r="B594" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>ief_fecomercio</t>
+        </is>
+      </c>
+      <c r="D594" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E594" t="n">
+        <v>-5.407011809487698e-09</v>
+      </c>
+      <c r="F594" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr"/>
+      <c r="B595" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>igp10</t>
+        </is>
+      </c>
+      <c r="D595" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E595" t="n">
+        <v>-1.716444753948955e-08</v>
+      </c>
+      <c r="F595" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr"/>
+      <c r="B596" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>igpdi</t>
+        </is>
+      </c>
+      <c r="D596" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E596" t="n">
+        <v>1.322330949895569e-07</v>
+      </c>
+      <c r="F596" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr"/>
+      <c r="B597" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>igpm</t>
+        </is>
+      </c>
+      <c r="D597" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E597" t="n">
+        <v>7.437237510637705e-08</v>
+      </c>
+      <c r="F597" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr"/>
+      <c r="B598" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>incc</t>
+        </is>
+      </c>
+      <c r="D598" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E598" t="n">
+        <v>-1.465285461477367e-07</v>
+      </c>
+      <c r="F598" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr"/>
+      <c r="B599" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>ipam</t>
+        </is>
+      </c>
+      <c r="D599" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E599" t="n">
+        <v>6.22857033126969e-08</v>
+      </c>
+      <c r="F599" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr"/>
+      <c r="B600" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>ipc_fipe</t>
+        </is>
+      </c>
+      <c r="D600" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E600" t="n">
+        <v>-3.91264943512455e-07</v>
+      </c>
+      <c r="F600" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr"/>
+      <c r="B601" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>ipca15</t>
+        </is>
+      </c>
+      <c r="D601" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E601" t="n">
+        <v>6.960121897027208e-08</v>
+      </c>
+      <c r="F601" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr"/>
+      <c r="B602" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>ipcbr</t>
+        </is>
+      </c>
+      <c r="D602" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E602" t="n">
+        <v>1.339025967747242e-08</v>
+      </c>
+      <c r="F602" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr"/>
+      <c r="B603" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>icc_fecomercio</t>
+        </is>
+      </c>
+      <c r="D603" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E603" t="n">
+        <v>-3.125327050938829e-08</v>
+      </c>
+      <c r="F603" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr"/>
+      <c r="B604" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>icea_fecomercio</t>
+        </is>
+      </c>
+      <c r="D604" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E604" t="n">
+        <v>-6.094390930961535e-08</v>
+      </c>
+      <c r="F604" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr"/>
+      <c r="B605" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>ief_fecomercio</t>
+        </is>
+      </c>
+      <c r="D605" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E605" t="n">
+        <v>3.536312647023959e-08</v>
+      </c>
+      <c r="F605" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr"/>
+      <c r="B606" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>igp10</t>
+        </is>
+      </c>
+      <c r="D606" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E606" t="n">
+        <v>3.228931359874574e-08</v>
+      </c>
+      <c r="F606" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr"/>
+      <c r="B607" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>igpdi</t>
+        </is>
+      </c>
+      <c r="D607" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E607" t="n">
+        <v>2.176949544943953e-07</v>
+      </c>
+      <c r="F607" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr"/>
+      <c r="B608" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>igpm</t>
+        </is>
+      </c>
+      <c r="D608" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E608" t="n">
+        <v>1.049150029440349e-07</v>
+      </c>
+      <c r="F608" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr"/>
+      <c r="B609" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>incc</t>
+        </is>
+      </c>
+      <c r="D609" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E609" t="n">
+        <v>-9.742237951378327e-09</v>
+      </c>
+      <c r="F609" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr"/>
+      <c r="B610" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>ipam</t>
+        </is>
+      </c>
+      <c r="D610" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E610" t="n">
+        <v>8.357411217242249e-08</v>
+      </c>
+      <c r="F610" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr"/>
+      <c r="B611" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>ipc_fipe</t>
+        </is>
+      </c>
+      <c r="D611" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E611" t="n">
+        <v>-1.640064516341276e-07</v>
+      </c>
+      <c r="F611" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr"/>
+      <c r="B612" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>ipca15</t>
+        </is>
+      </c>
+      <c r="D612" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E612" t="n">
+        <v>3.16847102805251e-07</v>
+      </c>
+      <c r="F612" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr"/>
+      <c r="B613" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>ipcbr</t>
+        </is>
+      </c>
+      <c r="D613" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E613" t="n">
+        <v>5.5270650876953e-08</v>
+      </c>
+      <c r="F613" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr"/>
+      <c r="B614" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>icc_fecomercio</t>
+        </is>
+      </c>
+      <c r="D614" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E614" t="n">
+        <v>1.111952581560798e-07</v>
+      </c>
+      <c r="F614" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr"/>
+      <c r="B615" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>icea_fecomercio</t>
+        </is>
+      </c>
+      <c r="D615" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E615" t="n">
+        <v>-2.575192600584808e-08</v>
+      </c>
+      <c r="F615" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr"/>
+      <c r="B616" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>ief_fecomercio</t>
+        </is>
+      </c>
+      <c r="D616" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E616" t="n">
+        <v>2.805982168679181e-07</v>
+      </c>
+      <c r="F616" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr"/>
+      <c r="B617" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>igp10</t>
+        </is>
+      </c>
+      <c r="D617" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E617" t="n">
+        <v>6.111305444962169e-08</v>
+      </c>
+      <c r="F617" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr"/>
+      <c r="B618" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>igpdi</t>
+        </is>
+      </c>
+      <c r="D618" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E618" t="n">
+        <v>3.094880154463584e-07</v>
+      </c>
+      <c r="F618" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr"/>
+      <c r="B619" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>igpm</t>
+        </is>
+      </c>
+      <c r="D619" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E619" t="n">
+        <v>1.782562286729674e-07</v>
+      </c>
+      <c r="F619" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr"/>
+      <c r="B620" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>incc</t>
+        </is>
+      </c>
+      <c r="D620" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E620" t="n">
+        <v>1.82104503534578e-07</v>
+      </c>
+      <c r="F620" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr"/>
+      <c r="B621" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>ipam</t>
+        </is>
+      </c>
+      <c r="D621" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E621" t="n">
+        <v>1.349715192704798e-07</v>
+      </c>
+      <c r="F621" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr"/>
+      <c r="B622" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>ipc_fipe</t>
+        </is>
+      </c>
+      <c r="D622" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E622" t="n">
+        <v>-5.107544694767119e-07</v>
+      </c>
+      <c r="F622" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr"/>
+      <c r="B623" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>ipca15</t>
+        </is>
+      </c>
+      <c r="D623" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E623" t="n">
+        <v>2.580574337195764e-07</v>
+      </c>
+      <c r="F623" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr"/>
+      <c r="B624" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>ipcbr</t>
+        </is>
+      </c>
+      <c r="D624" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E624" t="n">
+        <v>7.759524353142549e-08</v>
+      </c>
+      <c r="F624" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr"/>
+      <c r="B625" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>icc_fecomercio</t>
+        </is>
+      </c>
+      <c r="D625" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E625" t="n">
+        <v>3.486753828494398e-07</v>
+      </c>
+      <c r="F625" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr"/>
+      <c r="B626" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>icea_fecomercio</t>
+        </is>
+      </c>
+      <c r="D626" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E626" t="n">
+        <v>-4.058206845530338e-08</v>
+      </c>
+      <c r="F626" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr"/>
+      <c r="B627" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>ief_fecomercio</t>
+        </is>
+      </c>
+      <c r="D627" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E627" t="n">
+        <v>6.074106589615748e-07</v>
+      </c>
+      <c r="F627" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr"/>
+      <c r="B628" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>igp10</t>
+        </is>
+      </c>
+      <c r="D628" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E628" t="n">
+        <v>1.103667367445988e-09</v>
+      </c>
+      <c r="F628" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr"/>
+      <c r="B629" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>igpdi</t>
+        </is>
+      </c>
+      <c r="D629" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E629" t="n">
+        <v>3.800568972239605e-08</v>
+      </c>
+      <c r="F629" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr"/>
+      <c r="B630" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>igpm</t>
+        </is>
+      </c>
+      <c r="D630" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E630" t="n">
+        <v>2.483768284525599e-08</v>
+      </c>
+      <c r="F630" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr"/>
+      <c r="B631" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>incc</t>
+        </is>
+      </c>
+      <c r="D631" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E631" t="n">
+        <v>3.887626949696322e-07</v>
+      </c>
+      <c r="F631" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr"/>
+      <c r="B632" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>ipam</t>
+        </is>
+      </c>
+      <c r="D632" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E632" t="n">
+        <v>1.622926852466443e-08</v>
+      </c>
+      <c r="F632" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr"/>
+      <c r="B633" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>ipc_fipe</t>
+        </is>
+      </c>
+      <c r="D633" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E633" t="n">
+        <v>-1.211403920979414e-06</v>
+      </c>
+      <c r="F633" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr"/>
+      <c r="B634" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>ipca15</t>
+        </is>
+      </c>
+      <c r="D634" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E634" t="n">
+        <v>1.364210110738776e-06</v>
+      </c>
+      <c r="F634" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr"/>
+      <c r="B635" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>ipcbr</t>
+        </is>
+      </c>
+      <c r="D635" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E635" t="n">
+        <v>2.130139828538096e-07</v>
+      </c>
+      <c r="F635" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr"/>
+      <c r="B636" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>icc_fecomercio</t>
+        </is>
+      </c>
+      <c r="D636" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E636" t="n">
+        <v>8.850894897059163e-07</v>
+      </c>
+      <c r="F636" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr"/>
+      <c r="B637" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>icea_fecomercio</t>
+        </is>
+      </c>
+      <c r="D637" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E637" t="n">
+        <v>1.987304731385118e-07</v>
+      </c>
+      <c r="F637" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr"/>
+      <c r="B638" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>ief_fecomercio</t>
+        </is>
+      </c>
+      <c r="D638" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E638" t="n">
+        <v>1.089565431647479e-06</v>
+      </c>
+      <c r="F638" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr"/>
+      <c r="B639" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>igp10</t>
+        </is>
+      </c>
+      <c r="D639" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E639" t="n">
+        <v>-1.845922734772898e-08</v>
+      </c>
+      <c r="F639" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr"/>
+      <c r="B640" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>igpdi</t>
+        </is>
+      </c>
+      <c r="D640" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E640" t="n">
+        <v>8.71886401130988e-07</v>
+      </c>
+      <c r="F640" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr"/>
+      <c r="B641" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>igpm</t>
+        </is>
+      </c>
+      <c r="D641" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E641" t="n">
+        <v>-7.83191801060636e-07</v>
+      </c>
+      <c r="F641" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr"/>
+      <c r="B642" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>incc</t>
+        </is>
+      </c>
+      <c r="D642" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E642" t="n">
+        <v>4.875452408728762e-07</v>
+      </c>
+      <c r="F642" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr"/>
+      <c r="B643" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>ipam</t>
+        </is>
+      </c>
+      <c r="D643" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E643" t="n">
+        <v>-5.441725568148302e-07</v>
+      </c>
+      <c r="F643" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr"/>
+      <c r="B644" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>ipc_fipe</t>
+        </is>
+      </c>
+      <c r="D644" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E644" t="n">
+        <v>-1.458298334969669e-06</v>
+      </c>
+      <c r="F644" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr"/>
+      <c r="B645" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>ipca15</t>
+        </is>
+      </c>
+      <c r="D645" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E645" t="n">
+        <v>8.455720906284331e-07</v>
+      </c>
+      <c r="F645" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr"/>
+      <c r="B646" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>ipcbr</t>
+        </is>
+      </c>
+      <c r="D646" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E646" t="n">
+        <v>3.985896192184019e-07</v>
+      </c>
+      <c r="F646" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr"/>
+      <c r="B647" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>icc_fecomercio</t>
+        </is>
+      </c>
+      <c r="D647" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E647" t="n">
+        <v>1.387507764409721e-06</v>
+      </c>
+      <c r="F647" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr"/>
+      <c r="B648" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>icea_fecomercio</t>
+        </is>
+      </c>
+      <c r="D648" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E648" t="n">
+        <v>2.214365443464186e-07</v>
+      </c>
+      <c r="F648" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr"/>
+      <c r="B649" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>ief_fecomercio</t>
+        </is>
+      </c>
+      <c r="D649" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E649" t="n">
+        <v>2.424160666854079e-06</v>
+      </c>
+      <c r="F649" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr"/>
+      <c r="B650" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>igp10</t>
+        </is>
+      </c>
+      <c r="D650" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E650" t="n">
+        <v>-1.932798254821169e-07</v>
+      </c>
+      <c r="F650" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr"/>
+      <c r="B651" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>igpdi</t>
+        </is>
+      </c>
+      <c r="D651" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E651" t="n">
+        <v>2.118839586304651e-06</v>
+      </c>
+      <c r="F651" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr"/>
+      <c r="B652" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>igpm</t>
+        </is>
+      </c>
+      <c r="D652" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E652" t="n">
+        <v>-9.569497029346147e-07</v>
+      </c>
+      <c r="F652" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr"/>
+      <c r="B653" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>incc</t>
+        </is>
+      </c>
+      <c r="D653" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E653" t="n">
+        <v>3.128577251776614e-07</v>
+      </c>
+      <c r="F653" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr"/>
+      <c r="B654" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>ipam</t>
+        </is>
+      </c>
+      <c r="D654" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E654" t="n">
+        <v>-3.775818441050819e-07</v>
+      </c>
+      <c r="F654" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr"/>
+      <c r="B655" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>ipc_fipe</t>
+        </is>
+      </c>
+      <c r="D655" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E655" t="n">
+        <v>-2.646791924960496e-06</v>
+      </c>
+      <c r="F655" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr"/>
+      <c r="B656" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>ipca15</t>
+        </is>
+      </c>
+      <c r="D656" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E656" t="n">
+        <v>-2.678852126456998e-06</v>
+      </c>
+      <c r="F656" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr"/>
+      <c r="B657" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>ipcbr</t>
+        </is>
+      </c>
+      <c r="D657" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E657" t="n">
+        <v>-1.95767822718043e-08</v>
+      </c>
+      <c r="F657" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr"/>
+      <c r="B658" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>icc_fecomercio</t>
+        </is>
+      </c>
+      <c r="D658" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E658" t="n">
+        <v>-1.254185823893938e-05</v>
+      </c>
+      <c r="F658" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr"/>
+      <c r="B659" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>icea_fecomercio</t>
+        </is>
+      </c>
+      <c r="D659" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E659" t="n">
+        <v>-3.45292443964759e-06</v>
+      </c>
+      <c r="F659" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr"/>
+      <c r="B660" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>ief_fecomercio</t>
+        </is>
+      </c>
+      <c r="D660" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E660" t="n">
+        <v>-1.52194382415683e-05</v>
+      </c>
+      <c r="F660" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr"/>
+      <c r="B661" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>igp10</t>
+        </is>
+      </c>
+      <c r="D661" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E661" t="n">
+        <v>-5.850050357297738e-06</v>
+      </c>
+      <c r="F661" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr"/>
+      <c r="B662" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>igpdi</t>
+        </is>
+      </c>
+      <c r="D662" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E662" t="n">
+        <v>8.346929508284692e-05</v>
+      </c>
+      <c r="F662" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr"/>
+      <c r="B663" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>igpm</t>
+        </is>
+      </c>
+      <c r="D663" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E663" t="n">
+        <v>3.10735090652846e-05</v>
+      </c>
+      <c r="F663" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr"/>
+      <c r="B664" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>incc</t>
+        </is>
+      </c>
+      <c r="D664" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E664" t="n">
+        <v>6.83211155505446e-06</v>
+      </c>
+      <c r="F664" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr"/>
+      <c r="B665" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>ipam</t>
+        </is>
+      </c>
+      <c r="D665" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E665" t="n">
+        <v>2.306130506689642e-05</v>
+      </c>
+      <c r="F665" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr"/>
+      <c r="B666" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>ipc_fipe</t>
+        </is>
+      </c>
+      <c r="D666" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E666" t="n">
+        <v>-3.925957523311686e-06</v>
+      </c>
+      <c r="F666" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr"/>
+      <c r="B667" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>ipca15</t>
+        </is>
+      </c>
+      <c r="D667" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E667" t="n">
+        <v>1.122119603130818e-05</v>
+      </c>
+      <c r="F667" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr"/>
+      <c r="B668" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>ipcbr</t>
+        </is>
+      </c>
+      <c r="D668" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E668" t="n">
+        <v>-9.415318167331627e-08</v>
+      </c>
+      <c r="F668" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr"/>
+      <c r="B669" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>fgv_nuci</t>
+        </is>
+      </c>
+      <c r="D669" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E669" t="n">
+        <v>0.01893126005117361</v>
+      </c>
+      <c r="F669" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr"/>
+      <c r="B670" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>icc_fecomercio</t>
+        </is>
+      </c>
+      <c r="D670" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E670" t="n">
+        <v>-0.0009353589919405733</v>
+      </c>
+      <c r="F670" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr"/>
+      <c r="B671" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>icea_fecomercio</t>
+        </is>
+      </c>
+      <c r="D671" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E671" t="n">
+        <v>-0.0001548123064984771</v>
+      </c>
+      <c r="F671" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr"/>
+      <c r="B672" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>ics_fgv</t>
+        </is>
+      </c>
+      <c r="D672" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E672" t="n">
+        <v>0.002068830578486529</v>
+      </c>
+      <c r="F672" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr"/>
+      <c r="B673" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>ief_fecomercio</t>
+        </is>
+      </c>
+      <c r="D673" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E673" t="n">
+        <v>-0.0007972815566123205</v>
+      </c>
+      <c r="F673" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr"/>
+      <c r="B674" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>ies_fgv</t>
+        </is>
+      </c>
+      <c r="D674" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E674" t="n">
+        <v>-0.0001258781556493125</v>
+      </c>
+      <c r="F674" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr"/>
+      <c r="B675" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>igp10</t>
+        </is>
+      </c>
+      <c r="D675" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E675" t="n">
+        <v>0.000332003176168411</v>
+      </c>
+      <c r="F675" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr"/>
+      <c r="B676" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>igpdi</t>
+        </is>
+      </c>
+      <c r="D676" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E676" t="n">
+        <v>0.0001863876319144707</v>
+      </c>
+      <c r="F676" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr"/>
+      <c r="B677" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>igpm</t>
+        </is>
+      </c>
+      <c r="D677" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E677" t="n">
+        <v>0.0006061196088752263</v>
+      </c>
+      <c r="F677" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr"/>
+      <c r="B678" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>incc</t>
+        </is>
+      </c>
+      <c r="D678" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E678" t="n">
+        <v>0.000629458258882743</v>
+      </c>
+      <c r="F678" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr"/>
+      <c r="B679" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>ipam</t>
+        </is>
+      </c>
+      <c r="D679" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E679" t="n">
+        <v>0.0004890552037101052</v>
+      </c>
+      <c r="F679" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr"/>
+      <c r="B680" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>ipc_fipe</t>
+        </is>
+      </c>
+      <c r="D680" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E680" t="n">
+        <v>5.327260063251168e-05</v>
+      </c>
+      <c r="F680" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr"/>
+      <c r="B681" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>ipca15</t>
+        </is>
+      </c>
+      <c r="D681" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E681" t="n">
+        <v>5.977736909610429e-05</v>
+      </c>
+      <c r="F681" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr"/>
+      <c r="B682" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>ipcbr</t>
+        </is>
+      </c>
+      <c r="D682" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E682" t="n">
+        <v>4.982882064727492e-05</v>
+      </c>
+      <c r="F682" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr"/>
+      <c r="B683" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>isas_fgv</t>
+        </is>
+      </c>
+      <c r="D683" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E683" t="n">
+        <v>0.001952280825646123</v>
+      </c>
+      <c r="F683" s="2" t="n">
+        <v>46211</v>
       </c>
     </row>
   </sheetData>

--- a/pib_nowcast/data/news_impacts.xlsx
+++ b/pib_nowcast/data/news_impacts.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1453"/>
+  <dimension ref="A1:F1491"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28997,7 +28997,7 @@
       <c r="E1427" t="n">
         <v>-8.051771222268495e-07</v>
       </c>
-      <c r="F1427" s="2" t="n">
+      <c r="F1427" s="1" t="n">
         <v>46217</v>
       </c>
     </row>
@@ -29017,7 +29017,7 @@
       <c r="E1428" t="n">
         <v>1.884430877710319e-06</v>
       </c>
-      <c r="F1428" s="2" t="n">
+      <c r="F1428" s="1" t="n">
         <v>46217</v>
       </c>
     </row>
@@ -29037,7 +29037,7 @@
       <c r="E1429" t="n">
         <v>4.153267275885883e-06</v>
       </c>
-      <c r="F1429" s="2" t="n">
+      <c r="F1429" s="1" t="n">
         <v>46217</v>
       </c>
     </row>
@@ -29057,7 +29057,7 @@
       <c r="E1430" t="n">
         <v>-1.160736078490229e-08</v>
       </c>
-      <c r="F1430" s="2" t="n">
+      <c r="F1430" s="1" t="n">
         <v>46217</v>
       </c>
     </row>
@@ -29077,7 +29077,7 @@
       <c r="E1431" t="n">
         <v>-5.669187366074513e-09</v>
       </c>
-      <c r="F1431" s="2" t="n">
+      <c r="F1431" s="1" t="n">
         <v>46217</v>
       </c>
     </row>
@@ -29097,7 +29097,7 @@
       <c r="E1432" t="n">
         <v>-4.717657837464598e-07</v>
       </c>
-      <c r="F1432" s="2" t="n">
+      <c r="F1432" s="1" t="n">
         <v>46217</v>
       </c>
     </row>
@@ -29117,7 +29117,7 @@
       <c r="E1433" t="n">
         <v>-7.384553455012511e-07</v>
       </c>
-      <c r="F1433" s="2" t="n">
+      <c r="F1433" s="1" t="n">
         <v>46217</v>
       </c>
     </row>
@@ -29137,7 +29137,7 @@
       <c r="E1434" t="n">
         <v>-6.599217909453931e-07</v>
       </c>
-      <c r="F1434" s="2" t="n">
+      <c r="F1434" s="1" t="n">
         <v>46217</v>
       </c>
     </row>
@@ -29157,7 +29157,7 @@
       <c r="E1435" t="n">
         <v>-8.414211376174013e-07</v>
       </c>
-      <c r="F1435" s="2" t="n">
+      <c r="F1435" s="1" t="n">
         <v>46217</v>
       </c>
     </row>
@@ -29177,7 +29177,7 @@
       <c r="E1436" t="n">
         <v>6.478979859471019e-08</v>
       </c>
-      <c r="F1436" s="2" t="n">
+      <c r="F1436" s="1" t="n">
         <v>46217</v>
       </c>
     </row>
@@ -29197,7 +29197,7 @@
       <c r="E1437" t="n">
         <v>1.158141114129981e-07</v>
       </c>
-      <c r="F1437" s="2" t="n">
+      <c r="F1437" s="1" t="n">
         <v>46217</v>
       </c>
     </row>
@@ -29217,7 +29217,7 @@
       <c r="E1438" t="n">
         <v>-1.105120331107403e-07</v>
       </c>
-      <c r="F1438" s="2" t="n">
+      <c r="F1438" s="1" t="n">
         <v>46217</v>
       </c>
     </row>
@@ -29237,7 +29237,7 @@
       <c r="E1439" t="n">
         <v>-4.902310380447639e-09</v>
       </c>
-      <c r="F1439" s="2" t="n">
+      <c r="F1439" s="1" t="n">
         <v>46217</v>
       </c>
     </row>
@@ -29257,7 +29257,7 @@
       <c r="E1440" t="n">
         <v>-1.150675445237932e-06</v>
       </c>
-      <c r="F1440" s="2" t="n">
+      <c r="F1440" s="1" t="n">
         <v>46217</v>
       </c>
     </row>
@@ -29277,7 +29277,7 @@
       <c r="E1441" t="n">
         <v>-3.399527403416085e-06</v>
       </c>
-      <c r="F1441" s="2" t="n">
+      <c r="F1441" s="1" t="n">
         <v>46217</v>
       </c>
     </row>
@@ -29297,7 +29297,7 @@
       <c r="E1442" t="n">
         <v>-5.202183374591961e-07</v>
       </c>
-      <c r="F1442" s="2" t="n">
+      <c r="F1442" s="1" t="n">
         <v>46217</v>
       </c>
     </row>
@@ -29317,7 +29317,7 @@
       <c r="E1443" t="n">
         <v>-1.124436659325238e-06</v>
       </c>
-      <c r="F1443" s="2" t="n">
+      <c r="F1443" s="1" t="n">
         <v>46217</v>
       </c>
     </row>
@@ -29337,7 +29337,7 @@
       <c r="E1444" t="n">
         <v>1.497975240054872e-06</v>
       </c>
-      <c r="F1444" s="2" t="n">
+      <c r="F1444" s="1" t="n">
         <v>46217</v>
       </c>
     </row>
@@ -29357,7 +29357,7 @@
       <c r="E1445" t="n">
         <v>3.340331491466267e-06</v>
       </c>
-      <c r="F1445" s="2" t="n">
+      <c r="F1445" s="1" t="n">
         <v>46217</v>
       </c>
     </row>
@@ -29377,7 +29377,7 @@
       <c r="E1446" t="n">
         <v>5.255421735438866e-06</v>
       </c>
-      <c r="F1446" s="2" t="n">
+      <c r="F1446" s="1" t="n">
         <v>46217</v>
       </c>
     </row>
@@ -29397,7 +29397,7 @@
       <c r="E1447" t="n">
         <v>2.760293543739292e-06</v>
       </c>
-      <c r="F1447" s="2" t="n">
+      <c r="F1447" s="1" t="n">
         <v>46217</v>
       </c>
     </row>
@@ -29417,7 +29417,7 @@
       <c r="E1448" t="n">
         <v>-2.304142945796337e-07</v>
       </c>
-      <c r="F1448" s="2" t="n">
+      <c r="F1448" s="1" t="n">
         <v>46217</v>
       </c>
     </row>
@@ -29437,7 +29437,7 @@
       <c r="E1449" t="n">
         <v>-1.700375609635689e-05</v>
       </c>
-      <c r="F1449" s="2" t="n">
+      <c r="F1449" s="1" t="n">
         <v>46217</v>
       </c>
     </row>
@@ -29457,7 +29457,7 @@
       <c r="E1450" t="n">
         <v>4.673316653570576e-06</v>
       </c>
-      <c r="F1450" s="2" t="n">
+      <c r="F1450" s="1" t="n">
         <v>46217</v>
       </c>
     </row>
@@ -29477,7 +29477,7 @@
       <c r="E1451" t="n">
         <v>5.449360908101761e-05</v>
       </c>
-      <c r="F1451" s="2" t="n">
+      <c r="F1451" s="1" t="n">
         <v>46217</v>
       </c>
     </row>
@@ -29497,7 +29497,7 @@
       <c r="E1452" t="n">
         <v>4.570714986718283e-05</v>
       </c>
-      <c r="F1452" s="2" t="n">
+      <c r="F1452" s="1" t="n">
         <v>46217</v>
       </c>
     </row>
@@ -29517,8 +29517,768 @@
       <c r="E1453" t="n">
         <v>0.000181785091013791</v>
       </c>
-      <c r="F1453" s="2" t="n">
+      <c r="F1453" s="1" t="n">
         <v>46217</v>
+      </c>
+    </row>
+    <row r="1454">
+      <c r="A1454" t="inlineStr"/>
+      <c r="B1454" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C1454" t="inlineStr">
+        <is>
+          <t>all prior revisions</t>
+        </is>
+      </c>
+      <c r="D1454" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1454" t="n">
+        <v>-9.786307453749011e-07</v>
+      </c>
+      <c r="F1454" s="2" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1455">
+      <c r="A1455" t="inlineStr"/>
+      <c r="B1455" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C1455" t="inlineStr">
+        <is>
+          <t>abras</t>
+        </is>
+      </c>
+      <c r="D1455" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1455" t="n">
+        <v>-4.643050563367927e-07</v>
+      </c>
+      <c r="F1455" s="2" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1456">
+      <c r="A1456" t="inlineStr"/>
+      <c r="B1456" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C1456" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1456" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1456" t="n">
+        <v>2.166297245841953e-06</v>
+      </c>
+      <c r="F1456" s="2" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1457">
+      <c r="A1457" t="inlineStr"/>
+      <c r="B1457" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C1457" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1457" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1457" t="n">
+        <v>6.090334463304047e-06</v>
+      </c>
+      <c r="F1457" s="2" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1458">
+      <c r="A1458" t="inlineStr"/>
+      <c r="B1458" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C1458" t="inlineStr">
+        <is>
+          <t>abras</t>
+        </is>
+      </c>
+      <c r="D1458" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1458" t="n">
+        <v>1.089752598243485e-08</v>
+      </c>
+      <c r="F1458" s="2" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1459">
+      <c r="A1459" t="inlineStr"/>
+      <c r="B1459" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C1459" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1459" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1459" t="n">
+        <v>-1.587679995335668e-08</v>
+      </c>
+      <c r="F1459" s="2" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1460">
+      <c r="A1460" t="inlineStr"/>
+      <c r="B1460" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C1460" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1460" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1460" t="n">
+        <v>-3.409175663751516e-08</v>
+      </c>
+      <c r="F1460" s="2" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1461">
+      <c r="A1461" t="inlineStr"/>
+      <c r="B1461" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C1461" t="inlineStr">
+        <is>
+          <t>abras</t>
+        </is>
+      </c>
+      <c r="D1461" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1461" t="n">
+        <v>5.16884739774179e-08</v>
+      </c>
+      <c r="F1461" s="2" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1462">
+      <c r="A1462" t="inlineStr"/>
+      <c r="B1462" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C1462" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1462" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1462" t="n">
+        <v>-5.576905459104573e-07</v>
+      </c>
+      <c r="F1462" s="2" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1463">
+      <c r="A1463" t="inlineStr"/>
+      <c r="B1463" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C1463" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1463" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1463" t="n">
+        <v>-1.264060076015918e-06</v>
+      </c>
+      <c r="F1463" s="2" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1464">
+      <c r="A1464" t="inlineStr"/>
+      <c r="B1464" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C1464" t="inlineStr">
+        <is>
+          <t>abras</t>
+        </is>
+      </c>
+      <c r="D1464" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1464" t="n">
+        <v>1.905463660247267e-07</v>
+      </c>
+      <c r="F1464" s="2" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1465">
+      <c r="A1465" t="inlineStr"/>
+      <c r="B1465" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C1465" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1465" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1465" t="n">
+        <v>-7.694284092892581e-07</v>
+      </c>
+      <c r="F1465" s="2" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1466">
+      <c r="A1466" t="inlineStr"/>
+      <c r="B1466" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C1466" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1466" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1466" t="n">
+        <v>-1.448457538695752e-06</v>
+      </c>
+      <c r="F1466" s="2" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1467">
+      <c r="A1467" t="inlineStr"/>
+      <c r="B1467" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C1467" t="inlineStr">
+        <is>
+          <t>abras</t>
+        </is>
+      </c>
+      <c r="D1467" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1467" t="n">
+        <v>3.175879782997984e-07</v>
+      </c>
+      <c r="F1467" s="2" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1468">
+      <c r="A1468" t="inlineStr"/>
+      <c r="B1468" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C1468" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1468" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1468" t="n">
+        <v>8.538606666306967e-08</v>
+      </c>
+      <c r="F1468" s="2" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1469">
+      <c r="A1469" t="inlineStr"/>
+      <c r="B1469" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C1469" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1469" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1469" t="n">
+        <v>1.410610943956866e-07</v>
+      </c>
+      <c r="F1469" s="2" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1470">
+      <c r="A1470" t="inlineStr"/>
+      <c r="B1470" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C1470" t="inlineStr">
+        <is>
+          <t>abras</t>
+        </is>
+      </c>
+      <c r="D1470" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1470" t="n">
+        <v>1.94478376839643e-06</v>
+      </c>
+      <c r="F1470" s="2" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1471">
+      <c r="A1471" t="inlineStr"/>
+      <c r="B1471" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C1471" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1471" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1471" t="n">
+        <v>-1.326082580014748e-07</v>
+      </c>
+      <c r="F1471" s="2" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1472">
+      <c r="A1472" t="inlineStr"/>
+      <c r="B1472" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C1472" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1472" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1472" t="n">
+        <v>-7.326873255555712e-09</v>
+      </c>
+      <c r="F1472" s="2" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1473">
+      <c r="A1473" t="inlineStr"/>
+      <c r="B1473" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C1473" t="inlineStr">
+        <is>
+          <t>abras</t>
+        </is>
+      </c>
+      <c r="D1473" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1473" t="n">
+        <v>3.274550326780346e-06</v>
+      </c>
+      <c r="F1473" s="2" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1474">
+      <c r="A1474" t="inlineStr"/>
+      <c r="B1474" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C1474" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1474" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1474" t="n">
+        <v>-1.359722111741666e-06</v>
+      </c>
+      <c r="F1474" s="2" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1475">
+      <c r="A1475" t="inlineStr"/>
+      <c r="B1475" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C1475" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1475" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1475" t="n">
+        <v>-5.396939133600158e-06</v>
+      </c>
+      <c r="F1475" s="2" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1476">
+      <c r="A1476" t="inlineStr"/>
+      <c r="B1476" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C1476" t="inlineStr">
+        <is>
+          <t>abras</t>
+        </is>
+      </c>
+      <c r="D1476" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1476" t="n">
+        <v>-2.344523628828648e-08</v>
+      </c>
+      <c r="F1476" s="2" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1477">
+      <c r="A1477" t="inlineStr"/>
+      <c r="B1477" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C1477" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1477" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1477" t="n">
+        <v>-4.811249641314511e-07</v>
+      </c>
+      <c r="F1477" s="2" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1478">
+      <c r="A1478" t="inlineStr"/>
+      <c r="B1478" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C1478" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1478" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1478" t="n">
+        <v>-1.660095572095659e-06</v>
+      </c>
+      <c r="F1478" s="2" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1479">
+      <c r="A1479" t="inlineStr"/>
+      <c r="B1479" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C1479" t="inlineStr">
+        <is>
+          <t>abras</t>
+        </is>
+      </c>
+      <c r="D1479" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1479" t="n">
+        <v>1.34528974488232e-06</v>
+      </c>
+      <c r="F1479" s="2" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1480">
+      <c r="A1480" t="inlineStr"/>
+      <c r="B1480" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C1480" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1480" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1480" t="n">
+        <v>2.096795130260158e-06</v>
+      </c>
+      <c r="F1480" s="2" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1481">
+      <c r="A1481" t="inlineStr"/>
+      <c r="B1481" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C1481" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1481" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1481" t="n">
+        <v>5.251364439226888e-06</v>
+      </c>
+      <c r="F1481" s="2" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1482">
+      <c r="A1482" t="inlineStr"/>
+      <c r="B1482" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C1482" t="inlineStr">
+        <is>
+          <t>abras</t>
+        </is>
+      </c>
+      <c r="D1482" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1482" t="n">
+        <v>4.054701956137024e-05</v>
+      </c>
+      <c r="F1482" s="2" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1483">
+      <c r="A1483" t="inlineStr"/>
+      <c r="B1483" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C1483" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1483" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1483" t="n">
+        <v>2.939374008019273e-07</v>
+      </c>
+      <c r="F1483" s="2" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1484">
+      <c r="A1484" t="inlineStr"/>
+      <c r="B1484" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C1484" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1484" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1484" t="n">
+        <v>-2.696154510232201e-07</v>
+      </c>
+      <c r="F1484" s="2" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1485">
+      <c r="A1485" t="inlineStr"/>
+      <c r="B1485" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C1485" t="inlineStr">
+        <is>
+          <t>abras</t>
+        </is>
+      </c>
+      <c r="D1485" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1485" t="n">
+        <v>-0.003690569824990196</v>
+      </c>
+      <c r="F1485" s="2" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1486">
+      <c r="A1486" t="inlineStr"/>
+      <c r="B1486" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C1486" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1486" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1486" t="n">
+        <v>-1.140261170751256e-06</v>
+      </c>
+      <c r="F1486" s="2" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1487">
+      <c r="A1487" t="inlineStr"/>
+      <c r="B1487" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C1487" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1487" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1487" t="n">
+        <v>-8.419149605881594e-06</v>
+      </c>
+      <c r="F1487" s="2" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1488">
+      <c r="A1488" t="inlineStr"/>
+      <c r="B1488" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C1488" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1488" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1488" t="n">
+        <v>2.642644986857226e-05</v>
+      </c>
+      <c r="F1488" s="2" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1489">
+      <c r="A1489" t="inlineStr"/>
+      <c r="B1489" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C1489" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1489" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1489" t="n">
+        <v>7.201420833716409e-05</v>
+      </c>
+      <c r="F1489" s="2" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1490">
+      <c r="A1490" t="inlineStr"/>
+      <c r="B1490" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="C1490" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1490" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1490" t="n">
+        <v>3.083344407047495e-05</v>
+      </c>
+      <c r="F1490" s="2" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1491">
+      <c r="A1491" t="inlineStr"/>
+      <c r="B1491" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="C1491" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1491" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1491" t="n">
+        <v>0.0001151693110182952</v>
+      </c>
+      <c r="F1491" s="2" t="n">
+        <v>46218</v>
       </c>
     </row>
   </sheetData>

--- a/pib_nowcast/data/news_impacts.xlsx
+++ b/pib_nowcast/data/news_impacts.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1491"/>
+  <dimension ref="A1:F1572"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29537,7 +29537,7 @@
       <c r="E1454" t="n">
         <v>-9.786307453749011e-07</v>
       </c>
-      <c r="F1454" s="2" t="n">
+      <c r="F1454" s="1" t="n">
         <v>46218</v>
       </c>
     </row>
@@ -29557,7 +29557,7 @@
       <c r="E1455" t="n">
         <v>-4.643050563367927e-07</v>
       </c>
-      <c r="F1455" s="2" t="n">
+      <c r="F1455" s="1" t="n">
         <v>46218</v>
       </c>
     </row>
@@ -29577,7 +29577,7 @@
       <c r="E1456" t="n">
         <v>2.166297245841953e-06</v>
       </c>
-      <c r="F1456" s="2" t="n">
+      <c r="F1456" s="1" t="n">
         <v>46218</v>
       </c>
     </row>
@@ -29597,7 +29597,7 @@
       <c r="E1457" t="n">
         <v>6.090334463304047e-06</v>
       </c>
-      <c r="F1457" s="2" t="n">
+      <c r="F1457" s="1" t="n">
         <v>46218</v>
       </c>
     </row>
@@ -29617,7 +29617,7 @@
       <c r="E1458" t="n">
         <v>1.089752598243485e-08</v>
       </c>
-      <c r="F1458" s="2" t="n">
+      <c r="F1458" s="1" t="n">
         <v>46218</v>
       </c>
     </row>
@@ -29637,7 +29637,7 @@
       <c r="E1459" t="n">
         <v>-1.587679995335668e-08</v>
       </c>
-      <c r="F1459" s="2" t="n">
+      <c r="F1459" s="1" t="n">
         <v>46218</v>
       </c>
     </row>
@@ -29657,7 +29657,7 @@
       <c r="E1460" t="n">
         <v>-3.409175663751516e-08</v>
       </c>
-      <c r="F1460" s="2" t="n">
+      <c r="F1460" s="1" t="n">
         <v>46218</v>
       </c>
     </row>
@@ -29677,7 +29677,7 @@
       <c r="E1461" t="n">
         <v>5.16884739774179e-08</v>
       </c>
-      <c r="F1461" s="2" t="n">
+      <c r="F1461" s="1" t="n">
         <v>46218</v>
       </c>
     </row>
@@ -29697,7 +29697,7 @@
       <c r="E1462" t="n">
         <v>-5.576905459104573e-07</v>
       </c>
-      <c r="F1462" s="2" t="n">
+      <c r="F1462" s="1" t="n">
         <v>46218</v>
       </c>
     </row>
@@ -29717,7 +29717,7 @@
       <c r="E1463" t="n">
         <v>-1.264060076015918e-06</v>
       </c>
-      <c r="F1463" s="2" t="n">
+      <c r="F1463" s="1" t="n">
         <v>46218</v>
       </c>
     </row>
@@ -29737,7 +29737,7 @@
       <c r="E1464" t="n">
         <v>1.905463660247267e-07</v>
       </c>
-      <c r="F1464" s="2" t="n">
+      <c r="F1464" s="1" t="n">
         <v>46218</v>
       </c>
     </row>
@@ -29757,7 +29757,7 @@
       <c r="E1465" t="n">
         <v>-7.694284092892581e-07</v>
       </c>
-      <c r="F1465" s="2" t="n">
+      <c r="F1465" s="1" t="n">
         <v>46218</v>
       </c>
     </row>
@@ -29777,7 +29777,7 @@
       <c r="E1466" t="n">
         <v>-1.448457538695752e-06</v>
       </c>
-      <c r="F1466" s="2" t="n">
+      <c r="F1466" s="1" t="n">
         <v>46218</v>
       </c>
     </row>
@@ -29797,7 +29797,7 @@
       <c r="E1467" t="n">
         <v>3.175879782997984e-07</v>
       </c>
-      <c r="F1467" s="2" t="n">
+      <c r="F1467" s="1" t="n">
         <v>46218</v>
       </c>
     </row>
@@ -29817,7 +29817,7 @@
       <c r="E1468" t="n">
         <v>8.538606666306967e-08</v>
       </c>
-      <c r="F1468" s="2" t="n">
+      <c r="F1468" s="1" t="n">
         <v>46218</v>
       </c>
     </row>
@@ -29837,7 +29837,7 @@
       <c r="E1469" t="n">
         <v>1.410610943956866e-07</v>
       </c>
-      <c r="F1469" s="2" t="n">
+      <c r="F1469" s="1" t="n">
         <v>46218</v>
       </c>
     </row>
@@ -29857,7 +29857,7 @@
       <c r="E1470" t="n">
         <v>1.94478376839643e-06</v>
       </c>
-      <c r="F1470" s="2" t="n">
+      <c r="F1470" s="1" t="n">
         <v>46218</v>
       </c>
     </row>
@@ -29877,7 +29877,7 @@
       <c r="E1471" t="n">
         <v>-1.326082580014748e-07</v>
       </c>
-      <c r="F1471" s="2" t="n">
+      <c r="F1471" s="1" t="n">
         <v>46218</v>
       </c>
     </row>
@@ -29897,7 +29897,7 @@
       <c r="E1472" t="n">
         <v>-7.326873255555712e-09</v>
       </c>
-      <c r="F1472" s="2" t="n">
+      <c r="F1472" s="1" t="n">
         <v>46218</v>
       </c>
     </row>
@@ -29917,7 +29917,7 @@
       <c r="E1473" t="n">
         <v>3.274550326780346e-06</v>
       </c>
-      <c r="F1473" s="2" t="n">
+      <c r="F1473" s="1" t="n">
         <v>46218</v>
       </c>
     </row>
@@ -29937,7 +29937,7 @@
       <c r="E1474" t="n">
         <v>-1.359722111741666e-06</v>
       </c>
-      <c r="F1474" s="2" t="n">
+      <c r="F1474" s="1" t="n">
         <v>46218</v>
       </c>
     </row>
@@ -29957,7 +29957,7 @@
       <c r="E1475" t="n">
         <v>-5.396939133600158e-06</v>
       </c>
-      <c r="F1475" s="2" t="n">
+      <c r="F1475" s="1" t="n">
         <v>46218</v>
       </c>
     </row>
@@ -29977,7 +29977,7 @@
       <c r="E1476" t="n">
         <v>-2.344523628828648e-08</v>
       </c>
-      <c r="F1476" s="2" t="n">
+      <c r="F1476" s="1" t="n">
         <v>46218</v>
       </c>
     </row>
@@ -29997,7 +29997,7 @@
       <c r="E1477" t="n">
         <v>-4.811249641314511e-07</v>
       </c>
-      <c r="F1477" s="2" t="n">
+      <c r="F1477" s="1" t="n">
         <v>46218</v>
       </c>
     </row>
@@ -30017,7 +30017,7 @@
       <c r="E1478" t="n">
         <v>-1.660095572095659e-06</v>
       </c>
-      <c r="F1478" s="2" t="n">
+      <c r="F1478" s="1" t="n">
         <v>46218</v>
       </c>
     </row>
@@ -30037,7 +30037,7 @@
       <c r="E1479" t="n">
         <v>1.34528974488232e-06</v>
       </c>
-      <c r="F1479" s="2" t="n">
+      <c r="F1479" s="1" t="n">
         <v>46218</v>
       </c>
     </row>
@@ -30057,7 +30057,7 @@
       <c r="E1480" t="n">
         <v>2.096795130260158e-06</v>
       </c>
-      <c r="F1480" s="2" t="n">
+      <c r="F1480" s="1" t="n">
         <v>46218</v>
       </c>
     </row>
@@ -30077,7 +30077,7 @@
       <c r="E1481" t="n">
         <v>5.251364439226888e-06</v>
       </c>
-      <c r="F1481" s="2" t="n">
+      <c r="F1481" s="1" t="n">
         <v>46218</v>
       </c>
     </row>
@@ -30097,7 +30097,7 @@
       <c r="E1482" t="n">
         <v>4.054701956137024e-05</v>
       </c>
-      <c r="F1482" s="2" t="n">
+      <c r="F1482" s="1" t="n">
         <v>46218</v>
       </c>
     </row>
@@ -30117,7 +30117,7 @@
       <c r="E1483" t="n">
         <v>2.939374008019273e-07</v>
       </c>
-      <c r="F1483" s="2" t="n">
+      <c r="F1483" s="1" t="n">
         <v>46218</v>
       </c>
     </row>
@@ -30137,7 +30137,7 @@
       <c r="E1484" t="n">
         <v>-2.696154510232201e-07</v>
       </c>
-      <c r="F1484" s="2" t="n">
+      <c r="F1484" s="1" t="n">
         <v>46218</v>
       </c>
     </row>
@@ -30157,7 +30157,7 @@
       <c r="E1485" t="n">
         <v>-0.003690569824990196</v>
       </c>
-      <c r="F1485" s="2" t="n">
+      <c r="F1485" s="1" t="n">
         <v>46218</v>
       </c>
     </row>
@@ -30177,7 +30177,7 @@
       <c r="E1486" t="n">
         <v>-1.140261170751256e-06</v>
       </c>
-      <c r="F1486" s="2" t="n">
+      <c r="F1486" s="1" t="n">
         <v>46218</v>
       </c>
     </row>
@@ -30197,7 +30197,7 @@
       <c r="E1487" t="n">
         <v>-8.419149605881594e-06</v>
       </c>
-      <c r="F1487" s="2" t="n">
+      <c r="F1487" s="1" t="n">
         <v>46218</v>
       </c>
     </row>
@@ -30217,7 +30217,7 @@
       <c r="E1488" t="n">
         <v>2.642644986857226e-05</v>
       </c>
-      <c r="F1488" s="2" t="n">
+      <c r="F1488" s="1" t="n">
         <v>46218</v>
       </c>
     </row>
@@ -30237,7 +30237,7 @@
       <c r="E1489" t="n">
         <v>7.201420833716409e-05</v>
       </c>
-      <c r="F1489" s="2" t="n">
+      <c r="F1489" s="1" t="n">
         <v>46218</v>
       </c>
     </row>
@@ -30257,7 +30257,7 @@
       <c r="E1490" t="n">
         <v>3.083344407047495e-05</v>
       </c>
-      <c r="F1490" s="2" t="n">
+      <c r="F1490" s="1" t="n">
         <v>46218</v>
       </c>
     </row>
@@ -30277,8 +30277,1628 @@
       <c r="E1491" t="n">
         <v>0.0001151693110182952</v>
       </c>
-      <c r="F1491" s="2" t="n">
+      <c r="F1491" s="1" t="n">
         <v>46218</v>
+      </c>
+    </row>
+    <row r="1492">
+      <c r="A1492" t="inlineStr"/>
+      <c r="B1492" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C1492" t="inlineStr">
+        <is>
+          <t>all prior revisions</t>
+        </is>
+      </c>
+      <c r="D1492" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1492" t="n">
+        <v>-7.24251276526879e-07</v>
+      </c>
+      <c r="F1492" s="1" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1493">
+      <c r="A1493" t="inlineStr"/>
+      <c r="B1493" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C1493" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1493" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1493" t="n">
+        <v>1.386632265242799e-06</v>
+      </c>
+      <c r="F1493" s="1" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1494">
+      <c r="A1494" t="inlineStr"/>
+      <c r="B1494" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C1494" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1494" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1494" t="n">
+        <v>4.105487657631983e-06</v>
+      </c>
+      <c r="F1494" s="1" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1495">
+      <c r="A1495" t="inlineStr"/>
+      <c r="B1495" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C1495" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1495" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1495" t="n">
+        <v>-9.325264658295986e-09</v>
+      </c>
+      <c r="F1495" s="1" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1496">
+      <c r="A1496" t="inlineStr"/>
+      <c r="B1496" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C1496" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1496" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1496" t="n">
+        <v>-1.230310321818384e-08</v>
+      </c>
+      <c r="F1496" s="1" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1497">
+      <c r="A1497" t="inlineStr"/>
+      <c r="B1497" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C1497" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1497" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1497" t="n">
+        <v>-3.514310015980611e-07</v>
+      </c>
+      <c r="F1497" s="1" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1498">
+      <c r="A1498" t="inlineStr"/>
+      <c r="B1498" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C1498" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1498" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1498" t="n">
+        <v>-7.809828022894468e-07</v>
+      </c>
+      <c r="F1498" s="1" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1499">
+      <c r="A1499" t="inlineStr"/>
+      <c r="B1499" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C1499" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1499" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1499" t="n">
+        <v>-4.744215456878828e-07</v>
+      </c>
+      <c r="F1499" s="1" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1500">
+      <c r="A1500" t="inlineStr"/>
+      <c r="B1500" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C1500" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1500" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1500" t="n">
+        <v>-8.950986858025184e-07</v>
+      </c>
+      <c r="F1500" s="1" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1501">
+      <c r="A1501" t="inlineStr"/>
+      <c r="B1501" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C1501" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1501" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1501" t="n">
+        <v>6.061845228836438e-08</v>
+      </c>
+      <c r="F1501" s="1" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1502">
+      <c r="A1502" t="inlineStr"/>
+      <c r="B1502" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C1502" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1502" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1502" t="n">
+        <v>1.082624978921632e-07</v>
+      </c>
+      <c r="F1502" s="1" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1503">
+      <c r="A1503" t="inlineStr"/>
+      <c r="B1503" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C1503" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1503" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1503" t="n">
+        <v>-8.64580116525008e-08</v>
+      </c>
+      <c r="F1503" s="1" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1504">
+      <c r="A1504" t="inlineStr"/>
+      <c r="B1504" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C1504" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1504" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1504" t="n">
+        <v>-4.957677562033722e-09</v>
+      </c>
+      <c r="F1504" s="1" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1505">
+      <c r="A1505" t="inlineStr"/>
+      <c r="B1505" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C1505" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1505" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1505" t="n">
+        <v>-8.590841262541763e-07</v>
+      </c>
+      <c r="F1505" s="1" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1506">
+      <c r="A1506" t="inlineStr"/>
+      <c r="B1506" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C1506" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1506" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1506" t="n">
+        <v>-3.539534014229655e-06</v>
+      </c>
+      <c r="F1506" s="1" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1507">
+      <c r="A1507" t="inlineStr"/>
+      <c r="B1507" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C1507" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1507" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1507" t="n">
+        <v>-2.792317035122746e-07</v>
+      </c>
+      <c r="F1507" s="1" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1508">
+      <c r="A1508" t="inlineStr"/>
+      <c r="B1508" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C1508" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1508" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1508" t="n">
+        <v>-1.112827163440125e-06</v>
+      </c>
+      <c r="F1508" s="1" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1509">
+      <c r="A1509" t="inlineStr"/>
+      <c r="B1509" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C1509" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1509" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1509" t="n">
+        <v>1.445443189986301e-06</v>
+      </c>
+      <c r="F1509" s="1" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1510">
+      <c r="A1510" t="inlineStr"/>
+      <c r="B1510" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C1510" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1510" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1510" t="n">
+        <v>3.490670582373105e-06</v>
+      </c>
+      <c r="F1510" s="1" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1511">
+      <c r="A1511" t="inlineStr"/>
+      <c r="B1511" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C1511" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1511" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1511" t="n">
+        <v>5.127366799991139e-09</v>
+      </c>
+      <c r="F1511" s="1" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1512">
+      <c r="A1512" t="inlineStr"/>
+      <c r="B1512" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C1512" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1512" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1512" t="n">
+        <v>-7.918824450833028e-07</v>
+      </c>
+      <c r="F1512" s="1" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1513">
+      <c r="A1513" t="inlineStr"/>
+      <c r="B1513" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C1513" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1513" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1513" t="n">
+        <v>4.101197910349164e-07</v>
+      </c>
+      <c r="F1513" s="1" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1514">
+      <c r="A1514" t="inlineStr"/>
+      <c r="B1514" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C1514" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1514" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1514" t="n">
+        <v>-7.648692480836118e-06</v>
+      </c>
+      <c r="F1514" s="1" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1515">
+      <c r="A1515" t="inlineStr"/>
+      <c r="B1515" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C1515" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1515" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1515" t="n">
+        <v>1.622750307940169e-05</v>
+      </c>
+      <c r="F1515" s="1" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1516">
+      <c r="A1516" t="inlineStr"/>
+      <c r="B1516" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C1516" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1516" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1516" t="n">
+        <v>4.868443502447485e-05</v>
+      </c>
+      <c r="F1516" s="1" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1517">
+      <c r="A1517" t="inlineStr"/>
+      <c r="B1517" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="C1517" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1517" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1517" t="n">
+        <v>5.112177454633025e-05</v>
+      </c>
+      <c r="F1517" s="1" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1518">
+      <c r="A1518" t="inlineStr"/>
+      <c r="B1518" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="C1518" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1518" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1518" t="n">
+        <v>0.0001731558105813594</v>
+      </c>
+      <c r="F1518" s="1" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1519">
+      <c r="A1519" t="inlineStr"/>
+      <c r="B1519" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C1519" t="inlineStr">
+        <is>
+          <t>all prior revisions</t>
+        </is>
+      </c>
+      <c r="D1519" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1519" t="n">
+        <v>2.809307326791585e-06</v>
+      </c>
+      <c r="F1519" s="1" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1520">
+      <c r="A1520" t="inlineStr"/>
+      <c r="B1520" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C1520" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1520" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1520" t="n">
+        <v>8.132145606695422e-06</v>
+      </c>
+      <c r="F1520" s="1" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1521">
+      <c r="A1521" t="inlineStr"/>
+      <c r="B1521" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C1521" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1521" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1521" t="n">
+        <v>1.906430565520166e-05</v>
+      </c>
+      <c r="F1521" s="1" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1522">
+      <c r="A1522" t="inlineStr"/>
+      <c r="B1522" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C1522" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1522" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1522" t="n">
+        <v>-1.00878681400455e-09</v>
+      </c>
+      <c r="F1522" s="1" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1523">
+      <c r="A1523" t="inlineStr"/>
+      <c r="B1523" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C1523" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1523" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1523" t="n">
+        <v>1.742932258263146e-07</v>
+      </c>
+      <c r="F1523" s="1" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1524">
+      <c r="A1524" t="inlineStr"/>
+      <c r="B1524" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C1524" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1524" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1524" t="n">
+        <v>2.48782450957887e-07</v>
+      </c>
+      <c r="F1524" s="1" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1525">
+      <c r="A1525" t="inlineStr"/>
+      <c r="B1525" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C1525" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1525" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1525" t="n">
+        <v>-2.333316143875242e-07</v>
+      </c>
+      <c r="F1525" s="1" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1526">
+      <c r="A1526" t="inlineStr"/>
+      <c r="B1526" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C1526" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1526" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1526" t="n">
+        <v>-2.947058210721374e-06</v>
+      </c>
+      <c r="F1526" s="1" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1527">
+      <c r="A1527" t="inlineStr"/>
+      <c r="B1527" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C1527" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1527" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1527" t="n">
+        <v>-4.958508361597885e-06</v>
+      </c>
+      <c r="F1527" s="1" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1528">
+      <c r="A1528" t="inlineStr"/>
+      <c r="B1528" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C1528" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1528" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1528" t="n">
+        <v>4.962725541416656e-08</v>
+      </c>
+      <c r="F1528" s="1" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1529">
+      <c r="A1529" t="inlineStr"/>
+      <c r="B1529" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C1529" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1529" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1529" t="n">
+        <v>-1.659063673138697e-07</v>
+      </c>
+      <c r="F1529" s="1" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1530">
+      <c r="A1530" t="inlineStr"/>
+      <c r="B1530" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C1530" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1530" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1530" t="n">
+        <v>3.636213945455957e-08</v>
+      </c>
+      <c r="F1530" s="1" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1531">
+      <c r="A1531" t="inlineStr"/>
+      <c r="B1531" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C1531" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1531" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1531" t="n">
+        <v>-5.846235776132669e-10</v>
+      </c>
+      <c r="F1531" s="1" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1532">
+      <c r="A1532" t="inlineStr"/>
+      <c r="B1532" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C1532" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1532" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1532" t="n">
+        <v>-3.210205076518717e-06</v>
+      </c>
+      <c r="F1532" s="1" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1533">
+      <c r="A1533" t="inlineStr"/>
+      <c r="B1533" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C1533" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1533" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1533" t="n">
+        <v>-1.111792303120784e-05</v>
+      </c>
+      <c r="F1533" s="1" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1534">
+      <c r="A1534" t="inlineStr"/>
+      <c r="B1534" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C1534" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1534" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1534" t="n">
+        <v>4.155831221036004e-07</v>
+      </c>
+      <c r="F1534" s="1" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1535">
+      <c r="A1535" t="inlineStr"/>
+      <c r="B1535" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C1535" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1535" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1535" t="n">
+        <v>-3.633593109160144e-07</v>
+      </c>
+      <c r="F1535" s="1" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1536">
+      <c r="A1536" t="inlineStr"/>
+      <c r="B1536" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C1536" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1536" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1536" t="n">
+        <v>-3.810779292827258e-06</v>
+      </c>
+      <c r="F1536" s="1" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1537">
+      <c r="A1537" t="inlineStr"/>
+      <c r="B1537" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C1537" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1537" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1537" t="n">
+        <v>-8.616392670046246e-06</v>
+      </c>
+      <c r="F1537" s="1" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1538">
+      <c r="A1538" t="inlineStr"/>
+      <c r="B1538" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C1538" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1538" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1538" t="n">
+        <v>1.010853439079625e-05</v>
+      </c>
+      <c r="F1538" s="1" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1539">
+      <c r="A1539" t="inlineStr"/>
+      <c r="B1539" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C1539" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1539" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1539" t="n">
+        <v>2.312271847955274e-05</v>
+      </c>
+      <c r="F1539" s="1" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1540">
+      <c r="A1540" t="inlineStr"/>
+      <c r="B1540" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C1540" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1540" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1540" t="n">
+        <v>-6.405662386049243e-07</v>
+      </c>
+      <c r="F1540" s="1" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1541">
+      <c r="A1541" t="inlineStr"/>
+      <c r="B1541" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C1541" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1541" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1541" t="n">
+        <v>1.84198794161548e-05</v>
+      </c>
+      <c r="F1541" s="1" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1542">
+      <c r="A1542" t="inlineStr"/>
+      <c r="B1542" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C1542" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1542" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1542" t="n">
+        <v>9.189979158349312e-06</v>
+      </c>
+      <c r="F1542" s="1" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1543">
+      <c r="A1543" t="inlineStr"/>
+      <c r="B1543" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C1543" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1543" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1543" t="n">
+        <v>-1.30871583691224e-05</v>
+      </c>
+      <c r="F1543" s="1" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1544">
+      <c r="A1544" t="inlineStr"/>
+      <c r="B1544" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="C1544" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1544" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1544" t="n">
+        <v>-0.0003543622859028615</v>
+      </c>
+      <c r="F1544" s="1" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1545">
+      <c r="A1545" t="inlineStr"/>
+      <c r="B1545" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="C1545" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1545" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1545" t="n">
+        <v>-0.0006314899702911467</v>
+      </c>
+      <c r="F1545" s="1" t="n">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="1546">
+      <c r="A1546" t="inlineStr"/>
+      <c r="B1546" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C1546" t="inlineStr">
+        <is>
+          <t>all prior revisions</t>
+        </is>
+      </c>
+      <c r="D1546" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1546" t="n">
+        <v>2.809307326791585e-06</v>
+      </c>
+      <c r="F1546" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1547">
+      <c r="A1547" t="inlineStr"/>
+      <c r="B1547" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C1547" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1547" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1547" t="n">
+        <v>8.132145606695422e-06</v>
+      </c>
+      <c r="F1547" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1548">
+      <c r="A1548" t="inlineStr"/>
+      <c r="B1548" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C1548" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1548" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1548" t="n">
+        <v>1.906430565520166e-05</v>
+      </c>
+      <c r="F1548" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1549">
+      <c r="A1549" t="inlineStr"/>
+      <c r="B1549" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C1549" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1549" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1549" t="n">
+        <v>-1.00878681400455e-09</v>
+      </c>
+      <c r="F1549" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1550">
+      <c r="A1550" t="inlineStr"/>
+      <c r="B1550" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C1550" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1550" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1550" t="n">
+        <v>1.742932258263146e-07</v>
+      </c>
+      <c r="F1550" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1551">
+      <c r="A1551" t="inlineStr"/>
+      <c r="B1551" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C1551" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1551" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1551" t="n">
+        <v>2.48782450957887e-07</v>
+      </c>
+      <c r="F1551" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1552">
+      <c r="A1552" t="inlineStr"/>
+      <c r="B1552" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C1552" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1552" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1552" t="n">
+        <v>-2.333316143875242e-07</v>
+      </c>
+      <c r="F1552" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1553">
+      <c r="A1553" t="inlineStr"/>
+      <c r="B1553" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C1553" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1553" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1553" t="n">
+        <v>-2.947058210721374e-06</v>
+      </c>
+      <c r="F1553" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1554">
+      <c r="A1554" t="inlineStr"/>
+      <c r="B1554" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C1554" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1554" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1554" t="n">
+        <v>-4.958508361597885e-06</v>
+      </c>
+      <c r="F1554" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1555">
+      <c r="A1555" t="inlineStr"/>
+      <c r="B1555" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C1555" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1555" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1555" t="n">
+        <v>4.962725541416656e-08</v>
+      </c>
+      <c r="F1555" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1556">
+      <c r="A1556" t="inlineStr"/>
+      <c r="B1556" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C1556" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1556" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1556" t="n">
+        <v>-1.659063673138697e-07</v>
+      </c>
+      <c r="F1556" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1557">
+      <c r="A1557" t="inlineStr"/>
+      <c r="B1557" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C1557" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1557" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1557" t="n">
+        <v>3.636213945455957e-08</v>
+      </c>
+      <c r="F1557" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1558">
+      <c r="A1558" t="inlineStr"/>
+      <c r="B1558" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C1558" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1558" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1558" t="n">
+        <v>-5.846235776132669e-10</v>
+      </c>
+      <c r="F1558" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1559">
+      <c r="A1559" t="inlineStr"/>
+      <c r="B1559" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C1559" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1559" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1559" t="n">
+        <v>-3.210205076518717e-06</v>
+      </c>
+      <c r="F1559" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1560">
+      <c r="A1560" t="inlineStr"/>
+      <c r="B1560" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C1560" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1560" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1560" t="n">
+        <v>-1.111792303120784e-05</v>
+      </c>
+      <c r="F1560" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1561">
+      <c r="A1561" t="inlineStr"/>
+      <c r="B1561" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C1561" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1561" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1561" t="n">
+        <v>4.155831221036004e-07</v>
+      </c>
+      <c r="F1561" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1562">
+      <c r="A1562" t="inlineStr"/>
+      <c r="B1562" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C1562" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1562" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1562" t="n">
+        <v>-3.633593109160144e-07</v>
+      </c>
+      <c r="F1562" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1563">
+      <c r="A1563" t="inlineStr"/>
+      <c r="B1563" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C1563" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1563" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1563" t="n">
+        <v>-3.810779292827258e-06</v>
+      </c>
+      <c r="F1563" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1564">
+      <c r="A1564" t="inlineStr"/>
+      <c r="B1564" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C1564" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1564" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1564" t="n">
+        <v>-8.616392670046246e-06</v>
+      </c>
+      <c r="F1564" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1565">
+      <c r="A1565" t="inlineStr"/>
+      <c r="B1565" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C1565" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1565" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1565" t="n">
+        <v>1.010853439079625e-05</v>
+      </c>
+      <c r="F1565" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1566">
+      <c r="A1566" t="inlineStr"/>
+      <c r="B1566" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C1566" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1566" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1566" t="n">
+        <v>2.312271847955274e-05</v>
+      </c>
+      <c r="F1566" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1567">
+      <c r="A1567" t="inlineStr"/>
+      <c r="B1567" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C1567" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1567" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1567" t="n">
+        <v>-6.405662386049243e-07</v>
+      </c>
+      <c r="F1567" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1568">
+      <c r="A1568" t="inlineStr"/>
+      <c r="B1568" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C1568" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1568" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1568" t="n">
+        <v>1.84198794161548e-05</v>
+      </c>
+      <c r="F1568" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1569">
+      <c r="A1569" t="inlineStr"/>
+      <c r="B1569" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C1569" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1569" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1569" t="n">
+        <v>9.189979158349312e-06</v>
+      </c>
+      <c r="F1569" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1570">
+      <c r="A1570" t="inlineStr"/>
+      <c r="B1570" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C1570" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1570" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1570" t="n">
+        <v>-1.30871583691224e-05</v>
+      </c>
+      <c r="F1570" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1571">
+      <c r="A1571" t="inlineStr"/>
+      <c r="B1571" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="C1571" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1571" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1571" t="n">
+        <v>-0.0003543622859028615</v>
+      </c>
+      <c r="F1571" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1572">
+      <c r="A1572" t="inlineStr"/>
+      <c r="B1572" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="C1572" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1572" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1572" t="n">
+        <v>-0.0006314899702911467</v>
+      </c>
+      <c r="F1572" s="2" t="n">
+        <v>46219</v>
       </c>
     </row>
   </sheetData>

--- a/pib_nowcast/data/news_impacts.xlsx
+++ b/pib_nowcast/data/news_impacts.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1572"/>
+  <dimension ref="A1:F1599"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31377,7 +31377,7 @@
       <c r="E1546" t="n">
         <v>2.809307326791585e-06</v>
       </c>
-      <c r="F1546" s="2" t="n">
+      <c r="F1546" s="1" t="n">
         <v>46219</v>
       </c>
     </row>
@@ -31397,7 +31397,7 @@
       <c r="E1547" t="n">
         <v>8.132145606695422e-06</v>
       </c>
-      <c r="F1547" s="2" t="n">
+      <c r="F1547" s="1" t="n">
         <v>46219</v>
       </c>
     </row>
@@ -31417,7 +31417,7 @@
       <c r="E1548" t="n">
         <v>1.906430565520166e-05</v>
       </c>
-      <c r="F1548" s="2" t="n">
+      <c r="F1548" s="1" t="n">
         <v>46219</v>
       </c>
     </row>
@@ -31437,7 +31437,7 @@
       <c r="E1549" t="n">
         <v>-1.00878681400455e-09</v>
       </c>
-      <c r="F1549" s="2" t="n">
+      <c r="F1549" s="1" t="n">
         <v>46219</v>
       </c>
     </row>
@@ -31457,7 +31457,7 @@
       <c r="E1550" t="n">
         <v>1.742932258263146e-07</v>
       </c>
-      <c r="F1550" s="2" t="n">
+      <c r="F1550" s="1" t="n">
         <v>46219</v>
       </c>
     </row>
@@ -31477,7 +31477,7 @@
       <c r="E1551" t="n">
         <v>2.48782450957887e-07</v>
       </c>
-      <c r="F1551" s="2" t="n">
+      <c r="F1551" s="1" t="n">
         <v>46219</v>
       </c>
     </row>
@@ -31497,7 +31497,7 @@
       <c r="E1552" t="n">
         <v>-2.333316143875242e-07</v>
       </c>
-      <c r="F1552" s="2" t="n">
+      <c r="F1552" s="1" t="n">
         <v>46219</v>
       </c>
     </row>
@@ -31517,7 +31517,7 @@
       <c r="E1553" t="n">
         <v>-2.947058210721374e-06</v>
       </c>
-      <c r="F1553" s="2" t="n">
+      <c r="F1553" s="1" t="n">
         <v>46219</v>
       </c>
     </row>
@@ -31537,7 +31537,7 @@
       <c r="E1554" t="n">
         <v>-4.958508361597885e-06</v>
       </c>
-      <c r="F1554" s="2" t="n">
+      <c r="F1554" s="1" t="n">
         <v>46219</v>
       </c>
     </row>
@@ -31557,7 +31557,7 @@
       <c r="E1555" t="n">
         <v>4.962725541416656e-08</v>
       </c>
-      <c r="F1555" s="2" t="n">
+      <c r="F1555" s="1" t="n">
         <v>46219</v>
       </c>
     </row>
@@ -31577,7 +31577,7 @@
       <c r="E1556" t="n">
         <v>-1.659063673138697e-07</v>
       </c>
-      <c r="F1556" s="2" t="n">
+      <c r="F1556" s="1" t="n">
         <v>46219</v>
       </c>
     </row>
@@ -31597,7 +31597,7 @@
       <c r="E1557" t="n">
         <v>3.636213945455957e-08</v>
       </c>
-      <c r="F1557" s="2" t="n">
+      <c r="F1557" s="1" t="n">
         <v>46219</v>
       </c>
     </row>
@@ -31617,7 +31617,7 @@
       <c r="E1558" t="n">
         <v>-5.846235776132669e-10</v>
       </c>
-      <c r="F1558" s="2" t="n">
+      <c r="F1558" s="1" t="n">
         <v>46219</v>
       </c>
     </row>
@@ -31637,7 +31637,7 @@
       <c r="E1559" t="n">
         <v>-3.210205076518717e-06</v>
       </c>
-      <c r="F1559" s="2" t="n">
+      <c r="F1559" s="1" t="n">
         <v>46219</v>
       </c>
     </row>
@@ -31657,7 +31657,7 @@
       <c r="E1560" t="n">
         <v>-1.111792303120784e-05</v>
       </c>
-      <c r="F1560" s="2" t="n">
+      <c r="F1560" s="1" t="n">
         <v>46219</v>
       </c>
     </row>
@@ -31677,7 +31677,7 @@
       <c r="E1561" t="n">
         <v>4.155831221036004e-07</v>
       </c>
-      <c r="F1561" s="2" t="n">
+      <c r="F1561" s="1" t="n">
         <v>46219</v>
       </c>
     </row>
@@ -31697,7 +31697,7 @@
       <c r="E1562" t="n">
         <v>-3.633593109160144e-07</v>
       </c>
-      <c r="F1562" s="2" t="n">
+      <c r="F1562" s="1" t="n">
         <v>46219</v>
       </c>
     </row>
@@ -31717,7 +31717,7 @@
       <c r="E1563" t="n">
         <v>-3.810779292827258e-06</v>
       </c>
-      <c r="F1563" s="2" t="n">
+      <c r="F1563" s="1" t="n">
         <v>46219</v>
       </c>
     </row>
@@ -31737,7 +31737,7 @@
       <c r="E1564" t="n">
         <v>-8.616392670046246e-06</v>
       </c>
-      <c r="F1564" s="2" t="n">
+      <c r="F1564" s="1" t="n">
         <v>46219</v>
       </c>
     </row>
@@ -31757,7 +31757,7 @@
       <c r="E1565" t="n">
         <v>1.010853439079625e-05</v>
       </c>
-      <c r="F1565" s="2" t="n">
+      <c r="F1565" s="1" t="n">
         <v>46219</v>
       </c>
     </row>
@@ -31777,7 +31777,7 @@
       <c r="E1566" t="n">
         <v>2.312271847955274e-05</v>
       </c>
-      <c r="F1566" s="2" t="n">
+      <c r="F1566" s="1" t="n">
         <v>46219</v>
       </c>
     </row>
@@ -31797,7 +31797,7 @@
       <c r="E1567" t="n">
         <v>-6.405662386049243e-07</v>
       </c>
-      <c r="F1567" s="2" t="n">
+      <c r="F1567" s="1" t="n">
         <v>46219</v>
       </c>
     </row>
@@ -31817,7 +31817,7 @@
       <c r="E1568" t="n">
         <v>1.84198794161548e-05</v>
       </c>
-      <c r="F1568" s="2" t="n">
+      <c r="F1568" s="1" t="n">
         <v>46219</v>
       </c>
     </row>
@@ -31837,7 +31837,7 @@
       <c r="E1569" t="n">
         <v>9.189979158349312e-06</v>
       </c>
-      <c r="F1569" s="2" t="n">
+      <c r="F1569" s="1" t="n">
         <v>46219</v>
       </c>
     </row>
@@ -31857,7 +31857,7 @@
       <c r="E1570" t="n">
         <v>-1.30871583691224e-05</v>
       </c>
-      <c r="F1570" s="2" t="n">
+      <c r="F1570" s="1" t="n">
         <v>46219</v>
       </c>
     </row>
@@ -31877,7 +31877,7 @@
       <c r="E1571" t="n">
         <v>-0.0003543622859028615</v>
       </c>
-      <c r="F1571" s="2" t="n">
+      <c r="F1571" s="1" t="n">
         <v>46219</v>
       </c>
     </row>
@@ -31897,7 +31897,547 @@
       <c r="E1572" t="n">
         <v>-0.0006314899702911467</v>
       </c>
-      <c r="F1572" s="2" t="n">
+      <c r="F1572" s="1" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1573">
+      <c r="A1573" t="inlineStr"/>
+      <c r="B1573" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C1573" t="inlineStr">
+        <is>
+          <t>all prior revisions</t>
+        </is>
+      </c>
+      <c r="D1573" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1573" t="n">
+        <v>1.553876739583447e-05</v>
+      </c>
+      <c r="F1573" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1574">
+      <c r="A1574" t="inlineStr"/>
+      <c r="B1574" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C1574" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1574" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1574" t="n">
+        <v>6.799047636741352e-05</v>
+      </c>
+      <c r="F1574" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1575">
+      <c r="A1575" t="inlineStr"/>
+      <c r="B1575" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C1575" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1575" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1575" t="n">
+        <v>3.201613217076952e-05</v>
+      </c>
+      <c r="F1575" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1576">
+      <c r="A1576" t="inlineStr"/>
+      <c r="B1576" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C1576" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1576" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1576" t="n">
+        <v>-1.365499964584714e-06</v>
+      </c>
+      <c r="F1576" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1577">
+      <c r="A1577" t="inlineStr"/>
+      <c r="B1577" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C1577" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1577" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1577" t="n">
+        <v>-6.747376845784806e-07</v>
+      </c>
+      <c r="F1577" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1578">
+      <c r="A1578" t="inlineStr"/>
+      <c r="B1578" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C1578" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1578" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1578" t="n">
+        <v>1.013516667201559e-05</v>
+      </c>
+      <c r="F1578" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1579">
+      <c r="A1579" t="inlineStr"/>
+      <c r="B1579" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C1579" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1579" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1579" t="n">
+        <v>4.100450772425103e-06</v>
+      </c>
+      <c r="F1579" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1580">
+      <c r="A1580" t="inlineStr"/>
+      <c r="B1580" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C1580" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1580" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1580" t="n">
+        <v>-2.315601194368089e-05</v>
+      </c>
+      <c r="F1580" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1581">
+      <c r="A1581" t="inlineStr"/>
+      <c r="B1581" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C1581" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1581" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1581" t="n">
+        <v>-7.676561760304214e-06</v>
+      </c>
+      <c r="F1581" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1582">
+      <c r="A1582" t="inlineStr"/>
+      <c r="B1582" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C1582" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1582" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1582" t="n">
+        <v>3.724603344032278e-06</v>
+      </c>
+      <c r="F1582" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1583">
+      <c r="A1583" t="inlineStr"/>
+      <c r="B1583" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C1583" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1583" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1583" t="n">
+        <v>9.752973141372261e-07</v>
+      </c>
+      <c r="F1583" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1584">
+      <c r="A1584" t="inlineStr"/>
+      <c r="B1584" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C1584" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1584" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1584" t="n">
+        <v>1.450145653244642e-06</v>
+      </c>
+      <c r="F1584" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1585">
+      <c r="A1585" t="inlineStr"/>
+      <c r="B1585" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C1585" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1585" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1585" t="n">
+        <v>1.3504957050756e-08</v>
+      </c>
+      <c r="F1585" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1586">
+      <c r="A1586" t="inlineStr"/>
+      <c r="B1586" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C1586" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1586" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1586" t="n">
+        <v>-2.448566090115156e-05</v>
+      </c>
+      <c r="F1586" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1587">
+      <c r="A1587" t="inlineStr"/>
+      <c r="B1587" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C1587" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1587" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1587" t="n">
+        <v>-1.652591475586843e-05</v>
+      </c>
+      <c r="F1587" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1588">
+      <c r="A1588" t="inlineStr"/>
+      <c r="B1588" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C1588" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1588" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1588" t="n">
+        <v>1.724352544529105e-05</v>
+      </c>
+      <c r="F1588" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1589">
+      <c r="A1589" t="inlineStr"/>
+      <c r="B1589" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C1589" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1589" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1589" t="n">
+        <v>9.027067917747313e-06</v>
+      </c>
+      <c r="F1589" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1590">
+      <c r="A1590" t="inlineStr"/>
+      <c r="B1590" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C1590" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1590" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1590" t="n">
+        <v>-3.199072818885431e-05</v>
+      </c>
+      <c r="F1590" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1591">
+      <c r="A1591" t="inlineStr"/>
+      <c r="B1591" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C1591" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1591" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1591" t="n">
+        <v>-1.472211075041957e-05</v>
+      </c>
+      <c r="F1591" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1592">
+      <c r="A1592" t="inlineStr"/>
+      <c r="B1592" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C1592" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1592" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1592" t="n">
+        <v>6.355112636674094e-05</v>
+      </c>
+      <c r="F1592" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1593">
+      <c r="A1593" t="inlineStr"/>
+      <c r="B1593" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C1593" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1593" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1593" t="n">
+        <v>2.655915066490321e-05</v>
+      </c>
+      <c r="F1593" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1594">
+      <c r="A1594" t="inlineStr"/>
+      <c r="B1594" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C1594" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1594" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1594" t="n">
+        <v>-0.0003432469883904847</v>
+      </c>
+      <c r="F1594" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1595">
+      <c r="A1595" t="inlineStr"/>
+      <c r="B1595" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C1595" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1595" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1595" t="n">
+        <v>-0.0001348669960979755</v>
+      </c>
+      <c r="F1595" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1596">
+      <c r="A1596" t="inlineStr"/>
+      <c r="B1596" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C1596" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1596" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1596" t="n">
+        <v>0.0003975238149137991</v>
+      </c>
+      <c r="F1596" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1597">
+      <c r="A1597" t="inlineStr"/>
+      <c r="B1597" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C1597" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1597" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1597" t="n">
+        <v>0.000189487343414863</v>
+      </c>
+      <c r="F1597" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1598">
+      <c r="A1598" t="inlineStr"/>
+      <c r="B1598" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="C1598" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1598" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1598" t="n">
+        <v>-0.006453514378236496</v>
+      </c>
+      <c r="F1598" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1599">
+      <c r="A1599" t="inlineStr"/>
+      <c r="B1599" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="C1599" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1599" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1599" t="n">
+        <v>-0.006465210588967209</v>
+      </c>
+      <c r="F1599" s="2" t="n">
         <v>46219</v>
       </c>
     </row>

--- a/pib_nowcast/data/news_impacts.xlsx
+++ b/pib_nowcast/data/news_impacts.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1572"/>
+  <dimension ref="A1:F1653"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31377,7 +31377,7 @@
       <c r="E1546" t="n">
         <v>2.809307326791585e-06</v>
       </c>
-      <c r="F1546" s="2" t="n">
+      <c r="F1546" s="1" t="n">
         <v>46219</v>
       </c>
     </row>
@@ -31397,7 +31397,7 @@
       <c r="E1547" t="n">
         <v>8.132145606695422e-06</v>
       </c>
-      <c r="F1547" s="2" t="n">
+      <c r="F1547" s="1" t="n">
         <v>46219</v>
       </c>
     </row>
@@ -31417,7 +31417,7 @@
       <c r="E1548" t="n">
         <v>1.906430565520166e-05</v>
       </c>
-      <c r="F1548" s="2" t="n">
+      <c r="F1548" s="1" t="n">
         <v>46219</v>
       </c>
     </row>
@@ -31437,7 +31437,7 @@
       <c r="E1549" t="n">
         <v>-1.00878681400455e-09</v>
       </c>
-      <c r="F1549" s="2" t="n">
+      <c r="F1549" s="1" t="n">
         <v>46219</v>
       </c>
     </row>
@@ -31457,7 +31457,7 @@
       <c r="E1550" t="n">
         <v>1.742932258263146e-07</v>
       </c>
-      <c r="F1550" s="2" t="n">
+      <c r="F1550" s="1" t="n">
         <v>46219</v>
       </c>
     </row>
@@ -31477,7 +31477,7 @@
       <c r="E1551" t="n">
         <v>2.48782450957887e-07</v>
       </c>
-      <c r="F1551" s="2" t="n">
+      <c r="F1551" s="1" t="n">
         <v>46219</v>
       </c>
     </row>
@@ -31497,7 +31497,7 @@
       <c r="E1552" t="n">
         <v>-2.333316143875242e-07</v>
       </c>
-      <c r="F1552" s="2" t="n">
+      <c r="F1552" s="1" t="n">
         <v>46219</v>
       </c>
     </row>
@@ -31517,7 +31517,7 @@
       <c r="E1553" t="n">
         <v>-2.947058210721374e-06</v>
       </c>
-      <c r="F1553" s="2" t="n">
+      <c r="F1553" s="1" t="n">
         <v>46219</v>
       </c>
     </row>
@@ -31537,7 +31537,7 @@
       <c r="E1554" t="n">
         <v>-4.958508361597885e-06</v>
       </c>
-      <c r="F1554" s="2" t="n">
+      <c r="F1554" s="1" t="n">
         <v>46219</v>
       </c>
     </row>
@@ -31557,7 +31557,7 @@
       <c r="E1555" t="n">
         <v>4.962725541416656e-08</v>
       </c>
-      <c r="F1555" s="2" t="n">
+      <c r="F1555" s="1" t="n">
         <v>46219</v>
       </c>
     </row>
@@ -31577,7 +31577,7 @@
       <c r="E1556" t="n">
         <v>-1.659063673138697e-07</v>
       </c>
-      <c r="F1556" s="2" t="n">
+      <c r="F1556" s="1" t="n">
         <v>46219</v>
       </c>
     </row>
@@ -31597,7 +31597,7 @@
       <c r="E1557" t="n">
         <v>3.636213945455957e-08</v>
       </c>
-      <c r="F1557" s="2" t="n">
+      <c r="F1557" s="1" t="n">
         <v>46219</v>
       </c>
     </row>
@@ -31617,7 +31617,7 @@
       <c r="E1558" t="n">
         <v>-5.846235776132669e-10</v>
       </c>
-      <c r="F1558" s="2" t="n">
+      <c r="F1558" s="1" t="n">
         <v>46219</v>
       </c>
     </row>
@@ -31637,7 +31637,7 @@
       <c r="E1559" t="n">
         <v>-3.210205076518717e-06</v>
       </c>
-      <c r="F1559" s="2" t="n">
+      <c r="F1559" s="1" t="n">
         <v>46219</v>
       </c>
     </row>
@@ -31657,7 +31657,7 @@
       <c r="E1560" t="n">
         <v>-1.111792303120784e-05</v>
       </c>
-      <c r="F1560" s="2" t="n">
+      <c r="F1560" s="1" t="n">
         <v>46219</v>
       </c>
     </row>
@@ -31677,7 +31677,7 @@
       <c r="E1561" t="n">
         <v>4.155831221036004e-07</v>
       </c>
-      <c r="F1561" s="2" t="n">
+      <c r="F1561" s="1" t="n">
         <v>46219</v>
       </c>
     </row>
@@ -31697,7 +31697,7 @@
       <c r="E1562" t="n">
         <v>-3.633593109160144e-07</v>
       </c>
-      <c r="F1562" s="2" t="n">
+      <c r="F1562" s="1" t="n">
         <v>46219</v>
       </c>
     </row>
@@ -31717,7 +31717,7 @@
       <c r="E1563" t="n">
         <v>-3.810779292827258e-06</v>
       </c>
-      <c r="F1563" s="2" t="n">
+      <c r="F1563" s="1" t="n">
         <v>46219</v>
       </c>
     </row>
@@ -31737,7 +31737,7 @@
       <c r="E1564" t="n">
         <v>-8.616392670046246e-06</v>
       </c>
-      <c r="F1564" s="2" t="n">
+      <c r="F1564" s="1" t="n">
         <v>46219</v>
       </c>
     </row>
@@ -31757,7 +31757,7 @@
       <c r="E1565" t="n">
         <v>1.010853439079625e-05</v>
       </c>
-      <c r="F1565" s="2" t="n">
+      <c r="F1565" s="1" t="n">
         <v>46219</v>
       </c>
     </row>
@@ -31777,7 +31777,7 @@
       <c r="E1566" t="n">
         <v>2.312271847955274e-05</v>
       </c>
-      <c r="F1566" s="2" t="n">
+      <c r="F1566" s="1" t="n">
         <v>46219</v>
       </c>
     </row>
@@ -31797,7 +31797,7 @@
       <c r="E1567" t="n">
         <v>-6.405662386049243e-07</v>
       </c>
-      <c r="F1567" s="2" t="n">
+      <c r="F1567" s="1" t="n">
         <v>46219</v>
       </c>
     </row>
@@ -31817,7 +31817,7 @@
       <c r="E1568" t="n">
         <v>1.84198794161548e-05</v>
       </c>
-      <c r="F1568" s="2" t="n">
+      <c r="F1568" s="1" t="n">
         <v>46219</v>
       </c>
     </row>
@@ -31837,7 +31837,7 @@
       <c r="E1569" t="n">
         <v>9.189979158349312e-06</v>
       </c>
-      <c r="F1569" s="2" t="n">
+      <c r="F1569" s="1" t="n">
         <v>46219</v>
       </c>
     </row>
@@ -31857,7 +31857,7 @@
       <c r="E1570" t="n">
         <v>-1.30871583691224e-05</v>
       </c>
-      <c r="F1570" s="2" t="n">
+      <c r="F1570" s="1" t="n">
         <v>46219</v>
       </c>
     </row>
@@ -31877,7 +31877,7 @@
       <c r="E1571" t="n">
         <v>-0.0003543622859028615</v>
       </c>
-      <c r="F1571" s="2" t="n">
+      <c r="F1571" s="1" t="n">
         <v>46219</v>
       </c>
     </row>
@@ -31897,7 +31897,1627 @@
       <c r="E1572" t="n">
         <v>-0.0006314899702911467</v>
       </c>
-      <c r="F1572" s="2" t="n">
+      <c r="F1572" s="1" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1573">
+      <c r="A1573" t="inlineStr"/>
+      <c r="B1573" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C1573" t="inlineStr">
+        <is>
+          <t>all prior revisions</t>
+        </is>
+      </c>
+      <c r="D1573" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1573" t="n">
+        <v>9.419048249892836e-06</v>
+      </c>
+      <c r="F1573" s="1" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1574">
+      <c r="A1574" t="inlineStr"/>
+      <c r="B1574" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C1574" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1574" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1574" t="n">
+        <v>5.416603410725074e-05</v>
+      </c>
+      <c r="F1574" s="1" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1575">
+      <c r="A1575" t="inlineStr"/>
+      <c r="B1575" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C1575" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1575" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1575" t="n">
+        <v>2.593567622612428e-05</v>
+      </c>
+      <c r="F1575" s="1" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1576">
+      <c r="A1576" t="inlineStr"/>
+      <c r="B1576" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C1576" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1576" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1576" t="n">
+        <v>-1.289052302605704e-06</v>
+      </c>
+      <c r="F1576" s="1" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1577">
+      <c r="A1577" t="inlineStr"/>
+      <c r="B1577" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C1577" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1577" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1577" t="n">
+        <v>-6.668847731913935e-07</v>
+      </c>
+      <c r="F1577" s="1" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1578">
+      <c r="A1578" t="inlineStr"/>
+      <c r="B1578" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C1578" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1578" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1578" t="n">
+        <v>1.153436211218395e-05</v>
+      </c>
+      <c r="F1578" s="1" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1579">
+      <c r="A1579" t="inlineStr"/>
+      <c r="B1579" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C1579" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1579" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1579" t="n">
+        <v>4.779774385226123e-06</v>
+      </c>
+      <c r="F1579" s="1" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1580">
+      <c r="A1580" t="inlineStr"/>
+      <c r="B1580" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C1580" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1580" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1580" t="n">
+        <v>-2.879430607410339e-05</v>
+      </c>
+      <c r="F1580" s="1" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1581">
+      <c r="A1581" t="inlineStr"/>
+      <c r="B1581" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C1581" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1581" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1581" t="n">
+        <v>-9.693896232859104e-06</v>
+      </c>
+      <c r="F1581" s="1" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1582">
+      <c r="A1582" t="inlineStr"/>
+      <c r="B1582" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C1582" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1582" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1582" t="n">
+        <v>6.039586545300685e-06</v>
+      </c>
+      <c r="F1582" s="1" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1583">
+      <c r="A1583" t="inlineStr"/>
+      <c r="B1583" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C1583" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1583" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1583" t="n">
+        <v>1.650907277033887e-06</v>
+      </c>
+      <c r="F1583" s="1" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1584">
+      <c r="A1584" t="inlineStr"/>
+      <c r="B1584" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C1584" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1584" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1584" t="n">
+        <v>3.33271185099792e-06</v>
+      </c>
+      <c r="F1584" s="1" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1585">
+      <c r="A1585" t="inlineStr"/>
+      <c r="B1585" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C1585" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1585" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1585" t="n">
+        <v>3.171360722091044e-08</v>
+      </c>
+      <c r="F1585" s="1" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1586">
+      <c r="A1586" t="inlineStr"/>
+      <c r="B1586" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C1586" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1586" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1586" t="n">
+        <v>-6.421074594911338e-05</v>
+      </c>
+      <c r="F1586" s="1" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1587">
+      <c r="A1587" t="inlineStr"/>
+      <c r="B1587" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C1587" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1587" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1587" t="n">
+        <v>-4.395458975679065e-05</v>
+      </c>
+      <c r="F1587" s="1" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1588">
+      <c r="A1588" t="inlineStr"/>
+      <c r="B1588" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C1588" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1588" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1588" t="n">
+        <v>4.635396745860284e-05</v>
+      </c>
+      <c r="F1588" s="1" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1589">
+      <c r="A1589" t="inlineStr"/>
+      <c r="B1589" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C1589" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1589" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1589" t="n">
+        <v>2.540433694158567e-05</v>
+      </c>
+      <c r="F1589" s="1" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1590">
+      <c r="A1590" t="inlineStr"/>
+      <c r="B1590" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C1590" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1590" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1590" t="n">
+        <v>-0.0001145713796951409</v>
+      </c>
+      <c r="F1590" s="1" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1591">
+      <c r="A1591" t="inlineStr"/>
+      <c r="B1591" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C1591" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1591" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1591" t="n">
+        <v>-5.607209482759891e-05</v>
+      </c>
+      <c r="F1591" s="1" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1592">
+      <c r="A1592" t="inlineStr"/>
+      <c r="B1592" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C1592" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1592" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1592" t="n">
+        <v>0.0002280672510121145</v>
+      </c>
+      <c r="F1592" s="1" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1593">
+      <c r="A1593" t="inlineStr"/>
+      <c r="B1593" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C1593" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1593" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1593" t="n">
+        <v>0.0001025534853479611</v>
+      </c>
+      <c r="F1593" s="1" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1594">
+      <c r="A1594" t="inlineStr"/>
+      <c r="B1594" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C1594" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1594" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1594" t="n">
+        <v>-0.00100783921712422</v>
+      </c>
+      <c r="F1594" s="1" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1595">
+      <c r="A1595" t="inlineStr"/>
+      <c r="B1595" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C1595" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1595" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1595" t="n">
+        <v>-0.0004065250672846863</v>
+      </c>
+      <c r="F1595" s="1" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1596">
+      <c r="A1596" t="inlineStr"/>
+      <c r="B1596" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C1596" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1596" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1596" t="n">
+        <v>0.001185990003467645</v>
+      </c>
+      <c r="F1596" s="1" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1597">
+      <c r="A1597" t="inlineStr"/>
+      <c r="B1597" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C1597" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1597" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1597" t="n">
+        <v>0.0005771094524466857</v>
+      </c>
+      <c r="F1597" s="1" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1598">
+      <c r="A1598" t="inlineStr"/>
+      <c r="B1598" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="C1598" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1598" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1598" t="n">
+        <v>-0.02351583131534556</v>
+      </c>
+      <c r="F1598" s="1" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1599">
+      <c r="A1599" t="inlineStr"/>
+      <c r="B1599" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="C1599" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1599" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1599" t="n">
+        <v>-0.0261005733432178</v>
+      </c>
+      <c r="F1599" s="1" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1600">
+      <c r="A1600" t="inlineStr"/>
+      <c r="B1600" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C1600" t="inlineStr">
+        <is>
+          <t>all prior revisions</t>
+        </is>
+      </c>
+      <c r="D1600" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1600" t="n">
+        <v>2.197947727634353e-07</v>
+      </c>
+      <c r="F1600" s="1" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1601">
+      <c r="A1601" t="inlineStr"/>
+      <c r="B1601" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C1601" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1601" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1601" t="n">
+        <v>3.689627823182565e-06</v>
+      </c>
+      <c r="F1601" s="1" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1602">
+      <c r="A1602" t="inlineStr"/>
+      <c r="B1602" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C1602" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1602" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1602" t="n">
+        <v>1.846594716703196e-06</v>
+      </c>
+      <c r="F1602" s="1" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1603">
+      <c r="A1603" t="inlineStr"/>
+      <c r="B1603" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C1603" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1603" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1603" t="n">
+        <v>-2.674145027899875e-07</v>
+      </c>
+      <c r="F1603" s="1" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1604">
+      <c r="A1604" t="inlineStr"/>
+      <c r="B1604" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C1604" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1604" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1604" t="n">
+        <v>-1.434480743150217e-07</v>
+      </c>
+      <c r="F1604" s="1" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1605">
+      <c r="A1605" t="inlineStr"/>
+      <c r="B1605" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C1605" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1605" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1605" t="n">
+        <v>3.783576389359816e-06</v>
+      </c>
+      <c r="F1605" s="1" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1606">
+      <c r="A1606" t="inlineStr"/>
+      <c r="B1606" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C1606" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1606" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1606" t="n">
+        <v>1.592866201871558e-06</v>
+      </c>
+      <c r="F1606" s="1" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1607">
+      <c r="A1607" t="inlineStr"/>
+      <c r="B1607" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C1607" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1607" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1607" t="n">
+        <v>-1.011229896995737e-05</v>
+      </c>
+      <c r="F1607" s="1" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1608">
+      <c r="A1608" t="inlineStr"/>
+      <c r="B1608" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C1608" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1608" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1608" t="n">
+        <v>-3.425566709872101e-06</v>
+      </c>
+      <c r="F1608" s="1" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1609">
+      <c r="A1609" t="inlineStr"/>
+      <c r="B1609" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C1609" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1609" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1609" t="n">
+        <v>3.01216259216296e-06</v>
+      </c>
+      <c r="F1609" s="1" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1610">
+      <c r="A1610" t="inlineStr"/>
+      <c r="B1610" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C1610" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1610" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1610" t="n">
+        <v>8.32935751794964e-07</v>
+      </c>
+      <c r="F1610" s="1" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1611">
+      <c r="A1611" t="inlineStr"/>
+      <c r="B1611" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C1611" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1611" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1611" t="n">
+        <v>2.2179781819526e-06</v>
+      </c>
+      <c r="F1611" s="1" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1612">
+      <c r="A1612" t="inlineStr"/>
+      <c r="B1612" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C1612" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1612" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1612" t="n">
+        <v>2.114220913533787e-08</v>
+      </c>
+      <c r="F1612" s="1" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1613">
+      <c r="A1613" t="inlineStr"/>
+      <c r="B1613" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C1613" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1613" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1613" t="n">
+        <v>-4.609618137643959e-05</v>
+      </c>
+      <c r="F1613" s="1" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1614">
+      <c r="A1614" t="inlineStr"/>
+      <c r="B1614" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C1614" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1614" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1614" t="n">
+        <v>-3.150225312422281e-05</v>
+      </c>
+      <c r="F1614" s="1" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1615">
+      <c r="A1615" t="inlineStr"/>
+      <c r="B1615" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C1615" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1615" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1615" t="n">
+        <v>3.292159311021373e-05</v>
+      </c>
+      <c r="F1615" s="1" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1616">
+      <c r="A1616" t="inlineStr"/>
+      <c r="B1616" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C1616" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1616" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1616" t="n">
+        <v>1.810347884541396e-05</v>
+      </c>
+      <c r="F1616" s="1" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1617">
+      <c r="A1617" t="inlineStr"/>
+      <c r="B1617" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C1617" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1617" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1617" t="n">
+        <v>-8.418793516131797e-05</v>
+      </c>
+      <c r="F1617" s="1" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1618">
+      <c r="A1618" t="inlineStr"/>
+      <c r="B1618" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C1618" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1618" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1618" t="n">
+        <v>-4.120857865178074e-05</v>
+      </c>
+      <c r="F1618" s="1" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1619">
+      <c r="A1619" t="inlineStr"/>
+      <c r="B1619" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C1619" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1619" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1619" t="n">
+        <v>0.000182847950167109</v>
+      </c>
+      <c r="F1619" s="1" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1620">
+      <c r="A1620" t="inlineStr"/>
+      <c r="B1620" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C1620" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1620" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1620" t="n">
+        <v>8.162074443149614e-05</v>
+      </c>
+      <c r="F1620" s="1" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1621">
+      <c r="A1621" t="inlineStr"/>
+      <c r="B1621" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C1621" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1621" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1621" t="n">
+        <v>-0.0007729771983311101</v>
+      </c>
+      <c r="F1621" s="1" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1622">
+      <c r="A1622" t="inlineStr"/>
+      <c r="B1622" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C1622" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1622" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1622" t="n">
+        <v>-0.000308766579599158</v>
+      </c>
+      <c r="F1622" s="1" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1623">
+      <c r="A1623" t="inlineStr"/>
+      <c r="B1623" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C1623" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1623" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1623" t="n">
+        <v>0.0009026609697048307</v>
+      </c>
+      <c r="F1623" s="1" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1624">
+      <c r="A1624" t="inlineStr"/>
+      <c r="B1624" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C1624" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1624" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1624" t="n">
+        <v>0.0004359193524787822</v>
+      </c>
+      <c r="F1624" s="1" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1625">
+      <c r="A1625" t="inlineStr"/>
+      <c r="B1625" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="C1625" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1625" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1625" t="n">
+        <v>-0.01833344942771385</v>
+      </c>
+      <c r="F1625" s="1" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1626">
+      <c r="A1626" t="inlineStr"/>
+      <c r="B1626" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="C1626" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1626" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1626" t="n">
+        <v>-0.02003650800183343</v>
+      </c>
+      <c r="F1626" s="1" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1627">
+      <c r="A1627" t="inlineStr"/>
+      <c r="B1627" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C1627" t="inlineStr">
+        <is>
+          <t>all prior revisions</t>
+        </is>
+      </c>
+      <c r="D1627" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1627" t="n">
+        <v>1.596516846990493e-05</v>
+      </c>
+      <c r="F1627" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1628">
+      <c r="A1628" t="inlineStr"/>
+      <c r="B1628" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C1628" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1628" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1628" t="n">
+        <v>7.079783437588623e-05</v>
+      </c>
+      <c r="F1628" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1629">
+      <c r="A1629" t="inlineStr"/>
+      <c r="B1629" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C1629" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1629" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1629" t="n">
+        <v>3.377393778366496e-05</v>
+      </c>
+      <c r="F1629" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1630">
+      <c r="A1630" t="inlineStr"/>
+      <c r="B1630" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C1630" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1630" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1630" t="n">
+        <v>-1.389970203420545e-06</v>
+      </c>
+      <c r="F1630" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1631">
+      <c r="A1631" t="inlineStr"/>
+      <c r="B1631" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C1631" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1631" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1631" t="n">
+        <v>-7.097873923760381e-07</v>
+      </c>
+      <c r="F1631" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1632">
+      <c r="A1632" t="inlineStr"/>
+      <c r="B1632" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C1632" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1632" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1632" t="n">
+        <v>1.008669661340617e-05</v>
+      </c>
+      <c r="F1632" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1633">
+      <c r="A1633" t="inlineStr"/>
+      <c r="B1633" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C1633" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1633" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1633" t="n">
+        <v>4.134730299616449e-06</v>
+      </c>
+      <c r="F1633" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1634">
+      <c r="A1634" t="inlineStr"/>
+      <c r="B1634" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C1634" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1634" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1634" t="n">
+        <v>-2.397775811504432e-05</v>
+      </c>
+      <c r="F1634" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1635">
+      <c r="A1635" t="inlineStr"/>
+      <c r="B1635" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C1635" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1635" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1635" t="n">
+        <v>-8.033305053795513e-06</v>
+      </c>
+      <c r="F1635" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1636">
+      <c r="A1636" t="inlineStr"/>
+      <c r="B1636" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C1636" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1636" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1636" t="n">
+        <v>3.730344947494592e-06</v>
+      </c>
+      <c r="F1636" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1637">
+      <c r="A1637" t="inlineStr"/>
+      <c r="B1637" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C1637" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1637" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1637" t="n">
+        <v>1.003812611343475e-06</v>
+      </c>
+      <c r="F1637" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1638">
+      <c r="A1638" t="inlineStr"/>
+      <c r="B1638" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C1638" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1638" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1638" t="n">
+        <v>1.44435386982047e-06</v>
+      </c>
+      <c r="F1638" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1639">
+      <c r="A1639" t="inlineStr"/>
+      <c r="B1639" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C1639" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1639" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1639" t="n">
+        <v>1.363407436122501e-08</v>
+      </c>
+      <c r="F1639" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1640">
+      <c r="A1640" t="inlineStr"/>
+      <c r="B1640" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C1640" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1640" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1640" t="n">
+        <v>-2.533059969020942e-05</v>
+      </c>
+      <c r="F1640" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1641">
+      <c r="A1641" t="inlineStr"/>
+      <c r="B1641" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C1641" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1641" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1641" t="n">
+        <v>-1.729235377331692e-05</v>
+      </c>
+      <c r="F1641" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1642">
+      <c r="A1642" t="inlineStr"/>
+      <c r="B1642" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C1642" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1642" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1642" t="n">
+        <v>1.607387703001572e-05</v>
+      </c>
+      <c r="F1642" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1643">
+      <c r="A1643" t="inlineStr"/>
+      <c r="B1643" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C1643" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1643" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1643" t="n">
+        <v>8.679712205900085e-06</v>
+      </c>
+      <c r="F1643" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1644">
+      <c r="A1644" t="inlineStr"/>
+      <c r="B1644" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C1644" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1644" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1644" t="n">
+        <v>-3.149468719967078e-05</v>
+      </c>
+      <c r="F1644" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1645">
+      <c r="A1645" t="inlineStr"/>
+      <c r="B1645" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C1645" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1645" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1645" t="n">
+        <v>-1.52471051930737e-05</v>
+      </c>
+      <c r="F1645" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1646">
+      <c r="A1646" t="inlineStr"/>
+      <c r="B1646" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C1646" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1646" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1646" t="n">
+        <v>6.700298989707084e-05</v>
+      </c>
+      <c r="F1646" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1647">
+      <c r="A1647" t="inlineStr"/>
+      <c r="B1647" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C1647" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1647" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1647" t="n">
+        <v>2.969561851921743e-05</v>
+      </c>
+      <c r="F1647" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1648">
+      <c r="A1648" t="inlineStr"/>
+      <c r="B1648" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C1648" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1648" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1648" t="n">
+        <v>-0.0002249129464935356</v>
+      </c>
+      <c r="F1648" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1649">
+      <c r="A1649" t="inlineStr"/>
+      <c r="B1649" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C1649" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1649" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1649" t="n">
+        <v>-9.089563101524687e-05</v>
+      </c>
+      <c r="F1649" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1650">
+      <c r="A1650" t="inlineStr"/>
+      <c r="B1650" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C1650" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1650" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1650" t="n">
+        <v>0.0002610027407011109</v>
+      </c>
+      <c r="F1650" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1651">
+      <c r="A1651" t="inlineStr"/>
+      <c r="B1651" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C1651" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1651" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1651" t="n">
+        <v>0.0001272414258142382</v>
+      </c>
+      <c r="F1651" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1652">
+      <c r="A1652" t="inlineStr"/>
+      <c r="B1652" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="C1652" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1652" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1652" t="n">
+        <v>-0.005127509257727185</v>
+      </c>
+      <c r="F1652" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1653">
+      <c r="A1653" t="inlineStr"/>
+      <c r="B1653" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="C1653" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1653" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1653" t="n">
+        <v>-0.00572855887664415</v>
+      </c>
+      <c r="F1653" s="2" t="n">
         <v>46219</v>
       </c>
     </row>

--- a/pib_nowcast/data/news_impacts.xlsx
+++ b/pib_nowcast/data/news_impacts.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1653"/>
+  <dimension ref="A1:F1817"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32997,7 +32997,7 @@
       <c r="E1627" t="n">
         <v>1.596516846990493e-05</v>
       </c>
-      <c r="F1627" s="2" t="n">
+      <c r="F1627" s="1" t="n">
         <v>46219</v>
       </c>
     </row>
@@ -33017,7 +33017,7 @@
       <c r="E1628" t="n">
         <v>7.079783437588623e-05</v>
       </c>
-      <c r="F1628" s="2" t="n">
+      <c r="F1628" s="1" t="n">
         <v>46219</v>
       </c>
     </row>
@@ -33037,7 +33037,7 @@
       <c r="E1629" t="n">
         <v>3.377393778366496e-05</v>
       </c>
-      <c r="F1629" s="2" t="n">
+      <c r="F1629" s="1" t="n">
         <v>46219</v>
       </c>
     </row>
@@ -33057,7 +33057,7 @@
       <c r="E1630" t="n">
         <v>-1.389970203420545e-06</v>
       </c>
-      <c r="F1630" s="2" t="n">
+      <c r="F1630" s="1" t="n">
         <v>46219</v>
       </c>
     </row>
@@ -33077,7 +33077,7 @@
       <c r="E1631" t="n">
         <v>-7.097873923760381e-07</v>
       </c>
-      <c r="F1631" s="2" t="n">
+      <c r="F1631" s="1" t="n">
         <v>46219</v>
       </c>
     </row>
@@ -33097,7 +33097,7 @@
       <c r="E1632" t="n">
         <v>1.008669661340617e-05</v>
       </c>
-      <c r="F1632" s="2" t="n">
+      <c r="F1632" s="1" t="n">
         <v>46219</v>
       </c>
     </row>
@@ -33117,7 +33117,7 @@
       <c r="E1633" t="n">
         <v>4.134730299616449e-06</v>
       </c>
-      <c r="F1633" s="2" t="n">
+      <c r="F1633" s="1" t="n">
         <v>46219</v>
       </c>
     </row>
@@ -33137,7 +33137,7 @@
       <c r="E1634" t="n">
         <v>-2.397775811504432e-05</v>
       </c>
-      <c r="F1634" s="2" t="n">
+      <c r="F1634" s="1" t="n">
         <v>46219</v>
       </c>
     </row>
@@ -33157,7 +33157,7 @@
       <c r="E1635" t="n">
         <v>-8.033305053795513e-06</v>
       </c>
-      <c r="F1635" s="2" t="n">
+      <c r="F1635" s="1" t="n">
         <v>46219</v>
       </c>
     </row>
@@ -33177,7 +33177,7 @@
       <c r="E1636" t="n">
         <v>3.730344947494592e-06</v>
       </c>
-      <c r="F1636" s="2" t="n">
+      <c r="F1636" s="1" t="n">
         <v>46219</v>
       </c>
     </row>
@@ -33197,7 +33197,7 @@
       <c r="E1637" t="n">
         <v>1.003812611343475e-06</v>
       </c>
-      <c r="F1637" s="2" t="n">
+      <c r="F1637" s="1" t="n">
         <v>46219</v>
       </c>
     </row>
@@ -33217,7 +33217,7 @@
       <c r="E1638" t="n">
         <v>1.44435386982047e-06</v>
       </c>
-      <c r="F1638" s="2" t="n">
+      <c r="F1638" s="1" t="n">
         <v>46219</v>
       </c>
     </row>
@@ -33237,7 +33237,7 @@
       <c r="E1639" t="n">
         <v>1.363407436122501e-08</v>
       </c>
-      <c r="F1639" s="2" t="n">
+      <c r="F1639" s="1" t="n">
         <v>46219</v>
       </c>
     </row>
@@ -33257,7 +33257,7 @@
       <c r="E1640" t="n">
         <v>-2.533059969020942e-05</v>
       </c>
-      <c r="F1640" s="2" t="n">
+      <c r="F1640" s="1" t="n">
         <v>46219</v>
       </c>
     </row>
@@ -33277,7 +33277,7 @@
       <c r="E1641" t="n">
         <v>-1.729235377331692e-05</v>
       </c>
-      <c r="F1641" s="2" t="n">
+      <c r="F1641" s="1" t="n">
         <v>46219</v>
       </c>
     </row>
@@ -33297,7 +33297,7 @@
       <c r="E1642" t="n">
         <v>1.607387703001572e-05</v>
       </c>
-      <c r="F1642" s="2" t="n">
+      <c r="F1642" s="1" t="n">
         <v>46219</v>
       </c>
     </row>
@@ -33317,7 +33317,7 @@
       <c r="E1643" t="n">
         <v>8.679712205900085e-06</v>
       </c>
-      <c r="F1643" s="2" t="n">
+      <c r="F1643" s="1" t="n">
         <v>46219</v>
       </c>
     </row>
@@ -33337,7 +33337,7 @@
       <c r="E1644" t="n">
         <v>-3.149468719967078e-05</v>
       </c>
-      <c r="F1644" s="2" t="n">
+      <c r="F1644" s="1" t="n">
         <v>46219</v>
       </c>
     </row>
@@ -33357,7 +33357,7 @@
       <c r="E1645" t="n">
         <v>-1.52471051930737e-05</v>
       </c>
-      <c r="F1645" s="2" t="n">
+      <c r="F1645" s="1" t="n">
         <v>46219</v>
       </c>
     </row>
@@ -33377,7 +33377,7 @@
       <c r="E1646" t="n">
         <v>6.700298989707084e-05</v>
       </c>
-      <c r="F1646" s="2" t="n">
+      <c r="F1646" s="1" t="n">
         <v>46219</v>
       </c>
     </row>
@@ -33397,7 +33397,7 @@
       <c r="E1647" t="n">
         <v>2.969561851921743e-05</v>
       </c>
-      <c r="F1647" s="2" t="n">
+      <c r="F1647" s="1" t="n">
         <v>46219</v>
       </c>
     </row>
@@ -33417,7 +33417,7 @@
       <c r="E1648" t="n">
         <v>-0.0002249129464935356</v>
       </c>
-      <c r="F1648" s="2" t="n">
+      <c r="F1648" s="1" t="n">
         <v>46219</v>
       </c>
     </row>
@@ -33437,7 +33437,7 @@
       <c r="E1649" t="n">
         <v>-9.089563101524687e-05</v>
       </c>
-      <c r="F1649" s="2" t="n">
+      <c r="F1649" s="1" t="n">
         <v>46219</v>
       </c>
     </row>
@@ -33457,7 +33457,7 @@
       <c r="E1650" t="n">
         <v>0.0002610027407011109</v>
       </c>
-      <c r="F1650" s="2" t="n">
+      <c r="F1650" s="1" t="n">
         <v>46219</v>
       </c>
     </row>
@@ -33477,7 +33477,7 @@
       <c r="E1651" t="n">
         <v>0.0001272414258142382</v>
       </c>
-      <c r="F1651" s="2" t="n">
+      <c r="F1651" s="1" t="n">
         <v>46219</v>
       </c>
     </row>
@@ -33497,7 +33497,7 @@
       <c r="E1652" t="n">
         <v>-0.005127509257727185</v>
       </c>
-      <c r="F1652" s="2" t="n">
+      <c r="F1652" s="1" t="n">
         <v>46219</v>
       </c>
     </row>
@@ -33517,7 +33517,3287 @@
       <c r="E1653" t="n">
         <v>-0.00572855887664415</v>
       </c>
-      <c r="F1653" s="2" t="n">
+      <c r="F1653" s="1" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1654">
+      <c r="A1654" t="inlineStr"/>
+      <c r="B1654" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C1654" t="inlineStr">
+        <is>
+          <t>all prior revisions</t>
+        </is>
+      </c>
+      <c r="D1654" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1654" t="n">
+        <v>8.246007532440688e-06</v>
+      </c>
+      <c r="F1654" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1655">
+      <c r="A1655" t="inlineStr"/>
+      <c r="B1655" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C1655" t="inlineStr">
+        <is>
+          <t>pmc_automoveis</t>
+        </is>
+      </c>
+      <c r="D1655" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1655" t="n">
+        <v>1.207821897123077e-06</v>
+      </c>
+      <c r="F1655" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1656">
+      <c r="A1656" t="inlineStr"/>
+      <c r="B1656" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C1656" t="inlineStr">
+        <is>
+          <t>pmc_combustiveis</t>
+        </is>
+      </c>
+      <c r="D1656" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1656" t="n">
+        <v>1.344133175526301e-06</v>
+      </c>
+      <c r="F1656" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1657">
+      <c r="A1657" t="inlineStr"/>
+      <c r="B1657" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C1657" t="inlineStr">
+        <is>
+          <t>pmc_comercio_ampliado</t>
+        </is>
+      </c>
+      <c r="D1657" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1657" t="n">
+        <v>1.303542504504729e-06</v>
+      </c>
+      <c r="F1657" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1658">
+      <c r="A1658" t="inlineStr"/>
+      <c r="B1658" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C1658" t="inlineStr">
+        <is>
+          <t>pmc_eqp_material_escritorio</t>
+        </is>
+      </c>
+      <c r="D1658" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1658" t="n">
+        <v>1.091850950408452e-06</v>
+      </c>
+      <c r="F1658" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1659">
+      <c r="A1659" t="inlineStr"/>
+      <c r="B1659" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C1659" t="inlineStr">
+        <is>
+          <t>pmc_hiper_supermercados</t>
+        </is>
+      </c>
+      <c r="D1659" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1659" t="n">
+        <v>-2.830866322692004e-07</v>
+      </c>
+      <c r="F1659" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1660">
+      <c r="A1660" t="inlineStr"/>
+      <c r="B1660" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C1660" t="inlineStr">
+        <is>
+          <t>pmc_livros_jornais</t>
+        </is>
+      </c>
+      <c r="D1660" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1660" t="n">
+        <v>-1.562179801036465e-05</v>
+      </c>
+      <c r="F1660" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1661">
+      <c r="A1661" t="inlineStr"/>
+      <c r="B1661" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C1661" t="inlineStr">
+        <is>
+          <t>pmc_material_construcao</t>
+        </is>
+      </c>
+      <c r="D1661" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1661" t="n">
+        <v>4.437380453135534e-06</v>
+      </c>
+      <c r="F1661" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1662">
+      <c r="A1662" t="inlineStr"/>
+      <c r="B1662" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C1662" t="inlineStr">
+        <is>
+          <t>pmc_moveis_eletrodomesticos</t>
+        </is>
+      </c>
+      <c r="D1662" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1662" t="n">
+        <v>2.200102319914991e-07</v>
+      </c>
+      <c r="F1662" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1663">
+      <c r="A1663" t="inlineStr"/>
+      <c r="B1663" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C1663" t="inlineStr">
+        <is>
+          <t>pmc_outros_pessoal</t>
+        </is>
+      </c>
+      <c r="D1663" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1663" t="n">
+        <v>-4.442460479509944e-07</v>
+      </c>
+      <c r="F1663" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1664">
+      <c r="A1664" t="inlineStr"/>
+      <c r="B1664" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C1664" t="inlineStr">
+        <is>
+          <t>pmc_vestuário</t>
+        </is>
+      </c>
+      <c r="D1664" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1664" t="n">
+        <v>5.067140203301385e-07</v>
+      </c>
+      <c r="F1664" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1665">
+      <c r="A1665" t="inlineStr"/>
+      <c r="B1665" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C1665" t="inlineStr">
+        <is>
+          <t>abcr_trafego_veiculos_pesados</t>
+        </is>
+      </c>
+      <c r="D1665" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1665" t="n">
+        <v>-3.223645864602196e-06</v>
+      </c>
+      <c r="F1665" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1666">
+      <c r="A1666" t="inlineStr"/>
+      <c r="B1666" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C1666" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1666" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1666" t="n">
+        <v>7.79598762584275e-06</v>
+      </c>
+      <c r="F1666" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1667">
+      <c r="A1667" t="inlineStr"/>
+      <c r="B1667" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C1667" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1667" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1667" t="n">
+        <v>7.728324778615647e-06</v>
+      </c>
+      <c r="F1667" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1668">
+      <c r="A1668" t="inlineStr"/>
+      <c r="B1668" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C1668" t="inlineStr">
+        <is>
+          <t>pmc_automoveis</t>
+        </is>
+      </c>
+      <c r="D1668" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1668" t="n">
+        <v>-4.282267390561504e-06</v>
+      </c>
+      <c r="F1668" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1669">
+      <c r="A1669" t="inlineStr"/>
+      <c r="B1669" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C1669" t="inlineStr">
+        <is>
+          <t>pmc_combustiveis</t>
+        </is>
+      </c>
+      <c r="D1669" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1669" t="n">
+        <v>1.758134959688172e-07</v>
+      </c>
+      <c r="F1669" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1670">
+      <c r="A1670" t="inlineStr"/>
+      <c r="B1670" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C1670" t="inlineStr">
+        <is>
+          <t>pmc_comercio_ampliado</t>
+        </is>
+      </c>
+      <c r="D1670" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1670" t="n">
+        <v>4.37133093619608e-06</v>
+      </c>
+      <c r="F1670" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1671">
+      <c r="A1671" t="inlineStr"/>
+      <c r="B1671" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C1671" t="inlineStr">
+        <is>
+          <t>pmc_eqp_material_escritorio</t>
+        </is>
+      </c>
+      <c r="D1671" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1671" t="n">
+        <v>8.876970712714994e-06</v>
+      </c>
+      <c r="F1671" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1672">
+      <c r="A1672" t="inlineStr"/>
+      <c r="B1672" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C1672" t="inlineStr">
+        <is>
+          <t>pmc_farmaceuticos</t>
+        </is>
+      </c>
+      <c r="D1672" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1672" t="n">
+        <v>-3.256810676238053e-06</v>
+      </c>
+      <c r="F1672" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1673">
+      <c r="A1673" t="inlineStr"/>
+      <c r="B1673" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C1673" t="inlineStr">
+        <is>
+          <t>pmc_hiper_supermercados</t>
+        </is>
+      </c>
+      <c r="D1673" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1673" t="n">
+        <v>3.106706679624229e-06</v>
+      </c>
+      <c r="F1673" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1674">
+      <c r="A1674" t="inlineStr"/>
+      <c r="B1674" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C1674" t="inlineStr">
+        <is>
+          <t>pmc_livros_jornais</t>
+        </is>
+      </c>
+      <c r="D1674" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1674" t="n">
+        <v>-8.645071696717085e-06</v>
+      </c>
+      <c r="F1674" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1675">
+      <c r="A1675" t="inlineStr"/>
+      <c r="B1675" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C1675" t="inlineStr">
+        <is>
+          <t>pmc_material_construcao</t>
+        </is>
+      </c>
+      <c r="D1675" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1675" t="n">
+        <v>-5.58645023541549e-07</v>
+      </c>
+      <c r="F1675" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1676">
+      <c r="A1676" t="inlineStr"/>
+      <c r="B1676" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C1676" t="inlineStr">
+        <is>
+          <t>pmc_moveis_eletrodomesticos</t>
+        </is>
+      </c>
+      <c r="D1676" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1676" t="n">
+        <v>-6.337128968404089e-07</v>
+      </c>
+      <c r="F1676" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1677">
+      <c r="A1677" t="inlineStr"/>
+      <c r="B1677" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C1677" t="inlineStr">
+        <is>
+          <t>pmc_outros_pessoal</t>
+        </is>
+      </c>
+      <c r="D1677" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1677" t="n">
+        <v>2.151931706142258e-06</v>
+      </c>
+      <c r="F1677" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1678">
+      <c r="A1678" t="inlineStr"/>
+      <c r="B1678" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C1678" t="inlineStr">
+        <is>
+          <t>pmc_vestuário</t>
+        </is>
+      </c>
+      <c r="D1678" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1678" t="n">
+        <v>8.275101725335976e-07</v>
+      </c>
+      <c r="F1678" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1679">
+      <c r="A1679" t="inlineStr"/>
+      <c r="B1679" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C1679" t="inlineStr">
+        <is>
+          <t>abcr_trafego_veiculos_pesados</t>
+        </is>
+      </c>
+      <c r="D1679" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1679" t="n">
+        <v>-1.357864006546805e-05</v>
+      </c>
+      <c r="F1679" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1680">
+      <c r="A1680" t="inlineStr"/>
+      <c r="B1680" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C1680" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1680" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1680" t="n">
+        <v>9.553817236285189e-08</v>
+      </c>
+      <c r="F1680" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1681">
+      <c r="A1681" t="inlineStr"/>
+      <c r="B1681" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C1681" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1681" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1681" t="n">
+        <v>9.893616443810922e-08</v>
+      </c>
+      <c r="F1681" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1682">
+      <c r="A1682" t="inlineStr"/>
+      <c r="B1682" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C1682" t="inlineStr">
+        <is>
+          <t>pmc_automoveis</t>
+        </is>
+      </c>
+      <c r="D1682" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1682" t="n">
+        <v>-1.681185713881586e-06</v>
+      </c>
+      <c r="F1682" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1683">
+      <c r="A1683" t="inlineStr"/>
+      <c r="B1683" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C1683" t="inlineStr">
+        <is>
+          <t>pmc_combustiveis</t>
+        </is>
+      </c>
+      <c r="D1683" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1683" t="n">
+        <v>-8.552089650823777e-07</v>
+      </c>
+      <c r="F1683" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1684">
+      <c r="A1684" t="inlineStr"/>
+      <c r="B1684" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C1684" t="inlineStr">
+        <is>
+          <t>pmc_comercio_ampliado</t>
+        </is>
+      </c>
+      <c r="D1684" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1684" t="n">
+        <v>4.720969151807858e-06</v>
+      </c>
+      <c r="F1684" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1685">
+      <c r="A1685" t="inlineStr"/>
+      <c r="B1685" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C1685" t="inlineStr">
+        <is>
+          <t>pmc_eqp_material_escritorio</t>
+        </is>
+      </c>
+      <c r="D1685" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1685" t="n">
+        <v>1.25607410355818e-06</v>
+      </c>
+      <c r="F1685" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1686">
+      <c r="A1686" t="inlineStr"/>
+      <c r="B1686" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C1686" t="inlineStr">
+        <is>
+          <t>pmc_farmaceuticos</t>
+        </is>
+      </c>
+      <c r="D1686" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1686" t="n">
+        <v>-1.834134896548995e-06</v>
+      </c>
+      <c r="F1686" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1687">
+      <c r="A1687" t="inlineStr"/>
+      <c r="B1687" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C1687" t="inlineStr">
+        <is>
+          <t>pmc_hiper_supermercados</t>
+        </is>
+      </c>
+      <c r="D1687" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1687" t="n">
+        <v>1.044382590494506e-08</v>
+      </c>
+      <c r="F1687" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1688">
+      <c r="A1688" t="inlineStr"/>
+      <c r="B1688" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C1688" t="inlineStr">
+        <is>
+          <t>pmc_livros_jornais</t>
+        </is>
+      </c>
+      <c r="D1688" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1688" t="n">
+        <v>1.402205089333825e-06</v>
+      </c>
+      <c r="F1688" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1689">
+      <c r="A1689" t="inlineStr"/>
+      <c r="B1689" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C1689" t="inlineStr">
+        <is>
+          <t>pmc_material_construcao</t>
+        </is>
+      </c>
+      <c r="D1689" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1689" t="n">
+        <v>-1.836746130767779e-06</v>
+      </c>
+      <c r="F1689" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1690">
+      <c r="A1690" t="inlineStr"/>
+      <c r="B1690" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C1690" t="inlineStr">
+        <is>
+          <t>pmc_moveis_eletrodomesticos</t>
+        </is>
+      </c>
+      <c r="D1690" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1690" t="n">
+        <v>3.222603066605215e-07</v>
+      </c>
+      <c r="F1690" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1691">
+      <c r="A1691" t="inlineStr"/>
+      <c r="B1691" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C1691" t="inlineStr">
+        <is>
+          <t>pmc_outros_pessoal</t>
+        </is>
+      </c>
+      <c r="D1691" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1691" t="n">
+        <v>-4.169259318618176e-07</v>
+      </c>
+      <c r="F1691" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1692">
+      <c r="A1692" t="inlineStr"/>
+      <c r="B1692" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C1692" t="inlineStr">
+        <is>
+          <t>pmc_vestuário</t>
+        </is>
+      </c>
+      <c r="D1692" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1692" t="n">
+        <v>2.126029628015407e-06</v>
+      </c>
+      <c r="F1692" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1693">
+      <c r="A1693" t="inlineStr"/>
+      <c r="B1693" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C1693" t="inlineStr">
+        <is>
+          <t>abcr_trafego_veiculos_pesados</t>
+        </is>
+      </c>
+      <c r="D1693" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1693" t="n">
+        <v>3.384764906929038e-06</v>
+      </c>
+      <c r="F1693" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1694">
+      <c r="A1694" t="inlineStr"/>
+      <c r="B1694" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C1694" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1694" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1694" t="n">
+        <v>-7.844775854509416e-07</v>
+      </c>
+      <c r="F1694" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1695">
+      <c r="A1695" t="inlineStr"/>
+      <c r="B1695" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C1695" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1695" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1695" t="n">
+        <v>-7.061661830059068e-07</v>
+      </c>
+      <c r="F1695" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1696">
+      <c r="A1696" t="inlineStr"/>
+      <c r="B1696" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C1696" t="inlineStr">
+        <is>
+          <t>pmc_automoveis</t>
+        </is>
+      </c>
+      <c r="D1696" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1696" t="n">
+        <v>-2.269865432066461e-06</v>
+      </c>
+      <c r="F1696" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1697">
+      <c r="A1697" t="inlineStr"/>
+      <c r="B1697" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C1697" t="inlineStr">
+        <is>
+          <t>pmc_combustiveis</t>
+        </is>
+      </c>
+      <c r="D1697" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1697" t="n">
+        <v>1.454970477471619e-10</v>
+      </c>
+      <c r="F1697" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1698">
+      <c r="A1698" t="inlineStr"/>
+      <c r="B1698" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C1698" t="inlineStr">
+        <is>
+          <t>pmc_comercio_ampliado</t>
+        </is>
+      </c>
+      <c r="D1698" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1698" t="n">
+        <v>-2.071874838594209e-08</v>
+      </c>
+      <c r="F1698" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1699">
+      <c r="A1699" t="inlineStr"/>
+      <c r="B1699" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C1699" t="inlineStr">
+        <is>
+          <t>pmc_eqp_material_escritorio</t>
+        </is>
+      </c>
+      <c r="D1699" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1699" t="n">
+        <v>2.076165061212151e-07</v>
+      </c>
+      <c r="F1699" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1700">
+      <c r="A1700" t="inlineStr"/>
+      <c r="B1700" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C1700" t="inlineStr">
+        <is>
+          <t>pmc_farmaceuticos</t>
+        </is>
+      </c>
+      <c r="D1700" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1700" t="n">
+        <v>-6.370471881375176e-06</v>
+      </c>
+      <c r="F1700" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1701">
+      <c r="A1701" t="inlineStr"/>
+      <c r="B1701" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C1701" t="inlineStr">
+        <is>
+          <t>pmc_hiper_supermercados</t>
+        </is>
+      </c>
+      <c r="D1701" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1701" t="n">
+        <v>-7.11612997328711e-09</v>
+      </c>
+      <c r="F1701" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1702">
+      <c r="A1702" t="inlineStr"/>
+      <c r="B1702" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C1702" t="inlineStr">
+        <is>
+          <t>pmc_livros_jornais</t>
+        </is>
+      </c>
+      <c r="D1702" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1702" t="n">
+        <v>-9.5025578981992e-07</v>
+      </c>
+      <c r="F1702" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1703">
+      <c r="A1703" t="inlineStr"/>
+      <c r="B1703" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C1703" t="inlineStr">
+        <is>
+          <t>pmc_material_construcao</t>
+        </is>
+      </c>
+      <c r="D1703" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1703" t="n">
+        <v>-1.422084780368234e-06</v>
+      </c>
+      <c r="F1703" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1704">
+      <c r="A1704" t="inlineStr"/>
+      <c r="B1704" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C1704" t="inlineStr">
+        <is>
+          <t>pmc_moveis_eletrodomesticos</t>
+        </is>
+      </c>
+      <c r="D1704" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1704" t="n">
+        <v>-1.134222754805974e-06</v>
+      </c>
+      <c r="F1704" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1705">
+      <c r="A1705" t="inlineStr"/>
+      <c r="B1705" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C1705" t="inlineStr">
+        <is>
+          <t>pmc_outros_pessoal</t>
+        </is>
+      </c>
+      <c r="D1705" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1705" t="n">
+        <v>-4.94090707439678e-07</v>
+      </c>
+      <c r="F1705" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1706">
+      <c r="A1706" t="inlineStr"/>
+      <c r="B1706" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C1706" t="inlineStr">
+        <is>
+          <t>pmc_vestuário</t>
+        </is>
+      </c>
+      <c r="D1706" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1706" t="n">
+        <v>6.582069262039224e-06</v>
+      </c>
+      <c r="F1706" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1707">
+      <c r="A1707" t="inlineStr"/>
+      <c r="B1707" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C1707" t="inlineStr">
+        <is>
+          <t>abcr_trafego_veiculos_pesados</t>
+        </is>
+      </c>
+      <c r="D1707" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1707" t="n">
+        <v>-2.55677612534659e-05</v>
+      </c>
+      <c r="F1707" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1708">
+      <c r="A1708" t="inlineStr"/>
+      <c r="B1708" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C1708" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1708" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1708" t="n">
+        <v>-1.392604799512483e-06</v>
+      </c>
+      <c r="F1708" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1709">
+      <c r="A1709" t="inlineStr"/>
+      <c r="B1709" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C1709" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1709" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1709" t="n">
+        <v>-1.045412509170115e-06</v>
+      </c>
+      <c r="F1709" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1710">
+      <c r="A1710" t="inlineStr"/>
+      <c r="B1710" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C1710" t="inlineStr">
+        <is>
+          <t>pmc_automoveis</t>
+        </is>
+      </c>
+      <c r="D1710" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1710" t="n">
+        <v>1.692464386846422e-06</v>
+      </c>
+      <c r="F1710" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1711">
+      <c r="A1711" t="inlineStr"/>
+      <c r="B1711" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C1711" t="inlineStr">
+        <is>
+          <t>pmc_combustiveis</t>
+        </is>
+      </c>
+      <c r="D1711" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1711" t="n">
+        <v>-1.27214698668611e-06</v>
+      </c>
+      <c r="F1711" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1712">
+      <c r="A1712" t="inlineStr"/>
+      <c r="B1712" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C1712" t="inlineStr">
+        <is>
+          <t>pmc_comercio_ampliado</t>
+        </is>
+      </c>
+      <c r="D1712" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1712" t="n">
+        <v>-1.650922574162451e-06</v>
+      </c>
+      <c r="F1712" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1713">
+      <c r="A1713" t="inlineStr"/>
+      <c r="B1713" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C1713" t="inlineStr">
+        <is>
+          <t>pmc_eqp_material_escritorio</t>
+        </is>
+      </c>
+      <c r="D1713" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1713" t="n">
+        <v>-1.464687854390453e-06</v>
+      </c>
+      <c r="F1713" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1714">
+      <c r="A1714" t="inlineStr"/>
+      <c r="B1714" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C1714" t="inlineStr">
+        <is>
+          <t>pmc_farmaceuticos</t>
+        </is>
+      </c>
+      <c r="D1714" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1714" t="n">
+        <v>-3.178780136771357e-06</v>
+      </c>
+      <c r="F1714" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1715">
+      <c r="A1715" t="inlineStr"/>
+      <c r="B1715" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C1715" t="inlineStr">
+        <is>
+          <t>pmc_hiper_supermercados</t>
+        </is>
+      </c>
+      <c r="D1715" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1715" t="n">
+        <v>-7.708133229981593e-07</v>
+      </c>
+      <c r="F1715" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1716">
+      <c r="A1716" t="inlineStr"/>
+      <c r="B1716" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C1716" t="inlineStr">
+        <is>
+          <t>pmc_livros_jornais</t>
+        </is>
+      </c>
+      <c r="D1716" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1716" t="n">
+        <v>1.945843205343752e-06</v>
+      </c>
+      <c r="F1716" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1717">
+      <c r="A1717" t="inlineStr"/>
+      <c r="B1717" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C1717" t="inlineStr">
+        <is>
+          <t>pmc_material_construcao</t>
+        </is>
+      </c>
+      <c r="D1717" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1717" t="n">
+        <v>-4.99539097023956e-06</v>
+      </c>
+      <c r="F1717" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1718">
+      <c r="A1718" t="inlineStr"/>
+      <c r="B1718" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C1718" t="inlineStr">
+        <is>
+          <t>pmc_moveis_eletrodomesticos</t>
+        </is>
+      </c>
+      <c r="D1718" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1718" t="n">
+        <v>-4.339246916448694e-07</v>
+      </c>
+      <c r="F1718" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1719">
+      <c r="A1719" t="inlineStr"/>
+      <c r="B1719" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C1719" t="inlineStr">
+        <is>
+          <t>pmc_outros_pessoal</t>
+        </is>
+      </c>
+      <c r="D1719" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1719" t="n">
+        <v>-6.258779405171244e-08</v>
+      </c>
+      <c r="F1719" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1720">
+      <c r="A1720" t="inlineStr"/>
+      <c r="B1720" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C1720" t="inlineStr">
+        <is>
+          <t>pmc_vestuário</t>
+        </is>
+      </c>
+      <c r="D1720" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1720" t="n">
+        <v>4.242311911207739e-06</v>
+      </c>
+      <c r="F1720" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1721">
+      <c r="A1721" t="inlineStr"/>
+      <c r="B1721" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C1721" t="inlineStr">
+        <is>
+          <t>abcr_trafego_veiculos_pesados</t>
+        </is>
+      </c>
+      <c r="D1721" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1721" t="n">
+        <v>-1.17194629553493e-05</v>
+      </c>
+      <c r="F1721" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1722">
+      <c r="A1722" t="inlineStr"/>
+      <c r="B1722" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C1722" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1722" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1722" t="n">
+        <v>9.783802998802449e-07</v>
+      </c>
+      <c r="F1722" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1723">
+      <c r="A1723" t="inlineStr"/>
+      <c r="B1723" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C1723" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1723" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1723" t="n">
+        <v>5.17420230228916e-07</v>
+      </c>
+      <c r="F1723" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1724">
+      <c r="A1724" t="inlineStr"/>
+      <c r="B1724" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C1724" t="inlineStr">
+        <is>
+          <t>pmc_automoveis</t>
+        </is>
+      </c>
+      <c r="D1724" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1724" t="n">
+        <v>-1.656825728198241e-06</v>
+      </c>
+      <c r="F1724" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1725">
+      <c r="A1725" t="inlineStr"/>
+      <c r="B1725" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C1725" t="inlineStr">
+        <is>
+          <t>pmc_combustiveis</t>
+        </is>
+      </c>
+      <c r="D1725" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1725" t="n">
+        <v>-3.54709984801333e-06</v>
+      </c>
+      <c r="F1725" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1726">
+      <c r="A1726" t="inlineStr"/>
+      <c r="B1726" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C1726" t="inlineStr">
+        <is>
+          <t>pmc_comercio_ampliado</t>
+        </is>
+      </c>
+      <c r="D1726" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1726" t="n">
+        <v>1.556290912898975e-06</v>
+      </c>
+      <c r="F1726" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1727">
+      <c r="A1727" t="inlineStr"/>
+      <c r="B1727" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C1727" t="inlineStr">
+        <is>
+          <t>pmc_eqp_material_escritorio</t>
+        </is>
+      </c>
+      <c r="D1727" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1727" t="n">
+        <v>-3.531322139062435e-06</v>
+      </c>
+      <c r="F1727" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1728">
+      <c r="A1728" t="inlineStr"/>
+      <c r="B1728" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C1728" t="inlineStr">
+        <is>
+          <t>pmc_farmaceuticos</t>
+        </is>
+      </c>
+      <c r="D1728" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1728" t="n">
+        <v>-2.095565808661077e-07</v>
+      </c>
+      <c r="F1728" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1729">
+      <c r="A1729" t="inlineStr"/>
+      <c r="B1729" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C1729" t="inlineStr">
+        <is>
+          <t>pmc_hiper_supermercados</t>
+        </is>
+      </c>
+      <c r="D1729" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1729" t="n">
+        <v>-5.954591768286344e-07</v>
+      </c>
+      <c r="F1729" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1730">
+      <c r="A1730" t="inlineStr"/>
+      <c r="B1730" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C1730" t="inlineStr">
+        <is>
+          <t>pmc_livros_jornais</t>
+        </is>
+      </c>
+      <c r="D1730" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1730" t="n">
+        <v>3.315421252012244e-06</v>
+      </c>
+      <c r="F1730" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1731">
+      <c r="A1731" t="inlineStr"/>
+      <c r="B1731" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C1731" t="inlineStr">
+        <is>
+          <t>pmc_material_construcao</t>
+        </is>
+      </c>
+      <c r="D1731" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1731" t="n">
+        <v>-2.898052457153217e-05</v>
+      </c>
+      <c r="F1731" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1732">
+      <c r="A1732" t="inlineStr"/>
+      <c r="B1732" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C1732" t="inlineStr">
+        <is>
+          <t>pmc_moveis_eletrodomesticos</t>
+        </is>
+      </c>
+      <c r="D1732" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1732" t="n">
+        <v>-4.288843954040003e-06</v>
+      </c>
+      <c r="F1732" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1733">
+      <c r="A1733" t="inlineStr"/>
+      <c r="B1733" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C1733" t="inlineStr">
+        <is>
+          <t>pmc_outros_pessoal</t>
+        </is>
+      </c>
+      <c r="D1733" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1733" t="n">
+        <v>2.52020184985732e-06</v>
+      </c>
+      <c r="F1733" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1734">
+      <c r="A1734" t="inlineStr"/>
+      <c r="B1734" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C1734" t="inlineStr">
+        <is>
+          <t>pmc_vestuário</t>
+        </is>
+      </c>
+      <c r="D1734" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1734" t="n">
+        <v>3.009000544836067e-06</v>
+      </c>
+      <c r="F1734" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1735">
+      <c r="A1735" t="inlineStr"/>
+      <c r="B1735" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C1735" t="inlineStr">
+        <is>
+          <t>abcr_trafego_veiculos_pesados</t>
+        </is>
+      </c>
+      <c r="D1735" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1735" t="n">
+        <v>4.660149661729672e-06</v>
+      </c>
+      <c r="F1735" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1736">
+      <c r="A1736" t="inlineStr"/>
+      <c r="B1736" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C1736" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1736" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1736" t="n">
+        <v>-7.478091423833921e-07</v>
+      </c>
+      <c r="F1736" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1737">
+      <c r="A1737" t="inlineStr"/>
+      <c r="B1737" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C1737" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1737" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1737" t="n">
+        <v>-1.46537061462565e-08</v>
+      </c>
+      <c r="F1737" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1738">
+      <c r="A1738" t="inlineStr"/>
+      <c r="B1738" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C1738" t="inlineStr">
+        <is>
+          <t>pmc_automoveis</t>
+        </is>
+      </c>
+      <c r="D1738" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1738" t="n">
+        <v>-4.965344832456787e-07</v>
+      </c>
+      <c r="F1738" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1739">
+      <c r="A1739" t="inlineStr"/>
+      <c r="B1739" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C1739" t="inlineStr">
+        <is>
+          <t>pmc_combustiveis</t>
+        </is>
+      </c>
+      <c r="D1739" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1739" t="n">
+        <v>-1.77554264460069e-07</v>
+      </c>
+      <c r="F1739" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1740">
+      <c r="A1740" t="inlineStr"/>
+      <c r="B1740" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C1740" t="inlineStr">
+        <is>
+          <t>pmc_comercio_ampliado</t>
+        </is>
+      </c>
+      <c r="D1740" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1740" t="n">
+        <v>-9.723076937402438e-08</v>
+      </c>
+      <c r="F1740" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1741">
+      <c r="A1741" t="inlineStr"/>
+      <c r="B1741" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C1741" t="inlineStr">
+        <is>
+          <t>pmc_eqp_material_escritorio</t>
+        </is>
+      </c>
+      <c r="D1741" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1741" t="n">
+        <v>-1.332910566280778e-06</v>
+      </c>
+      <c r="F1741" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1742">
+      <c r="A1742" t="inlineStr"/>
+      <c r="B1742" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C1742" t="inlineStr">
+        <is>
+          <t>pmc_farmaceuticos</t>
+        </is>
+      </c>
+      <c r="D1742" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1742" t="n">
+        <v>1.48560464042056e-06</v>
+      </c>
+      <c r="F1742" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1743">
+      <c r="A1743" t="inlineStr"/>
+      <c r="B1743" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C1743" t="inlineStr">
+        <is>
+          <t>pmc_hiper_supermercados</t>
+        </is>
+      </c>
+      <c r="D1743" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1743" t="n">
+        <v>-1.804496814270316e-07</v>
+      </c>
+      <c r="F1743" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1744">
+      <c r="A1744" t="inlineStr"/>
+      <c r="B1744" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C1744" t="inlineStr">
+        <is>
+          <t>pmc_livros_jornais</t>
+        </is>
+      </c>
+      <c r="D1744" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1744" t="n">
+        <v>4.24534339459821e-06</v>
+      </c>
+      <c r="F1744" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1745">
+      <c r="A1745" t="inlineStr"/>
+      <c r="B1745" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C1745" t="inlineStr">
+        <is>
+          <t>pmc_material_construcao</t>
+        </is>
+      </c>
+      <c r="D1745" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1745" t="n">
+        <v>-2.528292766236643e-05</v>
+      </c>
+      <c r="F1745" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1746">
+      <c r="A1746" t="inlineStr"/>
+      <c r="B1746" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C1746" t="inlineStr">
+        <is>
+          <t>pmc_moveis_eletrodomesticos</t>
+        </is>
+      </c>
+      <c r="D1746" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1746" t="n">
+        <v>-8.8359938347581e-06</v>
+      </c>
+      <c r="F1746" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1747">
+      <c r="A1747" t="inlineStr"/>
+      <c r="B1747" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C1747" t="inlineStr">
+        <is>
+          <t>pmc_outros_pessoal</t>
+        </is>
+      </c>
+      <c r="D1747" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1747" t="n">
+        <v>5.71342778205716e-06</v>
+      </c>
+      <c r="F1747" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1748">
+      <c r="A1748" t="inlineStr"/>
+      <c r="B1748" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C1748" t="inlineStr">
+        <is>
+          <t>pmc_vestuário</t>
+        </is>
+      </c>
+      <c r="D1748" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1748" t="n">
+        <v>4.448596738461376e-06</v>
+      </c>
+      <c r="F1748" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1749">
+      <c r="A1749" t="inlineStr"/>
+      <c r="B1749" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C1749" t="inlineStr">
+        <is>
+          <t>abcr_trafego_veiculos_pesados</t>
+        </is>
+      </c>
+      <c r="D1749" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1749" t="n">
+        <v>7.128002264134215e-06</v>
+      </c>
+      <c r="F1749" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1750">
+      <c r="A1750" t="inlineStr"/>
+      <c r="B1750" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C1750" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1750" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1750" t="n">
+        <v>-6.988528217275407e-06</v>
+      </c>
+      <c r="F1750" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1751">
+      <c r="A1751" t="inlineStr"/>
+      <c r="B1751" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C1751" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1751" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1751" t="n">
+        <v>-1.008396559250897e-05</v>
+      </c>
+      <c r="F1751" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1752">
+      <c r="A1752" t="inlineStr"/>
+      <c r="B1752" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C1752" t="inlineStr">
+        <is>
+          <t>pmc_automoveis</t>
+        </is>
+      </c>
+      <c r="D1752" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1752" t="n">
+        <v>4.518743296349738e-06</v>
+      </c>
+      <c r="F1752" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1753">
+      <c r="A1753" t="inlineStr"/>
+      <c r="B1753" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C1753" t="inlineStr">
+        <is>
+          <t>pmc_combustiveis</t>
+        </is>
+      </c>
+      <c r="D1753" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1753" t="n">
+        <v>-8.374648018529942e-07</v>
+      </c>
+      <c r="F1753" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1754">
+      <c r="A1754" t="inlineStr"/>
+      <c r="B1754" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C1754" t="inlineStr">
+        <is>
+          <t>pmc_comercio_ampliado</t>
+        </is>
+      </c>
+      <c r="D1754" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1754" t="n">
+        <v>5.00669844825504e-06</v>
+      </c>
+      <c r="F1754" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1755">
+      <c r="A1755" t="inlineStr"/>
+      <c r="B1755" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C1755" t="inlineStr">
+        <is>
+          <t>pmc_eqp_material_escritorio</t>
+        </is>
+      </c>
+      <c r="D1755" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1755" t="n">
+        <v>-9.615458170035022e-06</v>
+      </c>
+      <c r="F1755" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1756">
+      <c r="A1756" t="inlineStr"/>
+      <c r="B1756" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C1756" t="inlineStr">
+        <is>
+          <t>pmc_farmaceuticos</t>
+        </is>
+      </c>
+      <c r="D1756" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1756" t="n">
+        <v>6.578148794722921e-06</v>
+      </c>
+      <c r="F1756" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1757">
+      <c r="A1757" t="inlineStr"/>
+      <c r="B1757" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C1757" t="inlineStr">
+        <is>
+          <t>pmc_hiper_supermercados</t>
+        </is>
+      </c>
+      <c r="D1757" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1757" t="n">
+        <v>-2.867621921860871e-06</v>
+      </c>
+      <c r="F1757" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1758">
+      <c r="A1758" t="inlineStr"/>
+      <c r="B1758" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C1758" t="inlineStr">
+        <is>
+          <t>pmc_livros_jornais</t>
+        </is>
+      </c>
+      <c r="D1758" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1758" t="n">
+        <v>2.281396574271436e-05</v>
+      </c>
+      <c r="F1758" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1759">
+      <c r="A1759" t="inlineStr"/>
+      <c r="B1759" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C1759" t="inlineStr">
+        <is>
+          <t>pmc_material_construcao</t>
+        </is>
+      </c>
+      <c r="D1759" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1759" t="n">
+        <v>-1.441025012932814e-05</v>
+      </c>
+      <c r="F1759" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1760">
+      <c r="A1760" t="inlineStr"/>
+      <c r="B1760" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C1760" t="inlineStr">
+        <is>
+          <t>pmc_moveis_eletrodomesticos</t>
+        </is>
+      </c>
+      <c r="D1760" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1760" t="n">
+        <v>8.115559455071278e-07</v>
+      </c>
+      <c r="F1760" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1761">
+      <c r="A1761" t="inlineStr"/>
+      <c r="B1761" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C1761" t="inlineStr">
+        <is>
+          <t>pmc_outros_pessoal</t>
+        </is>
+      </c>
+      <c r="D1761" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1761" t="n">
+        <v>-4.290938523234334e-06</v>
+      </c>
+      <c r="F1761" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1762">
+      <c r="A1762" t="inlineStr"/>
+      <c r="B1762" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C1762" t="inlineStr">
+        <is>
+          <t>pmc_vestuário</t>
+        </is>
+      </c>
+      <c r="D1762" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1762" t="n">
+        <v>3.804022267666051e-05</v>
+      </c>
+      <c r="F1762" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1763">
+      <c r="A1763" t="inlineStr"/>
+      <c r="B1763" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C1763" t="inlineStr">
+        <is>
+          <t>abcr_trafego_veiculos_pesados</t>
+        </is>
+      </c>
+      <c r="D1763" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1763" t="n">
+        <v>3.789766378615944e-06</v>
+      </c>
+      <c r="F1763" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1764">
+      <c r="A1764" t="inlineStr"/>
+      <c r="B1764" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C1764" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1764" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1764" t="n">
+        <v>-3.271985092355985e-06</v>
+      </c>
+      <c r="F1764" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1765">
+      <c r="A1765" t="inlineStr"/>
+      <c r="B1765" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C1765" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1765" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1765" t="n">
+        <v>-3.78053539057233e-06</v>
+      </c>
+      <c r="F1765" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1766">
+      <c r="A1766" t="inlineStr"/>
+      <c r="B1766" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C1766" t="inlineStr">
+        <is>
+          <t>pmc_automoveis</t>
+        </is>
+      </c>
+      <c r="D1766" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1766" t="n">
+        <v>1.818691264180486e-05</v>
+      </c>
+      <c r="F1766" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1767">
+      <c r="A1767" t="inlineStr"/>
+      <c r="B1767" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C1767" t="inlineStr">
+        <is>
+          <t>pmc_combustiveis</t>
+        </is>
+      </c>
+      <c r="D1767" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1767" t="n">
+        <v>4.913127553285524e-06</v>
+      </c>
+      <c r="F1767" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1768">
+      <c r="A1768" t="inlineStr"/>
+      <c r="B1768" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C1768" t="inlineStr">
+        <is>
+          <t>pmc_comercio_ampliado</t>
+        </is>
+      </c>
+      <c r="D1768" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1768" t="n">
+        <v>1.347721785417444e-05</v>
+      </c>
+      <c r="F1768" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1769">
+      <c r="A1769" t="inlineStr"/>
+      <c r="B1769" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C1769" t="inlineStr">
+        <is>
+          <t>pmc_eqp_material_escritorio</t>
+        </is>
+      </c>
+      <c r="D1769" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1769" t="n">
+        <v>7.25825110089727e-06</v>
+      </c>
+      <c r="F1769" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1770">
+      <c r="A1770" t="inlineStr"/>
+      <c r="B1770" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C1770" t="inlineStr">
+        <is>
+          <t>pmc_farmaceuticos</t>
+        </is>
+      </c>
+      <c r="D1770" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1770" t="n">
+        <v>2.493526774470899e-05</v>
+      </c>
+      <c r="F1770" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1771">
+      <c r="A1771" t="inlineStr"/>
+      <c r="B1771" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C1771" t="inlineStr">
+        <is>
+          <t>pmc_hiper_supermercados</t>
+        </is>
+      </c>
+      <c r="D1771" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1771" t="n">
+        <v>-1.887420460668735e-06</v>
+      </c>
+      <c r="F1771" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1772">
+      <c r="A1772" t="inlineStr"/>
+      <c r="B1772" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C1772" t="inlineStr">
+        <is>
+          <t>pmc_livros_jornais</t>
+        </is>
+      </c>
+      <c r="D1772" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1772" t="n">
+        <v>0.0001704812289414264</v>
+      </c>
+      <c r="F1772" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1773">
+      <c r="A1773" t="inlineStr"/>
+      <c r="B1773" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C1773" t="inlineStr">
+        <is>
+          <t>pmc_material_construcao</t>
+        </is>
+      </c>
+      <c r="D1773" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1773" t="n">
+        <v>-0.0001677443826252357</v>
+      </c>
+      <c r="F1773" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1774">
+      <c r="A1774" t="inlineStr"/>
+      <c r="B1774" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C1774" t="inlineStr">
+        <is>
+          <t>pmc_moveis_eletrodomesticos</t>
+        </is>
+      </c>
+      <c r="D1774" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1774" t="n">
+        <v>4.360484358980698e-05</v>
+      </c>
+      <c r="F1774" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1775">
+      <c r="A1775" t="inlineStr"/>
+      <c r="B1775" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C1775" t="inlineStr">
+        <is>
+          <t>pmc_outros_pessoal</t>
+        </is>
+      </c>
+      <c r="D1775" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1775" t="n">
+        <v>5.594026902069743e-06</v>
+      </c>
+      <c r="F1775" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1776">
+      <c r="A1776" t="inlineStr"/>
+      <c r="B1776" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C1776" t="inlineStr">
+        <is>
+          <t>pmc_vestuário</t>
+        </is>
+      </c>
+      <c r="D1776" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1776" t="n">
+        <v>0.0001198048835095701</v>
+      </c>
+      <c r="F1776" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1777">
+      <c r="A1777" t="inlineStr"/>
+      <c r="B1777" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C1777" t="inlineStr">
+        <is>
+          <t>abcr_trafego_veiculos_pesados</t>
+        </is>
+      </c>
+      <c r="D1777" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1777" t="n">
+        <v>-1.542816207991628e-05</v>
+      </c>
+      <c r="F1777" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1778">
+      <c r="A1778" t="inlineStr"/>
+      <c r="B1778" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C1778" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1778" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1778" t="n">
+        <v>9.195235197053188e-06</v>
+      </c>
+      <c r="F1778" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1779">
+      <c r="A1779" t="inlineStr"/>
+      <c r="B1779" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C1779" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1779" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1779" t="n">
+        <v>9.294120247812856e-06</v>
+      </c>
+      <c r="F1779" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1780">
+      <c r="A1780" t="inlineStr"/>
+      <c r="B1780" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C1780" t="inlineStr">
+        <is>
+          <t>pmc_automoveis</t>
+        </is>
+      </c>
+      <c r="D1780" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1780" t="n">
+        <v>0.0003107742763993191</v>
+      </c>
+      <c r="F1780" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1781">
+      <c r="A1781" t="inlineStr"/>
+      <c r="B1781" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C1781" t="inlineStr">
+        <is>
+          <t>pmc_combustiveis</t>
+        </is>
+      </c>
+      <c r="D1781" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1781" t="n">
+        <v>0.000407071724705421</v>
+      </c>
+      <c r="F1781" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1782">
+      <c r="A1782" t="inlineStr"/>
+      <c r="B1782" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C1782" t="inlineStr">
+        <is>
+          <t>pmc_comercio_ampliado</t>
+        </is>
+      </c>
+      <c r="D1782" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1782" t="n">
+        <v>-0.0001843962952209668</v>
+      </c>
+      <c r="F1782" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1783">
+      <c r="A1783" t="inlineStr"/>
+      <c r="B1783" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C1783" t="inlineStr">
+        <is>
+          <t>pmc_eqp_material_escritorio</t>
+        </is>
+      </c>
+      <c r="D1783" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1783" t="n">
+        <v>-3.763751942496211e-05</v>
+      </c>
+      <c r="F1783" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1784">
+      <c r="A1784" t="inlineStr"/>
+      <c r="B1784" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C1784" t="inlineStr">
+        <is>
+          <t>pmc_farmaceuticos</t>
+        </is>
+      </c>
+      <c r="D1784" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1784" t="n">
+        <v>0.0001559883978051725</v>
+      </c>
+      <c r="F1784" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1785">
+      <c r="A1785" t="inlineStr"/>
+      <c r="B1785" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C1785" t="inlineStr">
+        <is>
+          <t>pmc_hiper_supermercados</t>
+        </is>
+      </c>
+      <c r="D1785" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1785" t="n">
+        <v>-0.0001072825704768896</v>
+      </c>
+      <c r="F1785" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1786">
+      <c r="A1786" t="inlineStr"/>
+      <c r="B1786" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C1786" t="inlineStr">
+        <is>
+          <t>pmc_livros_jornais</t>
+        </is>
+      </c>
+      <c r="D1786" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1786" t="n">
+        <v>0.0008247145573440122</v>
+      </c>
+      <c r="F1786" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1787">
+      <c r="A1787" t="inlineStr"/>
+      <c r="B1787" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C1787" t="inlineStr">
+        <is>
+          <t>pmc_material_construcao</t>
+        </is>
+      </c>
+      <c r="D1787" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1787" t="n">
+        <v>1.271547172100993e-05</v>
+      </c>
+      <c r="F1787" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1788">
+      <c r="A1788" t="inlineStr"/>
+      <c r="B1788" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C1788" t="inlineStr">
+        <is>
+          <t>pmc_moveis_eletrodomesticos</t>
+        </is>
+      </c>
+      <c r="D1788" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1788" t="n">
+        <v>0.0001418576301955089</v>
+      </c>
+      <c r="F1788" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1789">
+      <c r="A1789" t="inlineStr"/>
+      <c r="B1789" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C1789" t="inlineStr">
+        <is>
+          <t>pmc_outros_pessoal</t>
+        </is>
+      </c>
+      <c r="D1789" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1789" t="n">
+        <v>-0.0002903057824728221</v>
+      </c>
+      <c r="F1789" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1790">
+      <c r="A1790" t="inlineStr"/>
+      <c r="B1790" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C1790" t="inlineStr">
+        <is>
+          <t>pmc_vestuário</t>
+        </is>
+      </c>
+      <c r="D1790" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1790" t="n">
+        <v>0.0003332860432011525</v>
+      </c>
+      <c r="F1790" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1791">
+      <c r="A1791" t="inlineStr"/>
+      <c r="B1791" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C1791" t="inlineStr">
+        <is>
+          <t>abcr_trafego_veiculos_pesados</t>
+        </is>
+      </c>
+      <c r="D1791" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1791" t="n">
+        <v>-0.001222592935300837</v>
+      </c>
+      <c r="F1791" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1792">
+      <c r="A1792" t="inlineStr"/>
+      <c r="B1792" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C1792" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1792" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1792" t="n">
+        <v>1.825260503734909e-05</v>
+      </c>
+      <c r="F1792" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1793">
+      <c r="A1793" t="inlineStr"/>
+      <c r="B1793" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C1793" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1793" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1793" t="n">
+        <v>1.711337240027396e-05</v>
+      </c>
+      <c r="F1793" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1794">
+      <c r="A1794" t="inlineStr"/>
+      <c r="B1794" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C1794" t="inlineStr">
+        <is>
+          <t>cni_horas_trabalhadas</t>
+        </is>
+      </c>
+      <c r="D1794" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1794" t="n">
+        <v>-0.00994773912289793</v>
+      </c>
+      <c r="F1794" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1795">
+      <c r="A1795" t="inlineStr"/>
+      <c r="B1795" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C1795" t="inlineStr">
+        <is>
+          <t>cni_massa_salarial</t>
+        </is>
+      </c>
+      <c r="D1795" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1795" t="n">
+        <v>0.002989199750704834</v>
+      </c>
+      <c r="F1795" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1796">
+      <c r="A1796" t="inlineStr"/>
+      <c r="B1796" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C1796" t="inlineStr">
+        <is>
+          <t>cni_nuci_transformacao</t>
+        </is>
+      </c>
+      <c r="D1796" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1796" t="n">
+        <v>-6.045640009189838e-05</v>
+      </c>
+      <c r="F1796" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1797">
+      <c r="A1797" t="inlineStr"/>
+      <c r="B1797" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C1797" t="inlineStr">
+        <is>
+          <t>cni_salario_industria</t>
+        </is>
+      </c>
+      <c r="D1797" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1797" t="n">
+        <v>0.002996357327640589</v>
+      </c>
+      <c r="F1797" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1798">
+      <c r="A1798" t="inlineStr"/>
+      <c r="B1798" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C1798" t="inlineStr">
+        <is>
+          <t>cni_vendas_industriais</t>
+        </is>
+      </c>
+      <c r="D1798" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1798" t="n">
+        <v>0.003410226941534979</v>
+      </c>
+      <c r="F1798" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1799">
+      <c r="A1799" t="inlineStr"/>
+      <c r="B1799" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C1799" t="inlineStr">
+        <is>
+          <t>pmc_automoveis</t>
+        </is>
+      </c>
+      <c r="D1799" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1799" t="n">
+        <v>0.005470538992492859</v>
+      </c>
+      <c r="F1799" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1800">
+      <c r="A1800" t="inlineStr"/>
+      <c r="B1800" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C1800" t="inlineStr">
+        <is>
+          <t>pmc_combustiveis</t>
+        </is>
+      </c>
+      <c r="D1800" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1800" t="n">
+        <v>0.005205787216556093</v>
+      </c>
+      <c r="F1800" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1801">
+      <c r="A1801" t="inlineStr"/>
+      <c r="B1801" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C1801" t="inlineStr">
+        <is>
+          <t>pmc_comercio_ampliado</t>
+        </is>
+      </c>
+      <c r="D1801" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1801" t="n">
+        <v>-0.002672488831409389</v>
+      </c>
+      <c r="F1801" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1802">
+      <c r="A1802" t="inlineStr"/>
+      <c r="B1802" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C1802" t="inlineStr">
+        <is>
+          <t>pmc_eqp_material_escritorio</t>
+        </is>
+      </c>
+      <c r="D1802" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1802" t="n">
+        <v>-0.004398151509546862</v>
+      </c>
+      <c r="F1802" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1803">
+      <c r="A1803" t="inlineStr"/>
+      <c r="B1803" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C1803" t="inlineStr">
+        <is>
+          <t>pmc_farmaceuticos</t>
+        </is>
+      </c>
+      <c r="D1803" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1803" t="n">
+        <v>-0.000631449677728147</v>
+      </c>
+      <c r="F1803" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1804">
+      <c r="A1804" t="inlineStr"/>
+      <c r="B1804" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C1804" t="inlineStr">
+        <is>
+          <t>pmc_hiper_supermercados</t>
+        </is>
+      </c>
+      <c r="D1804" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1804" t="n">
+        <v>-0.003573322393360627</v>
+      </c>
+      <c r="F1804" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1805">
+      <c r="A1805" t="inlineStr"/>
+      <c r="B1805" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C1805" t="inlineStr">
+        <is>
+          <t>pmc_livros_jornais</t>
+        </is>
+      </c>
+      <c r="D1805" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1805" t="n">
+        <v>0.01309881401250364</v>
+      </c>
+      <c r="F1805" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1806">
+      <c r="A1806" t="inlineStr"/>
+      <c r="B1806" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C1806" t="inlineStr">
+        <is>
+          <t>pmc_material_construcao</t>
+        </is>
+      </c>
+      <c r="D1806" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1806" t="n">
+        <v>0.003235814305630498</v>
+      </c>
+      <c r="F1806" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1807">
+      <c r="A1807" t="inlineStr"/>
+      <c r="B1807" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C1807" t="inlineStr">
+        <is>
+          <t>pmc_moveis_eletrodomesticos</t>
+        </is>
+      </c>
+      <c r="D1807" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1807" t="n">
+        <v>0.0009885000798712112</v>
+      </c>
+      <c r="F1807" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1808">
+      <c r="A1808" t="inlineStr"/>
+      <c r="B1808" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C1808" t="inlineStr">
+        <is>
+          <t>pmc_outros_pessoal</t>
+        </is>
+      </c>
+      <c r="D1808" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1808" t="n">
+        <v>-4.805689829863965e-05</v>
+      </c>
+      <c r="F1808" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1809">
+      <c r="A1809" t="inlineStr"/>
+      <c r="B1809" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C1809" t="inlineStr">
+        <is>
+          <t>pmc_vestuário</t>
+        </is>
+      </c>
+      <c r="D1809" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1809" t="n">
+        <v>0.00502996977254115</v>
+      </c>
+      <c r="F1809" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1810">
+      <c r="A1810" t="inlineStr"/>
+      <c r="B1810" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C1810" t="inlineStr">
+        <is>
+          <t>abcr_trafego_veiculos_pesados</t>
+        </is>
+      </c>
+      <c r="D1810" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1810" t="n">
+        <v>-0.0004360136871938982</v>
+      </c>
+      <c r="F1810" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1811">
+      <c r="A1811" t="inlineStr"/>
+      <c r="B1811" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C1811" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1811" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1811" t="n">
+        <v>-5.927403999358086e-05</v>
+      </c>
+      <c r="F1811" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1812">
+      <c r="A1812" t="inlineStr"/>
+      <c r="B1812" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C1812" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1812" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1812" t="n">
+        <v>-4.072862546970229e-05</v>
+      </c>
+      <c r="F1812" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1813">
+      <c r="A1813" t="inlineStr"/>
+      <c r="B1813" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C1813" t="inlineStr">
+        <is>
+          <t>abcr_trafego_veiculos_pesados</t>
+        </is>
+      </c>
+      <c r="D1813" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1813" t="n">
+        <v>-0.0008701938340283357</v>
+      </c>
+      <c r="F1813" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1814">
+      <c r="A1814" t="inlineStr"/>
+      <c r="B1814" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C1814" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1814" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1814" t="n">
+        <v>0.0001102986618497409</v>
+      </c>
+      <c r="F1814" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1815">
+      <c r="A1815" t="inlineStr"/>
+      <c r="B1815" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C1815" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1815" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1815" t="n">
+        <v>0.0001167651525236642</v>
+      </c>
+      <c r="F1815" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1816">
+      <c r="A1816" t="inlineStr"/>
+      <c r="B1816" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="C1816" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="D1816" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1816" t="n">
+        <v>0.0002066999010971059</v>
+      </c>
+      <c r="F1816" s="2" t="n">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="1817">
+      <c r="A1817" t="inlineStr"/>
+      <c r="B1817" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="C1817" t="inlineStr">
+        <is>
+          <t>tjlp</t>
+        </is>
+      </c>
+      <c r="D1817" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E1817" t="n">
+        <v>0.001468471090422343</v>
+      </c>
+      <c r="F1817" s="2" t="n">
         <v>46219</v>
       </c>
     </row>

--- a/pib_nowcast/data/news_impacts.xlsx
+++ b/pib_nowcast/data/news_impacts.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -465,7 +465,7 @@
       <c r="D2" t="n">
         <v>-8.126691234031311e-05</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="1" t="n">
         <v>46240</v>
       </c>
     </row>
@@ -484,7 +484,7 @@
       <c r="D3" t="n">
         <v>-0.001108608352338363</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" s="1" t="n">
         <v>46240</v>
       </c>
     </row>
@@ -503,7 +503,7 @@
       <c r="D4" t="n">
         <v>0.00024377539470378</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" s="1" t="n">
         <v>46240</v>
       </c>
     </row>
@@ -522,7 +522,7 @@
       <c r="D5" t="n">
         <v>-0.001614178628296726</v>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" s="1" t="n">
         <v>46240</v>
       </c>
     </row>
@@ -541,7 +541,7 @@
       <c r="D6" t="n">
         <v>0.001701871533936757</v>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" s="1" t="n">
         <v>46240</v>
       </c>
     </row>
@@ -560,7 +560,7 @@
       <c r="D7" t="n">
         <v>2.848873190176551e-05</v>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E7" s="1" t="n">
         <v>46240</v>
       </c>
     </row>
@@ -579,7 +579,7 @@
       <c r="D8" t="n">
         <v>0.001524521437704299</v>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E8" s="1" t="n">
         <v>46240</v>
       </c>
     </row>
@@ -598,7 +598,7 @@
       <c r="D9" t="n">
         <v>-0.001943998853195455</v>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="E9" s="1" t="n">
         <v>46240</v>
       </c>
     </row>
@@ -617,7 +617,7 @@
       <c r="D10" t="n">
         <v>-0.0002821097777659303</v>
       </c>
-      <c r="E10" s="2" t="n">
+      <c r="E10" s="1" t="n">
         <v>46240</v>
       </c>
     </row>
@@ -636,7 +636,7 @@
       <c r="D11" t="n">
         <v>-3.777919829660626e-05</v>
       </c>
-      <c r="E11" s="2" t="n">
+      <c r="E11" s="1" t="n">
         <v>46240</v>
       </c>
     </row>
@@ -655,7 +655,7 @@
       <c r="D12" t="n">
         <v>-0.0007694182548847285</v>
       </c>
-      <c r="E12" s="2" t="n">
+      <c r="E12" s="1" t="n">
         <v>46240</v>
       </c>
     </row>
@@ -674,7 +674,7 @@
       <c r="D13" t="n">
         <v>-4.454290374177225e-05</v>
       </c>
-      <c r="E13" s="2" t="n">
+      <c r="E13" s="1" t="n">
         <v>46240</v>
       </c>
     </row>
@@ -693,7 +693,7 @@
       <c r="D14" t="n">
         <v>0.000200308158571434</v>
       </c>
-      <c r="E14" s="2" t="n">
+      <c r="E14" s="1" t="n">
         <v>46240</v>
       </c>
     </row>
@@ -712,7 +712,7 @@
       <c r="D15" t="n">
         <v>5.666107010274721e-05</v>
       </c>
-      <c r="E15" s="2" t="n">
+      <c r="E15" s="1" t="n">
         <v>46240</v>
       </c>
     </row>
@@ -731,7 +731,7 @@
       <c r="D16" t="n">
         <v>-0.0003277568540141412</v>
       </c>
-      <c r="E16" s="2" t="n">
+      <c r="E16" s="1" t="n">
         <v>46240</v>
       </c>
     </row>
@@ -750,7 +750,7 @@
       <c r="D17" t="n">
         <v>-0.0001949986969875733</v>
       </c>
-      <c r="E17" s="2" t="n">
+      <c r="E17" s="1" t="n">
         <v>46240</v>
       </c>
     </row>
@@ -769,7 +769,7 @@
       <c r="D18" t="n">
         <v>0.0003117339059989349</v>
       </c>
-      <c r="E18" s="2" t="n">
+      <c r="E18" s="1" t="n">
         <v>46240</v>
       </c>
     </row>
@@ -788,7 +788,7 @@
       <c r="D19" t="n">
         <v>-0.000949587489302886</v>
       </c>
-      <c r="E19" s="2" t="n">
+      <c r="E19" s="1" t="n">
         <v>46240</v>
       </c>
     </row>
@@ -807,7 +807,7 @@
       <c r="D20" t="n">
         <v>-0.001043187779359275</v>
       </c>
-      <c r="E20" s="2" t="n">
+      <c r="E20" s="1" t="n">
         <v>46240</v>
       </c>
     </row>
@@ -826,7 +826,7 @@
       <c r="D21" t="n">
         <v>-4.79608085510735e-05</v>
       </c>
-      <c r="E21" s="2" t="n">
+      <c r="E21" s="1" t="n">
         <v>46240</v>
       </c>
     </row>
@@ -845,7 +845,653 @@
       <c r="D22" t="n">
         <v>-0.0004940493310861029</v>
       </c>
-      <c r="E22" s="2" t="n">
+      <c r="E22" s="1" t="n">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>all prior revisions</t>
+        </is>
+      </c>
+      <c r="C23" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1.15106464788057e-05</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>renda_disponivel_familias_restrita</t>
+        </is>
+      </c>
+      <c r="C24" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1.633816902168775e-05</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>renda_disponivel_familias_restrita</t>
+        </is>
+      </c>
+      <c r="C25" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2.471169484635856e-07</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>renda_disponivel_familias_restrita</t>
+        </is>
+      </c>
+      <c r="C26" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-1.419800479802919e-05</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>renda_disponivel_familias_restrita</t>
+        </is>
+      </c>
+      <c r="C27" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-2.317572198492144e-05</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>renda_disponivel_familias_restrita</t>
+        </is>
+      </c>
+      <c r="C28" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1.452149514361988e-05</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>renda_disponivel_familias_restrita</t>
+        </is>
+      </c>
+      <c r="C29" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="D29" t="n">
+        <v>6.393587692111317e-05</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>renda_disponivel_familias_restrita</t>
+        </is>
+      </c>
+      <c r="C30" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="D30" t="n">
+        <v>9.698704635327377e-06</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>renda_disponivel_familias_restrita</t>
+        </is>
+      </c>
+      <c r="C31" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="D31" t="n">
+        <v>-1.916503084360479e-05</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>renda_disponivel_familias_restrita</t>
+        </is>
+      </c>
+      <c r="C32" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.0001058249029697257</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>renda_disponivel_familias_restrita</t>
+        </is>
+      </c>
+      <c r="C33" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.0002160153670333602</v>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>renda_disponivel_familias_restrita</t>
+        </is>
+      </c>
+      <c r="C34" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.0002295363218063912</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>renda_disponivel_familias_restrita</t>
+        </is>
+      </c>
+      <c r="C35" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.000832071169331189</v>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>fenabrave_automoveis</t>
+        </is>
+      </c>
+      <c r="C36" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="D36" t="n">
+        <v>-8.142875761010998e-05</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>fenabrave_caminhoes</t>
+        </is>
+      </c>
+      <c r="C37" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="D37" t="n">
+        <v>-0.001108654383831067</v>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>fenabrave_comerciais_leves</t>
+        </is>
+      </c>
+      <c r="C38" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.000243284140548568</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>fenabrave_onibus</t>
+        </is>
+      </c>
+      <c r="C39" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="D39" t="n">
+        <v>-0.001613699684221471</v>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>fgv_nuci</t>
+        </is>
+      </c>
+      <c r="C40" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.001698634537654017</v>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>icc_fecomercio</t>
+        </is>
+      </c>
+      <c r="C41" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="D41" t="n">
+        <v>2.867230058804029e-05</v>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>icc_fgv</t>
+        </is>
+      </c>
+      <c r="C42" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.001523680762862606</v>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>icc_fgv_expectativas</t>
+        </is>
+      </c>
+      <c r="C43" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="D43" t="n">
+        <v>-0.001943337837204015</v>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>icc_fgv_sit_atual</t>
+        </is>
+      </c>
+      <c r="C44" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="D44" t="n">
+        <v>-0.0002829544528194856</v>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>icea_fecomercio</t>
+        </is>
+      </c>
+      <c r="C45" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="D45" t="n">
+        <v>-3.797481577728544e-05</v>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>ics_fgv</t>
+        </is>
+      </c>
+      <c r="C46" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="D46" t="n">
+        <v>-0.0007689275195947562</v>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>ief_fecomercio</t>
+        </is>
+      </c>
+      <c r="C47" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="D47" t="n">
+        <v>-4.410445251140596e-05</v>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>ies_fgv</t>
+        </is>
+      </c>
+      <c r="C48" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0.0001999728390234171</v>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>igp10</t>
+        </is>
+      </c>
+      <c r="C49" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="D49" t="n">
+        <v>5.661059667602294e-05</v>
+      </c>
+      <c r="E49" s="2" t="n">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>igpm</t>
+        </is>
+      </c>
+      <c r="C50" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="D50" t="n">
+        <v>-0.0003274813584186116</v>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>ipam</t>
+        </is>
+      </c>
+      <c r="C51" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="D51" t="n">
+        <v>-0.0001948173824728746</v>
+      </c>
+      <c r="E51" s="2" t="n">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>ipc_fipe</t>
+        </is>
+      </c>
+      <c r="C52" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0.0003118526883013769</v>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>ipca15</t>
+        </is>
+      </c>
+      <c r="C53" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="D53" t="n">
+        <v>-0.0009490116059240602</v>
+      </c>
+      <c r="E53" s="2" t="n">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>isas_fgv</t>
+        </is>
+      </c>
+      <c r="C54" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="D54" t="n">
+        <v>-0.001041463465361672</v>
+      </c>
+      <c r="E54" s="2" t="n">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="C55" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="D55" t="n">
+        <v>-4.819620790830977e-05</v>
+      </c>
+      <c r="E55" s="2" t="n">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="C56" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="D56" t="n">
+        <v>-0.0004943221834701289</v>
+      </c>
+      <c r="E56" s="2" t="n">
         <v>46240</v>
       </c>
     </row>

--- a/pib_nowcast/data/news_impacts.xlsx
+++ b/pib_nowcast/data/news_impacts.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:E90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -864,7 +864,7 @@
       <c r="D23" t="n">
         <v>1.15106464788057e-05</v>
       </c>
-      <c r="E23" s="2" t="n">
+      <c r="E23" s="1" t="n">
         <v>46240</v>
       </c>
     </row>
@@ -883,7 +883,7 @@
       <c r="D24" t="n">
         <v>1.633816902168775e-05</v>
       </c>
-      <c r="E24" s="2" t="n">
+      <c r="E24" s="1" t="n">
         <v>46240</v>
       </c>
     </row>
@@ -902,7 +902,7 @@
       <c r="D25" t="n">
         <v>2.471169484635856e-07</v>
       </c>
-      <c r="E25" s="2" t="n">
+      <c r="E25" s="1" t="n">
         <v>46240</v>
       </c>
     </row>
@@ -921,7 +921,7 @@
       <c r="D26" t="n">
         <v>-1.419800479802919e-05</v>
       </c>
-      <c r="E26" s="2" t="n">
+      <c r="E26" s="1" t="n">
         <v>46240</v>
       </c>
     </row>
@@ -940,7 +940,7 @@
       <c r="D27" t="n">
         <v>-2.317572198492144e-05</v>
       </c>
-      <c r="E27" s="2" t="n">
+      <c r="E27" s="1" t="n">
         <v>46240</v>
       </c>
     </row>
@@ -959,7 +959,7 @@
       <c r="D28" t="n">
         <v>1.452149514361988e-05</v>
       </c>
-      <c r="E28" s="2" t="n">
+      <c r="E28" s="1" t="n">
         <v>46240</v>
       </c>
     </row>
@@ -978,7 +978,7 @@
       <c r="D29" t="n">
         <v>6.393587692111317e-05</v>
       </c>
-      <c r="E29" s="2" t="n">
+      <c r="E29" s="1" t="n">
         <v>46240</v>
       </c>
     </row>
@@ -997,7 +997,7 @@
       <c r="D30" t="n">
         <v>9.698704635327377e-06</v>
       </c>
-      <c r="E30" s="2" t="n">
+      <c r="E30" s="1" t="n">
         <v>46240</v>
       </c>
     </row>
@@ -1016,7 +1016,7 @@
       <c r="D31" t="n">
         <v>-1.916503084360479e-05</v>
       </c>
-      <c r="E31" s="2" t="n">
+      <c r="E31" s="1" t="n">
         <v>46240</v>
       </c>
     </row>
@@ -1035,7 +1035,7 @@
       <c r="D32" t="n">
         <v>0.0001058249029697257</v>
       </c>
-      <c r="E32" s="2" t="n">
+      <c r="E32" s="1" t="n">
         <v>46240</v>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       <c r="D33" t="n">
         <v>0.0002160153670333602</v>
       </c>
-      <c r="E33" s="2" t="n">
+      <c r="E33" s="1" t="n">
         <v>46240</v>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       <c r="D34" t="n">
         <v>0.0002295363218063912</v>
       </c>
-      <c r="E34" s="2" t="n">
+      <c r="E34" s="1" t="n">
         <v>46240</v>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
       <c r="D35" t="n">
         <v>0.000832071169331189</v>
       </c>
-      <c r="E35" s="2" t="n">
+      <c r="E35" s="1" t="n">
         <v>46240</v>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
       <c r="D36" t="n">
         <v>-8.142875761010998e-05</v>
       </c>
-      <c r="E36" s="2" t="n">
+      <c r="E36" s="1" t="n">
         <v>46240</v>
       </c>
     </row>
@@ -1130,7 +1130,7 @@
       <c r="D37" t="n">
         <v>-0.001108654383831067</v>
       </c>
-      <c r="E37" s="2" t="n">
+      <c r="E37" s="1" t="n">
         <v>46240</v>
       </c>
     </row>
@@ -1149,7 +1149,7 @@
       <c r="D38" t="n">
         <v>0.000243284140548568</v>
       </c>
-      <c r="E38" s="2" t="n">
+      <c r="E38" s="1" t="n">
         <v>46240</v>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       <c r="D39" t="n">
         <v>-0.001613699684221471</v>
       </c>
-      <c r="E39" s="2" t="n">
+      <c r="E39" s="1" t="n">
         <v>46240</v>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       <c r="D40" t="n">
         <v>0.001698634537654017</v>
       </c>
-      <c r="E40" s="2" t="n">
+      <c r="E40" s="1" t="n">
         <v>46240</v>
       </c>
     </row>
@@ -1206,7 +1206,7 @@
       <c r="D41" t="n">
         <v>2.867230058804029e-05</v>
       </c>
-      <c r="E41" s="2" t="n">
+      <c r="E41" s="1" t="n">
         <v>46240</v>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       <c r="D42" t="n">
         <v>0.001523680762862606</v>
       </c>
-      <c r="E42" s="2" t="n">
+      <c r="E42" s="1" t="n">
         <v>46240</v>
       </c>
     </row>
@@ -1244,7 +1244,7 @@
       <c r="D43" t="n">
         <v>-0.001943337837204015</v>
       </c>
-      <c r="E43" s="2" t="n">
+      <c r="E43" s="1" t="n">
         <v>46240</v>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
       <c r="D44" t="n">
         <v>-0.0002829544528194856</v>
       </c>
-      <c r="E44" s="2" t="n">
+      <c r="E44" s="1" t="n">
         <v>46240</v>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="D45" t="n">
         <v>-3.797481577728544e-05</v>
       </c>
-      <c r="E45" s="2" t="n">
+      <c r="E45" s="1" t="n">
         <v>46240</v>
       </c>
     </row>
@@ -1301,7 +1301,7 @@
       <c r="D46" t="n">
         <v>-0.0007689275195947562</v>
       </c>
-      <c r="E46" s="2" t="n">
+      <c r="E46" s="1" t="n">
         <v>46240</v>
       </c>
     </row>
@@ -1320,7 +1320,7 @@
       <c r="D47" t="n">
         <v>-4.410445251140596e-05</v>
       </c>
-      <c r="E47" s="2" t="n">
+      <c r="E47" s="1" t="n">
         <v>46240</v>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
       <c r="D48" t="n">
         <v>0.0001999728390234171</v>
       </c>
-      <c r="E48" s="2" t="n">
+      <c r="E48" s="1" t="n">
         <v>46240</v>
       </c>
     </row>
@@ -1358,7 +1358,7 @@
       <c r="D49" t="n">
         <v>5.661059667602294e-05</v>
       </c>
-      <c r="E49" s="2" t="n">
+      <c r="E49" s="1" t="n">
         <v>46240</v>
       </c>
     </row>
@@ -1377,7 +1377,7 @@
       <c r="D50" t="n">
         <v>-0.0003274813584186116</v>
       </c>
-      <c r="E50" s="2" t="n">
+      <c r="E50" s="1" t="n">
         <v>46240</v>
       </c>
     </row>
@@ -1396,7 +1396,7 @@
       <c r="D51" t="n">
         <v>-0.0001948173824728746</v>
       </c>
-      <c r="E51" s="2" t="n">
+      <c r="E51" s="1" t="n">
         <v>46240</v>
       </c>
     </row>
@@ -1415,7 +1415,7 @@
       <c r="D52" t="n">
         <v>0.0003118526883013769</v>
       </c>
-      <c r="E52" s="2" t="n">
+      <c r="E52" s="1" t="n">
         <v>46240</v>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       <c r="D53" t="n">
         <v>-0.0009490116059240602</v>
       </c>
-      <c r="E53" s="2" t="n">
+      <c r="E53" s="1" t="n">
         <v>46240</v>
       </c>
     </row>
@@ -1453,7 +1453,7 @@
       <c r="D54" t="n">
         <v>-0.001041463465361672</v>
       </c>
-      <c r="E54" s="2" t="n">
+      <c r="E54" s="1" t="n">
         <v>46240</v>
       </c>
     </row>
@@ -1472,7 +1472,7 @@
       <c r="D55" t="n">
         <v>-4.819620790830977e-05</v>
       </c>
-      <c r="E55" s="2" t="n">
+      <c r="E55" s="1" t="n">
         <v>46240</v>
       </c>
     </row>
@@ -1491,8 +1491,654 @@
       <c r="D56" t="n">
         <v>-0.0004943221834701289</v>
       </c>
-      <c r="E56" s="2" t="n">
-        <v>46240</v>
+      <c r="E56" s="1" t="n">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>all prior revisions</t>
+        </is>
+      </c>
+      <c r="C57" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="D57" t="n">
+        <v>-2.528942744824517e-05</v>
+      </c>
+      <c r="E57" s="2" t="n">
+        <v>46244</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>renda_disponivel_familias_restrita</t>
+        </is>
+      </c>
+      <c r="C58" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="D58" t="n">
+        <v>-1.117764666225425e-05</v>
+      </c>
+      <c r="E58" s="2" t="n">
+        <v>46244</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>renda_disponivel_familias_restrita</t>
+        </is>
+      </c>
+      <c r="C59" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="D59" t="n">
+        <v>-1.24788089202755e-05</v>
+      </c>
+      <c r="E59" s="2" t="n">
+        <v>46244</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>renda_disponivel_familias_restrita</t>
+        </is>
+      </c>
+      <c r="C60" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="D60" t="n">
+        <v>-1.685278284713985e-05</v>
+      </c>
+      <c r="E60" s="2" t="n">
+        <v>46244</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>renda_disponivel_familias_restrita</t>
+        </is>
+      </c>
+      <c r="C61" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="D61" t="n">
+        <v>-1.87885197407752e-05</v>
+      </c>
+      <c r="E61" s="2" t="n">
+        <v>46244</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>renda_disponivel_familias_restrita</t>
+        </is>
+      </c>
+      <c r="C62" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="D62" t="n">
+        <v>-2.500184451735792e-05</v>
+      </c>
+      <c r="E62" s="2" t="n">
+        <v>46244</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>renda_disponivel_familias_restrita</t>
+        </is>
+      </c>
+      <c r="C63" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="D63" t="n">
+        <v>-4.271523438180692e-05</v>
+      </c>
+      <c r="E63" s="2" t="n">
+        <v>46244</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>renda_disponivel_familias_restrita</t>
+        </is>
+      </c>
+      <c r="C64" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="D64" t="n">
+        <v>-5.804784524227483e-06</v>
+      </c>
+      <c r="E64" s="2" t="n">
+        <v>46244</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>renda_disponivel_familias_restrita</t>
+        </is>
+      </c>
+      <c r="C65" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="D65" t="n">
+        <v>8.953889313844862e-05</v>
+      </c>
+      <c r="E65" s="2" t="n">
+        <v>46244</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>renda_disponivel_familias_restrita</t>
+        </is>
+      </c>
+      <c r="C66" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="D66" t="n">
+        <v>0.0008638617190723843</v>
+      </c>
+      <c r="E66" s="2" t="n">
+        <v>46244</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>renda_disponivel_familias_restrita</t>
+        </is>
+      </c>
+      <c r="C67" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="D67" t="n">
+        <v>0.0002939902121925856</v>
+      </c>
+      <c r="E67" s="2" t="n">
+        <v>46244</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>renda_disponivel_familias_restrita</t>
+        </is>
+      </c>
+      <c r="C68" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="D68" t="n">
+        <v>-0.002762835451270456</v>
+      </c>
+      <c r="E68" s="2" t="n">
+        <v>46244</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>renda_disponivel_familias_restrita</t>
+        </is>
+      </c>
+      <c r="C69" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="D69" t="n">
+        <v>-0.02698379305766073</v>
+      </c>
+      <c r="E69" s="2" t="n">
+        <v>46244</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>fenabrave_automoveis</t>
+        </is>
+      </c>
+      <c r="C70" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="D70" t="n">
+        <v>0.003512010340958517</v>
+      </c>
+      <c r="E70" s="2" t="n">
+        <v>46244</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>fenabrave_caminhoes</t>
+        </is>
+      </c>
+      <c r="C71" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="D71" t="n">
+        <v>-0.002686178116471233</v>
+      </c>
+      <c r="E71" s="2" t="n">
+        <v>46244</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>fenabrave_comerciais_leves</t>
+        </is>
+      </c>
+      <c r="C72" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0.002774834388765657</v>
+      </c>
+      <c r="E72" s="2" t="n">
+        <v>46244</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>fenabrave_onibus</t>
+        </is>
+      </c>
+      <c r="C73" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="D73" t="n">
+        <v>-0.006561046083275131</v>
+      </c>
+      <c r="E73" s="2" t="n">
+        <v>46244</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>fgv_nuci</t>
+        </is>
+      </c>
+      <c r="C74" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0.005694489430968932</v>
+      </c>
+      <c r="E74" s="2" t="n">
+        <v>46244</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>icc_fecomercio</t>
+        </is>
+      </c>
+      <c r="C75" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0.002347625462108646</v>
+      </c>
+      <c r="E75" s="2" t="n">
+        <v>46244</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>icea_fecomercio</t>
+        </is>
+      </c>
+      <c r="C76" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0.01015552718744247</v>
+      </c>
+      <c r="E76" s="2" t="n">
+        <v>46244</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>ics_fgv</t>
+        </is>
+      </c>
+      <c r="C77" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="D77" t="n">
+        <v>0.0006877711081332372</v>
+      </c>
+      <c r="E77" s="2" t="n">
+        <v>46244</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>ief_fecomercio</t>
+        </is>
+      </c>
+      <c r="C78" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="D78" t="n">
+        <v>-0.001772492048902851</v>
+      </c>
+      <c r="E78" s="2" t="n">
+        <v>46244</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>ies_fgv</t>
+        </is>
+      </c>
+      <c r="C79" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="D79" t="n">
+        <v>0.004508416076204451</v>
+      </c>
+      <c r="E79" s="2" t="n">
+        <v>46244</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>igp10</t>
+        </is>
+      </c>
+      <c r="C80" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="D80" t="n">
+        <v>-3.171614884085385e-05</v>
+      </c>
+      <c r="E80" s="2" t="n">
+        <v>46244</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>igpdi</t>
+        </is>
+      </c>
+      <c r="C81" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="D81" t="n">
+        <v>0.0008026557231704687</v>
+      </c>
+      <c r="E81" s="2" t="n">
+        <v>46244</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>igpm</t>
+        </is>
+      </c>
+      <c r="C82" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="D82" t="n">
+        <v>0.0006622111291148791</v>
+      </c>
+      <c r="E82" s="2" t="n">
+        <v>46244</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>incc</t>
+        </is>
+      </c>
+      <c r="C83" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="D83" t="n">
+        <v>-0.004446169057270473</v>
+      </c>
+      <c r="E83" s="2" t="n">
+        <v>46244</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>ipam</t>
+        </is>
+      </c>
+      <c r="C84" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="D84" t="n">
+        <v>0.0008250392256279481</v>
+      </c>
+      <c r="E84" s="2" t="n">
+        <v>46244</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>ipc_fipe</t>
+        </is>
+      </c>
+      <c r="C85" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="D85" t="n">
+        <v>0.0007516933096820372</v>
+      </c>
+      <c r="E85" s="2" t="n">
+        <v>46244</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>ipca15</t>
+        </is>
+      </c>
+      <c r="C86" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="D86" t="n">
+        <v>-0.003150723008772063</v>
+      </c>
+      <c r="E86" s="2" t="n">
+        <v>46244</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>ipcbr</t>
+        </is>
+      </c>
+      <c r="C87" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="D87" t="n">
+        <v>-0.002873056368610362</v>
+      </c>
+      <c r="E87" s="2" t="n">
+        <v>46244</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>isas_fgv</t>
+        </is>
+      </c>
+      <c r="C88" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="D88" t="n">
+        <v>-0.008277124040279978</v>
+      </c>
+      <c r="E88" s="2" t="n">
+        <v>46244</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="C89" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="D89" t="n">
+        <v>0.0009351672631495607</v>
+      </c>
+      <c r="E89" s="2" t="n">
+        <v>46244</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="C90" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="D90" t="n">
+        <v>0.0004802710789203777</v>
+      </c>
+      <c r="E90" s="2" t="n">
+        <v>46244</v>
       </c>
     </row>
   </sheetData>
